--- a/Live_Dummy_MCP_Traces.xlsx
+++ b/Live_Dummy_MCP_Traces.xlsx
@@ -878,21 +878,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Here’s what I found for order ORD-9002 (laptop stand) for Rahul Mehta:
-- Status: Delayed
-- Reason: Weather disruption at the regional sorting center
-- New estimated delivery: Today, 2026-07-13
+          <t>Here’s what I found for Rahul Mehta (C-1002) and order ORD-9002:
+- Status: Delayed in transit.
+- Cause: Weather disruption at the regional sorting center.
+- Item: Laptop stand ($45).
+- Current ETA: Today (2026-07-13).
 What happens next:
-- It should be delivered by end of day today. If it doesn’t arrive, reply here and I can escalate the shipment or discuss alternatives (reship or refund options) right away. If you’d like, I can also set up delivery alerts to rahul@example.com.</t>
+- It should arrive today. If it doesn’t show up by end of day, reply here and I’ll escalate with the carrier and update the ETA.
+- Refunds: Our system shows the item itself isn’t eligible for a refund right now. Per our delivery delay policy, we can review refunding shipping fees if the delay exceeds 5 days.
+Would you like me to open a support ticket to monitor the delivery and keep you updated automatically?</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status</t>
+          <t>get_customer_profile,get_order_status,search_policy_docs,calculate_refund</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -929,20 +932,21 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Here’s what I found:
-- Order ORD-9003 (Smartwatch) for customer C-1003 was delivered 42 days ago.
-- Our refund policy allows refunds within 30 days of delivery. After 30 days, refunds aren’t eligible unless the item is damaged/defective and needs manual review.
-- The system shows this order is not eligible for a standard refund because it’s beyond the 30‑day window.
-Next steps:
-- If the smartwatch is defective, damaged, or not working as expected, I can open a manual review ticket to assess options (exchange, repair, or exception). Please let me know the issue details (what’s wrong, when it started, photos or error messages). Otherwise, a standard refund isn’t available at this time.</t>
+- Order ORD-9003 for customer C-1003 was delivered 42 days ago.
+- Our refund policy allows most delivered items to be refunded within 30 days. After 30 days, only damaged/defective items can be escalated for manual review.
+- The refund check shows the order isn’t eligible for a standard refund (calculated refund amount: $0) because it’s outside the 30‑day window.
+What’s next:
+- If the smartwatch is damaged or defective, I can open a manual review ticket. Please confirm the issue and share any photos of the damage, and I’ll submit it right away.
+- If it’s not damaged, a refund isn’t available under the policy. If you’d like, I can check warranty or repair options.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>get_order_status,get_customer_profile,search_policy_docs,calculate_refund</t>
+          <t>get_order_status,search_policy_docs,calculate_refund</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -978,14 +982,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>I’ve created a support ticket for customer C-1001.
-- Ticket ID: T-1001
+          <t>I’ve created a support ticket for you.
+- Ticket ID: T-1002
+- Customer: C-1001
 - Issue: Delivered package arrived damaged
 - Priority: Normal
 - Status: Open
-Next steps:
-- A support agent will review the ticket and contact the customer for details and photos of the damage.
-- If confirmed, we’ll proceed with a replacement or refund according to policy.</t>
+What’s next:
+- A support agent will review the ticket and reach out for details or photos of the damage if needed.
+- If you have the order ID and any photos of the damaged items/packaging, please share them here to speed up the resolution.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1013,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,148 +1180,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CASE-002</t>
+          <t>CASE-001</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>get_order_status</t>
+          <t>search_policy_docs</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>{
-  "order_id": "ORD-9003"
+  "query": "late delivery policy weather disruption shipping refund eligibility"
 }</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>{
-  "order_id": "ORD-9003",
-  "customer_id": "C-1003",
-  "status": "delivered",
-  "item": "Smartwatch",
-  "amount": 149.0,
-  "delivered_days_ago": 42,
-  "issue": "Customer asked about refund eligibility."
-}</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>MCPToolCall(
-    name='get_order_status',
-    args={'order_id': 'ORD-9003'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"order_id": "ORD-9003", "customer_id": "C-1003", "status": "delivered", "item": "Smartwatch", "amount": 149.0, "delivered_days_ago": 42, "issue": "Customer asked about refund eligibility."}'
-        )
-    ],
-    isError=False
-)
-)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CASE-002</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>get_customer_profile</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1003"
-}</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1003",
-  "name": "Maya Rao",
-  "tier": "Standard",
-  "primary_order_id": "ORD-9003",
-  "email": "maya@example.com"
-}</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>MCPToolCall(
-    name='get_customer_profile',
-    args={'customer_id': 'C-1003'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"customer_id": "C-1003", "name": "Maya Rao", "tier": "Standard", "primary_order_id": "ORD-9003", "email": "maya@example.com"}'
-        )
-    ],
-    isError=False
-)
-)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CASE-002</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>search_policy_docs</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>{
-  "query": "refund policy for returns and refunds: return window days after delivery; electronics or smartwatches; exceptions for defective or DOA; restocking fees; store credit; warranty repair; late returns"
-}</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>{
-  "query": "refund policy for returns and refunds: return window days after delivery; electronics or smartwatches; exceptions for defective or DOA; restocking fees; store credit; warranty repair; late returns",
+  "query": "late delivery policy weather disruption shipping refund eligibility",
   "matches": [
     {
       "policy_id": "refund",
@@ -1332,16 +1223,16 @@
 }</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>MCPToolCall(
     name='search_policy_docs',
-    args={'query': 'refund policy for returns and refunds: return window days after delivery; electronics or smartwatches; exceptions for defective or DOA; restocking fees; store credit; warranty repair; late returns'},
+    args={'query': 'late delivery policy weather disruption shipping refund eligibility'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"query": "refund policy for returns and refunds: return window days after delivery; electronics or smartwatches; exceptions for defective or DOA; restocking fees; store credit; warranty repair; late returns", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
+            text='{"query": "late delivery policy weather disruption shipping refund eligibility", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
         )
     ],
     isError=False
@@ -1350,6 +1241,120 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CASE-001</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>calculate_refund</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9002",
+  "reason": "delivery delayed due to weather"
+}</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9002",
+  "eligible": false,
+  "refund_amount": 0.0,
+  "reason": "Order is outside the 30 day refund window."
+}</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MCPToolCall(
+    name='calculate_refund',
+    args={'order_id': 'ORD-9002', 'reason': 'delivery delayed due to weather'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"order_id": "ORD-9002", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
+        )
+    ],
+    isError=False
+)
+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CASE-002</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>get_order_status</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9003"
+}</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9003",
+  "customer_id": "C-1003",
+  "status": "delivered",
+  "item": "Smartwatch",
+  "amount": 149.0,
+  "delivered_days_ago": 42,
+  "issue": "Customer asked about refund eligibility."
+}</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>MCPToolCall(
+    name='get_order_status',
+    args={'order_id': 'ORD-9003'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"order_id": "ORD-9003", "customer_id": "C-1003", "status": "delivered", "item": "Smartwatch", "amount": 149.0, "delivered_days_ago": 42, "issue": "Customer asked about refund eligibility."}'
+        )
+    ],
+    isError=False
+)
+)</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -1360,25 +1365,89 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>search_policy_docs</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>{
+  "query": "refund policy delivered orders electronics smartwatch days since delivery window"
+}</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>{
+  "query": "refund policy delivered orders electronics smartwatch days since delivery window",
+  "matches": [
+    {
+      "policy_id": "refund",
+      "title": "Refund policy",
+      "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."
+    },
+    {
+      "policy_id": "delivery",
+      "title": "Delivery delay policy",
+      "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MCPToolCall(
+    name='search_policy_docs',
+    args={'query': 'refund policy delivered orders electronics smartwatch days since delivery window'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"query": "refund policy delivered orders electronics smartwatch days since delivery window", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
+        )
+    ],
+    isError=False
+)
+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CASE-002</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
         <v>3</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>calculate_refund</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>{
   "order_id": "ORD-9003",
-  "reason": "Customer inquiring about standard refund eligibility for delivered smartwatch 42 days after delivery"
+  "reason": "Customer is asking about refund eligibility for delivered smartwatch 42 days ago"
 }</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>{
   "order_id": "ORD-9003",
@@ -1388,11 +1457,11 @@
 }</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>MCPToolCall(
     name='calculate_refund',
-    args={'order_id': 'ORD-9003', 'reason': 'Customer inquiring about standard refund eligibility for delivered smartwatch 42 days after delivery'},
+    args={'order_id': 'ORD-9003', 'reason': 'Customer is asking about refund eligibility for delivered smartwatch 42 days ago'},
     result=CallToolResult(
     content=[
         TextContent(
@@ -1406,57 +1475,57 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>CASE-003</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C9" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>create_support_ticket</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>{
   "customer_id": "C-1001",
-  "issue_summary": "Delivered package arrived damaged.",
+  "issue_summary": "Delivered package arrived damaged",
   "priority": "normal"
 }</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>{
-  "ticket_id": "T-1001",
+  "ticket_id": "T-1002",
   "customer_id": "C-1001",
-  "issue_summary": "Delivered package arrived damaged.",
+  "issue_summary": "Delivered package arrived damaged",
   "priority": "normal",
   "status": "open",
-  "created_at": "2026-07-13T11:06:34"
+  "created_at": "2026-07-13T14:05:07"
 }</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>MCPToolCall(
     name='create_support_ticket',
-    args={'customer_id': 'C-1001', 'issue_summary': 'Delivered package arrived damaged.', 'priority': 'normal'},
+    args={'customer_id': 'C-1001', 'issue_summary': 'Delivered package arrived damaged', 'priority': 'normal'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"ticket_id": "T-1001", "customer_id": "C-1001", "issue_summary": "Delivered package arrived damaged.", "priority": "normal", "status": "open", "created_at": "2026-07-13T11:06:34"}'
+            text='{"ticket_id": "T-1002", "customer_id": "C-1001", "issue_summary": "Delivered package arrived damaged", "priority": "normal", "status": "open", "created_at": "2026-07-13T14:05:07"}'
         )
     ],
     isError=False
@@ -1601,6 +1670,32 @@
     ],
     isError=False
 )
+)
+MCPToolCall(
+    name='search_policy_docs',
+    args={'query': 'late delivery policy weather disruption shipping refund eligibility'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"query": "late delivery policy weather disruption shipping refund eligibility", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
+        )
+    ],
+    isError=False
+)
+)
+MCPToolCall(
+    name='calculate_refund',
+    args={'order_id': 'ORD-9002', 'reason': 'delivery delayed due to weather'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"order_id": "ORD-9002", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
+        )
+    ],
+    isError=False
+)
 )</t>
         </is>
       </c>
@@ -1608,7 +1703,7 @@
         <is>
           <t>LLMTestCase(
     input='Customer C-1002 says their order is late. Check what happened and explain it.',
-    actual_output='Here’s what I found for order ORD-9002 (laptop stand) for Rahul Mehta:\n\n- Status: Delayed\n- Reason: Weather disruption at the regional sorting center\n- New estimated delivery: Today, 2026-07-13\n\nWhat happens next:\n- It should be delivered by end of day today. If it doesn’t arrive, reply here and I can escalate the shipment or discuss alternatives (reship or refund options) right away. If you’d like, I can also set up delivery alerts to rahul@example.com.',
+    actual_output='Here’s what I found for Rahul Mehta (C-1002) and order ORD-9002:\n\n- Status: Delayed in transit.\n- Cause: Weather disruption at the regional sorting center.\n- Item: Laptop stand ($45).\n- Current ETA: Today (2026-07-13).\n\nWhat happens next:\n- It should arrive today. If it doesn’t show up by end of day, reply here and I’ll escalate with the carrier and update the ETA.\n- Refunds: Our system shows the item itself isn’t eligible for a refund right now. Per our delivery delay policy, we can review refunding shipping fees if the delay exceeds 5 days.\n\nWould you like me to open a support ticket to monitor the delivery and keep you updated automatically?',
     expected_outcome='The assistant should look up the customer/order, call the order status tool, and explain the delay.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
@@ -1633,6 +1728,32 @@
                 TextContent(
                     type="text",
                     text='{"order_id": "ORD-9002", "customer_id": "C-1002", "status": "delayed", "item": "Laptop stand", "amount": 45.0, "delay_reason": "Weather disruption at the regional sorting center.", "estimated_delivery": "2026-07-13"}'
+                )
+            ],
+            isError=False
+        )
+        ),
+        MCPToolCall(
+            name='search_policy_docs',
+            args={'query': 'late delivery policy weather disruption shipping refund eligibility'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"query": "late delivery policy weather disruption shipping refund eligibility", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
+                )
+            ],
+            isError=False
+        )
+        ),
+        MCPToolCall(
+            name='calculate_refund',
+            args={'order_id': 'ORD-9002', 'reason': 'delivery delayed due to weather'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"order_id": "ORD-9002", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
                 )
             ],
             isError=False
@@ -1732,26 +1853,13 @@
 )
 )
 MCPToolCall(
-    name='get_customer_profile',
-    args={'customer_id': 'C-1003'},
+    name='search_policy_docs',
+    args={'query': 'refund policy delivered orders electronics smartwatch days since delivery window'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"customer_id": "C-1003", "name": "Maya Rao", "tier": "Standard", "primary_order_id": "ORD-9003", "email": "maya@example.com"}'
-        )
-    ],
-    isError=False
-)
-)
-MCPToolCall(
-    name='search_policy_docs',
-    args={'query': 'refund policy for returns and refunds: return window days after delivery; electronics or smartwatches; exceptions for defective or DOA; restocking fees; store credit; warranty repair; late returns'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"query": "refund policy for returns and refunds: return window days after delivery; electronics or smartwatches; exceptions for defective or DOA; restocking fees; store credit; warranty repair; late returns", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
+            text='{"query": "refund policy delivered orders electronics smartwatch days since delivery window", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
         )
     ],
     isError=False
@@ -1759,7 +1867,7 @@
 )
 MCPToolCall(
     name='calculate_refund',
-    args={'order_id': 'ORD-9003', 'reason': 'Customer inquiring about standard refund eligibility for delivered smartwatch 42 days after delivery'},
+    args={'order_id': 'ORD-9003', 'reason': 'Customer is asking about refund eligibility for delivered smartwatch 42 days ago'},
     result=CallToolResult(
     content=[
         TextContent(
@@ -1776,7 +1884,7 @@
         <is>
           <t>LLMTestCase(
     input='Customer C-1003 wants to know whether order ORD-9003 can be refunded.',
-    actual_output='Here’s what I found:\n\n- Order ORD-9003 (Smartwatch) for customer C-1003 was delivered 42 days ago.\n- Our refund policy allows refunds within 30 days of delivery. After 30 days, refunds aren’t eligible unless the item is damaged/defective and needs manual review.\n- The system shows this order is not eligible for a standard refund because it’s beyond the 30‑day window.\n\nNext steps:\n- If the smartwatch is defective, damaged, or not working as expected, I can open a manual review ticket to assess options (exchange, repair, or exception). Please let me know the issue details (what’s wrong, when it started, photos or error messages). Otherwise, a standard refund isn’t available at this time.',
+    actual_output='Here’s what I found:\n- Order ORD-9003 for customer C-1003 was delivered 42 days ago.\n- Our refund policy allows most delivered items to be refunded within 30 days. After 30 days, only damaged/defective items can be escalated for manual review.\n- The refund check shows the order isn’t eligible for a standard refund (calculated refund amount: $0) because it’s outside the 30‑day window.\n\nWhat’s next:\n- If the smartwatch is damaged or defective, I can open a manual review ticket. Please confirm the issue and share any photos of the damage, and I’ll submit it right away.\n- If it’s not damaged, a refund isn’t available under the policy. If you’d like, I can check warranty or repair options.',
     expected_outcome='The assistant should inspect the order, check the refund policy, calculate refund eligibility, and explain the result.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
@@ -1794,34 +1902,21 @@
         )
         ),
         MCPToolCall(
-            name='get_customer_profile',
-            args={'customer_id': 'C-1003'},
+            name='search_policy_docs',
+            args={'query': 'refund policy delivered orders electronics smartwatch days since delivery window'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"customer_id": "C-1003", "name": "Maya Rao", "tier": "Standard", "primary_order_id": "ORD-9003", "email": "maya@example.com"}'
+                    text='{"query": "refund policy delivered orders electronics smartwatch days since delivery window", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
                 )
             ],
             isError=False
         )
         ),
         MCPToolCall(
-            name='search_policy_docs',
-            args={'query': 'refund policy for returns and refunds: return window days after delivery; electronics or smartwatches; exceptions for defective or DOA; restocking fees; store credit; warranty repair; late returns'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"query": "refund policy for returns and refunds: return window days after delivery; electronics or smartwatches; exceptions for defective or DOA; restocking fees; store credit; warranty repair; late returns", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
-                )
-            ],
-            isError=False
-        )
-        ),
-        MCPToolCall(
             name='calculate_refund',
-            args={'order_id': 'ORD-9003', 'reason': 'Customer inquiring about standard refund eligibility for delivered smartwatch 42 days after delivery'},
+            args={'order_id': 'ORD-9003', 'reason': 'Customer is asking about refund eligibility for delivered smartwatch 42 days ago'},
             result=CallToolResult(
             content=[
                 TextContent(
@@ -1914,12 +2009,12 @@
         <is>
           <t>MCPToolCall(
     name='create_support_ticket',
-    args={'customer_id': 'C-1001', 'issue_summary': 'Delivered package arrived damaged.', 'priority': 'normal'},
+    args={'customer_id': 'C-1001', 'issue_summary': 'Delivered package arrived damaged', 'priority': 'normal'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"ticket_id": "T-1001", "customer_id": "C-1001", "issue_summary": "Delivered package arrived damaged.", "priority": "normal", "status": "open", "created_at": "2026-07-13T11:06:34"}'
+            text='{"ticket_id": "T-1002", "customer_id": "C-1001", "issue_summary": "Delivered package arrived damaged", "priority": "normal", "status": "open", "created_at": "2026-07-13T14:05:07"}'
         )
     ],
     isError=False
@@ -1931,18 +2026,18 @@
         <is>
           <t>LLMTestCase(
     input='Create a support ticket for customer C-1001 because their delivered package arrived damaged.',
-    actual_output='I’ve created a support ticket for customer C-1001.\n\n- Ticket ID: T-1001\n- Issue: Delivered package arrived damaged\n- Priority: Normal\n- Status: Open\n\nNext steps:\n- A support agent will review the ticket and contact the customer for details and photos of the damage.\n- If confirmed, we’ll proceed with a replacement or refund according to policy.',
+    actual_output='I’ve created a support ticket for you.\n\n- Ticket ID: T-1002\n- Customer: C-1001\n- Issue: Delivered package arrived damaged\n- Priority: Normal\n- Status: Open\n\nWhat’s next:\n- A support agent will review the ticket and reach out for details or photos of the damage if needed.\n- If you have the order ID and any photos of the damaged items/packaging, please share them here to speed up the resolution.',
     expected_outcome='The assistant should look up the customer and create a support ticket with the damaged package issue.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
         MCPToolCall(
             name='create_support_ticket',
-            args={'customer_id': 'C-1001', 'issue_summary': 'Delivered package arrived damaged.', 'priority': 'normal'},
+            args={'customer_id': 'C-1001', 'issue_summary': 'Delivered package arrived damaged', 'priority': 'normal'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"ticket_id": "T-1001", "customer_id": "C-1001", "issue_summary": "Delivered package arrived damaged.", "priority": "normal", "status": "open", "created_at": "2026-07-13T11:06:34"}'
+                    text='{"ticket_id": "T-1002", "customer_id": "C-1001", "issue_summary": "Delivered package arrived damaged", "priority": "normal", "status": "open", "created_at": "2026-07-13T14:05:07"}'
                 )
             ],
             isError=False

--- a/Live_Dummy_MCP_Traces.xlsx
+++ b/Live_Dummy_MCP_Traces.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="input_cases" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="tool_definitions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="llm_outputs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="tool_calls" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="deepeval_objects" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="negative_demo_cases" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="tool_definitions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="llm_outputs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="tool_calls" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="deepeval_objects" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -559,6 +560,114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>case_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>user_input</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>expected_outcome</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>expected_tools</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>actual_output</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>tool_name</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tool_arguments</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>tool_result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NEGATIVE-DEMO-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Customer C-1002 says their order is late. Check what happened and explain it.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>The assistant should look up customer C-1002, identify order ORD-9002, call the order status tool, and explain the delay.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>I created a low-priority ticket for customer C-1003, but I did not check the delayed order.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>create_support_ticket</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>{'customer_id': 'C-1003', 'issue_summary': 'General follow-up requested.', 'priority': 'low'}</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{'ticket_id': 'T-NEGATIVE-DEMO', 'customer_id': 'C-1003', 'issue_summary': 'General follow-up requested.', 'priority': 'low', 'status': 'open'}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -794,231 +903,296 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>case_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>case_type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>user_input</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>expected_outcome</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>expected_tools</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>actual_output</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>tools_called</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tool_call_count</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>run_status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CASE-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Customer C-1002 says their order is late. Check what happened and explain it.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>The assistant should look up the customer/order, call the order status tool, and explain the delay.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Here’s what I found for Rahul Mehta (C-1002) and order ORD-9002:
-- Status: Delayed in transit.
-- Cause: Weather disruption at the regional sorting center.
-- Item: Laptop stand ($45).
-- Current ETA: Today (2026-07-13).
-What happens next:
-- It should arrive today. If it doesn’t show up by end of day, reply here and I’ll escalate with the carrier and update the ETA.
-- Refunds: Our system shows the item itself isn’t eligible for a refund right now. Per our delivery delay policy, we can review refunding shipping fees if the delay exceeds 5 days.
-Would you like me to open a support ticket to monitor the delivery and keep you updated automatically?</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,search_policy_docs,calculate_refund</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CASE-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Customer C-1003 wants to know whether order ORD-9003 can be refunded.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>The assistant should inspect the order, check the refund policy, calculate refund eligibility, and explain the result.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>get_order_status,search_policy_docs,calculate_refund</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Here’s what I found:
-- Order ORD-9003 for customer C-1003 was delivered 42 days ago.
-- Our refund policy allows most delivered items to be refunded within 30 days. After 30 days, only damaged/defective items can be escalated for manual review.
-- The refund check shows the order isn’t eligible for a standard refund (calculated refund amount: $0) because it’s outside the 30‑day window.
-What’s next:
-- If the smartwatch is damaged or defective, I can open a manual review ticket. Please confirm the issue and share any photos of the damage, and I’ll submit it right away.
-- If it’s not damaged, a refund isn’t available under the policy. If you’d like, I can check warranty or repair options.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>get_order_status,search_policy_docs,calculate_refund</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CASE-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Create a support ticket for customer C-1001 because their delivered package arrived damaged.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>The assistant should look up the customer and create a support ticket with the damaged package issue.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>get_customer_profile,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>I’ve created a support ticket for you.
-- Ticket ID: T-1002
-- Customer: C-1001
-- Issue: Delivered package arrived damaged
-- Priority: Normal
-- Status: Open
-What’s next:
-- A support agent will review the ticket and reach out for details or photos of the damage if needed.
-- If you have the order ID and any photos of the damaged items/packaging, please share them here to speed up the resolution.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>create_support_ticket</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>case_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>user_input</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>expected_outcome</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>expected_tools</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>expected_label</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>actual_output</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tools_called</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>tool_call_count</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>run_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CASE-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Customer C-1002 says their order is late. Check what happened and explain it.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>The assistant should look up the customer/order, call the order status tool, and explain the delay.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>I checked your order ORD-9002 (Laptop stand). It’s showing as delayed due to a weather disruption at the regional sorting center. The latest estimated delivery date is today, 2026-07-13.
+What happens next:
+- Please allow delivery until the end of today. It should arrive as the network clears.
+- If it doesn’t show up by end of day, reply here and I’ll escalate the case immediately and review options (such as a replacement or refund) per our policy.
+- If you’d like, I can also set up delivery updates for you.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CASE-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Customer C-1003 wants to know whether order ORD-9003 can be refunded.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The assistant should inspect the order, check the refund policy, calculate refund eligibility, and explain the result.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>get_order_status,search_policy_docs,calculate_refund</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Here’s what I found:
+- Order ORD-9003 (Smartwatch, $149) for customer C-1003 was delivered 42 days ago.
+- Our refund policy allows most delivered items to be refunded within 30 days. After 30 days, refunds are generally not available unless the item is damaged or defective, in which case we can escalate for manual review.
+What’s next:
+- If this is a change‑of‑mind return, it isn’t eligible for a refund.
+- If the smartwatch is damaged/defective, please share details and photos, and I can open a support ticket to escalate the case for review.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>get_order_status,search_policy_docs</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CASE-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Create a support ticket for customer C-1001 because their delivered package arrived damaged.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>The assistant should look up the customer and create a support ticket with the damaged package issue.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>get_customer_profile,create_support_ticket</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I’ve created a support ticket to address the damaged delivery.
+- Ticket ID: T-1005
+- Customer: C-1001
+- Issue: Delivered package arrived damaged; customer requests replacement or refund
+- Status: Open
+- Priority: Normal
+Next steps:
+- We’ll review the customer’s order and photos (if available) and reach out with replacement or refund options.
+- If you have the order ID or images of the damage, please share them here to expedite the resolution.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>create_support_ticket</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NEGATIVE-DEMO-001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Customer C-1002 says their order is late. Check what happened and explain it.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>The assistant should look up customer C-1002, identify order ORD-9002, call the order status tool, and explain the delay.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I created a low-priority ticket for customer C-1003, but I did not check the delayed order.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>create_support_ticket</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>negative_demo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1180,34 +1354,92 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CASE-001</t>
+          <t>CASE-002</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>get_order_status</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9003"
+}</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9003",
+  "customer_id": "C-1003",
+  "status": "delivered",
+  "item": "Smartwatch",
+  "amount": 149.0,
+  "delivered_days_ago": 42,
+  "issue": "Customer asked about refund eligibility."
+}</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>MCPToolCall(
+    name='get_order_status',
+    args={'order_id': 'ORD-9003'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"order_id": "ORD-9003", "customer_id": "C-1003", "status": "delivered", "item": "Smartwatch", "amount": 149.0, "delivered_days_ago": 42, "issue": "Customer asked about refund eligibility."}'
+        )
+    ],
+    isError=False
+)
+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CASE-002</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>search_policy_docs</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>{
-  "query": "late delivery policy weather disruption shipping refund eligibility"
+  "query": "refund policy return window eligibility delivered orders cancellations, defective item, change of mind"
 }</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>{
-  "query": "late delivery policy weather disruption shipping refund eligibility",
+  "query": "refund policy return window eligibility delivered orders cancellations, defective item, change of mind",
   "matches": [
     {
       "policy_id": "refund",
@@ -1223,16 +1455,16 @@
 }</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>MCPToolCall(
     name='search_policy_docs',
-    args={'query': 'late delivery policy weather disruption shipping refund eligibility'},
+    args={'query': 'refund policy return window eligibility delivered orders cancellations, defective item, change of mind'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"query": "late delivery policy weather disruption shipping refund eligibility", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
+            text='{"query": "refund policy return window eligibility delivered orders cancellations, defective item, change of mind", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
         )
     ],
     isError=False
@@ -1241,54 +1473,57 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CASE-001</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CASE-003</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>calculate_refund</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>create_support_ticket</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>{
-  "order_id": "ORD-9002",
-  "reason": "delivery delayed due to weather"
+  "customer_id": "C-1001",
+  "issue_summary": "Delivered package arrived damaged. Customer requests assistance with replacement or refund.",
+  "priority": "normal"
 }</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>{
-  "order_id": "ORD-9002",
-  "eligible": false,
-  "refund_amount": 0.0,
-  "reason": "Order is outside the 30 day refund window."
+  "ticket_id": "T-1005",
+  "customer_id": "C-1001",
+  "issue_summary": "Delivered package arrived damaged. Customer requests assistance with replacement or refund.",
+  "priority": "normal",
+  "status": "open",
+  "created_at": "2026-07-13T15:13:47"
 }</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>MCPToolCall(
-    name='calculate_refund',
-    args={'order_id': 'ORD-9002', 'reason': 'delivery delayed due to weather'},
+    name='create_support_ticket',
+    args={'customer_id': 'C-1001', 'issue_summary': 'Delivered package arrived damaged. Customer requests assistance with replacement or refund.', 'priority': 'normal'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"order_id": "ORD-9002", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
+            text='{"ticket_id": "T-1005", "customer_id": "C-1001", "issue_summary": "Delivered package arrived damaged. Customer requests assistance with replacement or refund.", "priority": "normal", "status": "open", "created_at": "2026-07-13T15:13:47"}'
         )
     ],
     isError=False
@@ -1297,235 +1532,56 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CASE-002</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NEGATIVE-DEMO-001</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>get_order_status</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>create_support_ticket</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>{
-  "order_id": "ORD-9003"
+  "customer_id": "C-1003",
+  "issue_summary": "General follow-up requested.",
+  "priority": "low"
 }</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>{
-  "order_id": "ORD-9003",
+  "ticket_id": "T-NEGATIVE-DEMO",
   "customer_id": "C-1003",
-  "status": "delivered",
-  "item": "Smartwatch",
-  "amount": 149.0,
-  "delivered_days_ago": 42,
-  "issue": "Customer asked about refund eligibility."
+  "issue_summary": "General follow-up requested.",
+  "priority": "low",
+  "status": "open"
 }</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>MCPToolCall(
-    name='get_order_status',
-    args={'order_id': 'ORD-9003'},
+    name='create_support_ticket',
+    args={'customer_id': 'C-1003', 'issue_summary': 'General follow-up requested.', 'priority': 'low'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"order_id": "ORD-9003", "customer_id": "C-1003", "status": "delivered", "item": "Smartwatch", "amount": 149.0, "delivered_days_ago": 42, "issue": "Customer asked about refund eligibility."}'
-        )
-    ],
-    isError=False
-)
-)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CASE-002</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>search_policy_docs</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>{
-  "query": "refund policy delivered orders electronics smartwatch days since delivery window"
-}</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>{
-  "query": "refund policy delivered orders electronics smartwatch days since delivery window",
-  "matches": [
-    {
-      "policy_id": "refund",
-      "title": "Refund policy",
-      "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."
-    },
-    {
-      "policy_id": "delivery",
-      "title": "Delivery delay policy",
-      "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>MCPToolCall(
-    name='search_policy_docs',
-    args={'query': 'refund policy delivered orders electronics smartwatch days since delivery window'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"query": "refund policy delivered orders electronics smartwatch days since delivery window", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
-        )
-    ],
-    isError=False
-)
-)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CASE-002</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>calculate_refund</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9003",
-  "reason": "Customer is asking about refund eligibility for delivered smartwatch 42 days ago"
-}</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9003",
-  "eligible": false,
-  "refund_amount": 0.0,
-  "reason": "Order is outside the 30 day refund window."
-}</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>MCPToolCall(
-    name='calculate_refund',
-    args={'order_id': 'ORD-9003', 'reason': 'Customer is asking about refund eligibility for delivered smartwatch 42 days ago'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"order_id": "ORD-9003", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
-        )
-    ],
-    isError=False
-)
-)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CASE-003</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>create_support_ticket</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1001",
-  "issue_summary": "Delivered package arrived damaged",
-  "priority": "normal"
-}</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>{
-  "ticket_id": "T-1002",
-  "customer_id": "C-1001",
-  "issue_summary": "Delivered package arrived damaged",
-  "priority": "normal",
-  "status": "open",
-  "created_at": "2026-07-13T14:05:07"
-}</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>MCPToolCall(
-    name='create_support_ticket',
-    args={'customer_id': 'C-1001', 'issue_summary': 'Delivered package arrived damaged', 'priority': 'normal'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"ticket_id": "T-1002", "customer_id": "C-1001", "issue_summary": "Delivered package arrived damaged", "priority": "normal", "status": "open", "created_at": "2026-07-13T14:05:07"}'
+            text='{"ticket_id": "T-NEGATIVE-DEMO", "customer_id": "C-1003", "issue_summary": "General follow-up requested.", "priority": "low", "status": "open"}'
         )
     ],
     isError=False
@@ -1539,13 +1595,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1670,32 +1726,6 @@
     ],
     isError=False
 )
-)
-MCPToolCall(
-    name='search_policy_docs',
-    args={'query': 'late delivery policy weather disruption shipping refund eligibility'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"query": "late delivery policy weather disruption shipping refund eligibility", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
-        )
-    ],
-    isError=False
-)
-)
-MCPToolCall(
-    name='calculate_refund',
-    args={'order_id': 'ORD-9002', 'reason': 'delivery delayed due to weather'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"order_id": "ORD-9002", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
-        )
-    ],
-    isError=False
-)
 )</t>
         </is>
       </c>
@@ -1703,7 +1733,7 @@
         <is>
           <t>LLMTestCase(
     input='Customer C-1002 says their order is late. Check what happened and explain it.',
-    actual_output='Here’s what I found for Rahul Mehta (C-1002) and order ORD-9002:\n\n- Status: Delayed in transit.\n- Cause: Weather disruption at the regional sorting center.\n- Item: Laptop stand ($45).\n- Current ETA: Today (2026-07-13).\n\nWhat happens next:\n- It should arrive today. If it doesn’t show up by end of day, reply here and I’ll escalate with the carrier and update the ETA.\n- Refunds: Our system shows the item itself isn’t eligible for a refund right now. Per our delivery delay policy, we can review refunding shipping fees if the delay exceeds 5 days.\n\nWould you like me to open a support ticket to monitor the delivery and keep you updated automatically?',
+    actual_output='I checked your order ORD-9002 (Laptop stand). It’s showing as delayed due to a weather disruption at the regional sorting center. The latest estimated delivery date is today, 2026-07-13.\n\nWhat happens next:\n- Please allow delivery until the end of today. It should arrive as the network clears.\n- If it doesn’t show up by end of day, reply here and I’ll escalate the case immediately and review options (such as a replacement or refund) per our policy.\n- If you’d like, I can also set up delivery updates for you.',
     expected_outcome='The assistant should look up the customer/order, call the order status tool, and explain the delay.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
@@ -1728,32 +1758,6 @@
                 TextContent(
                     type="text",
                     text='{"order_id": "ORD-9002", "customer_id": "C-1002", "status": "delayed", "item": "Laptop stand", "amount": 45.0, "delay_reason": "Weather disruption at the regional sorting center.", "estimated_delivery": "2026-07-13"}'
-                )
-            ],
-            isError=False
-        )
-        ),
-        MCPToolCall(
-            name='search_policy_docs',
-            args={'query': 'late delivery policy weather disruption shipping refund eligibility'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"query": "late delivery policy weather disruption shipping refund eligibility", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
-                )
-            ],
-            isError=False
-        )
-        ),
-        MCPToolCall(
-            name='calculate_refund',
-            args={'order_id': 'ORD-9002', 'reason': 'delivery delayed due to weather'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"order_id": "ORD-9002", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
                 )
             ],
             isError=False
@@ -1854,29 +1858,16 @@
 )
 MCPToolCall(
     name='search_policy_docs',
-    args={'query': 'refund policy delivered orders electronics smartwatch days since delivery window'},
+    args={'query': 'refund policy return window eligibility delivered orders cancellations, defective item, change of mind'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"query": "refund policy delivered orders electronics smartwatch days since delivery window", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
+            text='{"query": "refund policy return window eligibility delivered orders cancellations, defective item, change of mind", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
         )
     ],
     isError=False
 )
-)
-MCPToolCall(
-    name='calculate_refund',
-    args={'order_id': 'ORD-9003', 'reason': 'Customer is asking about refund eligibility for delivered smartwatch 42 days ago'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"order_id": "ORD-9003", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
-        )
-    ],
-    isError=False
-)
 )</t>
         </is>
       </c>
@@ -1884,7 +1875,7 @@
         <is>
           <t>LLMTestCase(
     input='Customer C-1003 wants to know whether order ORD-9003 can be refunded.',
-    actual_output='Here’s what I found:\n- Order ORD-9003 for customer C-1003 was delivered 42 days ago.\n- Our refund policy allows most delivered items to be refunded within 30 days. After 30 days, only damaged/defective items can be escalated for manual review.\n- The refund check shows the order isn’t eligible for a standard refund (calculated refund amount: $0) because it’s outside the 30‑day window.\n\nWhat’s next:\n- If the smartwatch is damaged or defective, I can open a manual review ticket. Please confirm the issue and share any photos of the damage, and I’ll submit it right away.\n- If it’s not damaged, a refund isn’t available under the policy. If you’d like, I can check warranty or repair options.',
+    actual_output='Here’s what I found:\n- Order ORD-9003 (Smartwatch, $149) for customer C-1003 was delivered 42 days ago.\n- Our refund policy allows most delivered items to be refunded within 30 days. After 30 days, refunds are generally not available unless the item is damaged or defective, in which case we can escalate for manual review.\n\nWhat’s next:\n- If this is a change‑of‑mind return, it isn’t eligible for a refund.\n- If the smartwatch is damaged/defective, please share details and photos, and I can open a support ticket to escalate the case for review.',
     expected_outcome='The assistant should inspect the order, check the refund policy, calculate refund eligibility, and explain the result.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
@@ -1903,25 +1894,12 @@
         ),
         MCPToolCall(
             name='search_policy_docs',
-            args={'query': 'refund policy delivered orders electronics smartwatch days since delivery window'},
+            args={'query': 'refund policy return window eligibility delivered orders cancellations, defective item, change of mind'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"query": "refund policy delivered orders electronics smartwatch days since delivery window", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
-                )
-            ],
-            isError=False
-        )
-        ),
-        MCPToolCall(
-            name='calculate_refund',
-            args={'order_id': 'ORD-9003', 'reason': 'Customer is asking about refund eligibility for delivered smartwatch 42 days ago'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"order_id": "ORD-9003", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
+                    text='{"query": "refund policy return window eligibility delivered orders cancellations, defective item, change of mind", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}]}'
                 )
             ],
             isError=False
@@ -2009,12 +1987,12 @@
         <is>
           <t>MCPToolCall(
     name='create_support_ticket',
-    args={'customer_id': 'C-1001', 'issue_summary': 'Delivered package arrived damaged', 'priority': 'normal'},
+    args={'customer_id': 'C-1001', 'issue_summary': 'Delivered package arrived damaged. Customer requests assistance with replacement or refund.', 'priority': 'normal'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"ticket_id": "T-1002", "customer_id": "C-1001", "issue_summary": "Delivered package arrived damaged", "priority": "normal", "status": "open", "created_at": "2026-07-13T14:05:07"}'
+            text='{"ticket_id": "T-1005", "customer_id": "C-1001", "issue_summary": "Delivered package arrived damaged. Customer requests assistance with replacement or refund.", "priority": "normal", "status": "open", "created_at": "2026-07-13T15:13:47"}'
         )
     ],
     isError=False
@@ -2026,18 +2004,18 @@
         <is>
           <t>LLMTestCase(
     input='Create a support ticket for customer C-1001 because their delivered package arrived damaged.',
-    actual_output='I’ve created a support ticket for you.\n\n- Ticket ID: T-1002\n- Customer: C-1001\n- Issue: Delivered package arrived damaged\n- Priority: Normal\n- Status: Open\n\nWhat’s next:\n- A support agent will review the ticket and reach out for details or photos of the damage if needed.\n- If you have the order ID and any photos of the damaged items/packaging, please share them here to speed up the resolution.',
+    actual_output='I’ve created a support ticket to address the damaged delivery.\n\n- Ticket ID: T-1005\n- Customer: C-1001\n- Issue: Delivered package arrived damaged; customer requests replacement or refund\n- Status: Open\n- Priority: Normal\n\nNext steps:\n- We’ll review the customer’s order and photos (if available) and reach out with replacement or refund options.\n- If you have the order ID or images of the damage, please share them here to expedite the resolution.',
     expected_outcome='The assistant should look up the customer and create a support ticket with the damaged package issue.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
         MCPToolCall(
             name='create_support_ticket',
-            args={'customer_id': 'C-1001', 'issue_summary': 'Delivered package arrived damaged', 'priority': 'normal'},
+            args={'customer_id': 'C-1001', 'issue_summary': 'Delivered package arrived damaged. Customer requests assistance with replacement or refund.', 'priority': 'normal'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"ticket_id": "T-1002", "customer_id": "C-1001", "issue_summary": "Delivered package arrived damaged", "priority": "normal", "status": "open", "created_at": "2026-07-13T14:05:07"}'
+                    text='{"ticket_id": "T-1005", "customer_id": "C-1001", "issue_summary": "Delivered package arrived damaged. Customer requests assistance with replacement or refund.", "priority": "normal", "status": "open", "created_at": "2026-07-13T15:13:47"}'
                 )
             ],
             isError=False
@@ -2048,6 +2026,122 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NEGATIVE-DEMO-001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>dummy_support_server = MCPServer(
+    server_name="dummy_support",
+    transport="streamable-http",
+    available_tools=[
+        Tool(
+            name="get_customer_profile",
+            description="Get a customer profile by customer ID.",
+            inputSchema={
+                "type": "object",
+                "properties": {"customer_id": {"type": "string"}},
+                "required": ["customer_id"],
+                "additionalProperties": False,
+            },
+        ),
+        Tool(
+            name="get_order_status",
+            description="Get order status and order details by order ID.",
+            inputSchema={
+                "type": "object",
+                "properties": {"order_id": {"type": "string"}},
+                "required": ["order_id"],
+                "additionalProperties": False,
+            },
+        ),
+        Tool(
+            name="search_policy_docs",
+            description="Search support policy documents.",
+            inputSchema={
+                "type": "object",
+                "properties": {"query": {"type": "string"}},
+                "required": ["query"],
+                "additionalProperties": False,
+            },
+        ),
+        Tool(
+            name="calculate_refund",
+            description="Calculate refund eligibility for an order.",
+            inputSchema={
+                "type": "object",
+                "properties": {
+                    "order_id": {"type": "string"},
+                    "reason": {"type": "string"},
+                },
+                "required": ["order_id", "reason"],
+                "additionalProperties": False,
+            },
+        ),
+        Tool(
+            name="create_support_ticket",
+            description="Create a support ticket for a customer issue.",
+            inputSchema={
+                "type": "object",
+                "properties": {
+                    "customer_id": {"type": "string"},
+                    "issue_summary": {"type": "string"},
+                    "priority": {"type": "string", "enum": ["low", "normal", "high"]},
+                },
+                "required": ["customer_id", "issue_summary", "priority"],
+                "additionalProperties": False,
+            },
+        ),
+    ],
+)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MCPToolCall(
+    name='create_support_ticket',
+    args={'customer_id': 'C-1003', 'issue_summary': 'General follow-up requested.', 'priority': 'low'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"ticket_id": "T-NEGATIVE-DEMO", "customer_id": "C-1003", "issue_summary": "General follow-up requested.", "priority": "low", "status": "open"}'
+        )
+    ],
+    isError=False
+)
+)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LLMTestCase(
+    input='Customer C-1002 says their order is late. Check what happened and explain it.',
+    actual_output='I created a low-priority ticket for customer C-1003, but I did not check the delayed order.',
+    expected_outcome='The assistant should look up customer C-1002, identify order ORD-9002, call the order status tool, and explain the delay.',
+    mcp_servers=[dummy_support_server],
+    mcp_tools_called=[
+        MCPToolCall(
+            name='create_support_ticket',
+            args={'customer_id': 'C-1003', 'issue_summary': 'General follow-up requested.', 'priority': 'low'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"ticket_id": "T-NEGATIVE-DEMO", "customer_id": "C-1003", "issue_summary": "General follow-up requested.", "priority": "low", "status": "open"}'
+                )
+            ],
+            isError=False
+        )
+        )
+    ],
+)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Live_Dummy_MCP_Traces.xlsx
+++ b/Live_Dummy_MCP_Traces.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CASE-001-20260714122913</t>
+          <t>CASE-001-20260714134756</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-14T12:29:13</t>
+          <t>2026-07-14T13:47:56</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -519,19 +519,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Here’s what I found:
-- Order ORD-9002 for Rahul Mehta is currently marked delayed.
-- Delay reason: weather disruption at the regional sorting center.
-- The last estimated delivery date was 2026-07-13, so it’s now running late.
+          <t>Here’s what I found for Rahul Mehta (C-1002):
+- Order ORD-9002 (Laptop stand) is currently delayed.
+- Reason: Weather disruption at the regional sorting center.
+- Last carrier ETA was July 13, 2026, so it’s running late.
 What happens next:
-- Once the sorting center clears the weather backlog, the package should move and deliver, typically within 1–2 business days.
-- If it hasn’t arrived within 2 business days, we’ll escalate with the carrier and discuss alternatives (such as a replacement or refund).
-Would you like me to open a support ticket to monitor this and contact the carrier for an updated scan? I can also set up email updates to rahul@example.com.</t>
+- These weather backlogs usually clear quickly, and carriers often deliver within the next 1–2 business days.
+- If it hasn’t arrived by July 16, I recommend we escalate a trace with the carrier. Per our policy, shipping fees may be refunded if the delay ends up exceeding 5 days.
+Would you like me to set up a proactive follow-up or open a ticket to monitor and escalate if it doesn’t move?</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status</t>
+          <t>get_customer_profile,get_order_status,search_policy_docs</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CASE-001-20260714122913</t>
+          <t>CASE-001-20260714134756</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-14T12:29:13</t>
+          <t>2026-07-14T13:47:56</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -599,19 +599,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Here’s what I found:
-- Order ORD-9002 for Rahul Mehta is currently marked delayed.
-- Delay reason: weather disruption at the regional sorting center.
-- The last estimated delivery date was 2026-07-13, so it’s now running late.
+          <t>Here’s what I found for Rahul Mehta (C-1002):
+- Order ORD-9002 (Laptop stand) is currently delayed.
+- Reason: Weather disruption at the regional sorting center.
+- Last carrier ETA was July 13, 2026, so it’s running late.
 What happens next:
-- Once the sorting center clears the weather backlog, the package should move and deliver, typically within 1–2 business days.
-- If it hasn’t arrived within 2 business days, we’ll escalate with the carrier and discuss alternatives (such as a replacement or refund).
-Would you like me to open a support ticket to monitor this and contact the carrier for an updated scan? I can also set up email updates to rahul@example.com.</t>
+- These weather backlogs usually clear quickly, and carriers often deliver within the next 1–2 business days.
+- If it hasn’t arrived by July 16, I recommend we escalate a trace with the carrier. Per our policy, shipping fees may be refunded if the delay ends up exceeding 5 days.
+Would you like me to set up a proactive follow-up or open a ticket to monitor and escalate if it doesn’t move?</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status</t>
+          <t>get_customer_profile,get_order_status,search_policy_docs</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -651,7 +651,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CASE-010-20260714123008</t>
+          <t>CASE-001-20260714134756</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -661,17 +661,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-14T12:30:08</t>
+          <t>2026-07-14T13:47:56</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Customer C-1004 asks for the current shipping status of order ORD-9010.</t>
+          <t>Customer C-1002 says their order is late. Check what happened and explain it.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Look up C-1004, inspect ORD-9010, and provide shipped status plus estimated delivery.</t>
+          <t>Look up customer C-1002, inspect order ORD-9002, and explain the weather delay with the estimated delivery date.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -681,40 +681,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I checked order ORD-9010 for customer C-1004. It has shipped and is in transit. Estimated delivery is 2026-07-15.
-Next step: You can expect delivery tomorrow. If you’d like, I can send the tracking details or set up delivery notifications—just let me know your preference.</t>
+          <t>Here’s what I found for Rahul Mehta (C-1002):
+- Order ORD-9002 (Laptop stand) is currently delayed.
+- Reason: Weather disruption at the regional sorting center.
+- Last carrier ETA was July 13, 2026, so it’s running late.
+What happens next:
+- These weather backlogs usually clear quickly, and carriers often deliver within the next 1–2 business days.
+- If it hasn’t arrived by July 16, I recommend we escalate a trace with the carrier. Per our policy, shipping fees may be refunded if the delay ends up exceeding 5 days.
+Would you like me to set up a proactive follow-up or open a ticket to monitor and escalate if it doesn’t move?</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>get_order_status</t>
+          <t>get_customer_profile,get_order_status,search_policy_docs</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>get_order_status</t>
+          <t>search_policy_docs</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>{
-  "order_id": "ORD-9010"
+  "query": "late delivery policy weather carrier delay compensation reship refund when to escalate"
 }</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>{
-  "order_id": "ORD-9010",
-  "customer_id": "C-1004",
-  "status": "shipped",
-  "item": "Portable SSD",
-  "amount": 119.0,
-  "estimated_delivery": "2026-07-15",
-  "issue": "Customer asks for current shipping status."
+  "query": "late delivery policy weather carrier delay compensation reship refund when to escalate",
+  "matches": [
+    {
+      "policy_id": "refund",
+      "title": "Refund policy",
+      "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."
+    },
+    {
+      "policy_id": "delivery",
+      "title": "Delivery delay policy",
+      "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."
+    },
+    {
+      "policy_id": "damaged_item",
+      "title": "Damaged item policy",
+      "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."
+    },
+    {
+      "policy_id": "cancellation",
+      "title": "Cancellation policy",
+      "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."
+    },
+    {
+      "policy_id": "shipping_status",
+      "title": "Shipping status policy",
+      "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."
+    }
+  ]
 }</t>
         </is>
       </c>
@@ -727,7 +754,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CASE-015-20260714123030</t>
+          <t>CASE-007-20260714134926</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -737,42 +764,201 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-14T12:30:30</t>
+          <t>2026-07-14T13:49:26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Why was Omar Ali's USB-C hub order ORD-9008 not shipped?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Check customer/order details and explain that ORD-9008 was cancelled because payment authorization failed.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I checked order ORD-9008 for Omar Ali. The order was canceled and therefore not shipped because the payment authorization failed. 
+Next steps:
+- If the payment method has been updated, you can place a new order for the USB‑C hub.
+- If you’d like, I can help verify the payment details on file or create a new order now.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>get_order_status,get_customer_profile</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>get_order_status</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9008"
+}</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9008",
+  "customer_id": "C-1008",
+  "status": "cancelled",
+  "item": "USB-C hub",
+  "amount": 39.0,
+  "cancelled_reason": "Payment authorization failed.",
+  "issue": "Customer asks why the order was not shipped."
+}</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CASE-007-20260714134926</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-07-14T13:49:26</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Why was Omar Ali's USB-C hub order ORD-9008 not shipped?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Check customer/order details and explain that ORD-9008 was cancelled because payment authorization failed.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I checked order ORD-9008 for Omar Ali. The order was canceled and therefore not shipped because the payment authorization failed. 
+Next steps:
+- If the payment method has been updated, you can place a new order for the USB‑C hub.
+- If you’d like, I can help verify the payment details on file or create a new order now.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>get_order_status,get_customer_profile</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>get_customer_profile</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1008"
+}</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1008",
+  "name": "Omar Ali",
+  "tier": "Standard",
+  "primary_order_id": "ORD-9008",
+  "email": "omar@example.com"
+}</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CASE-015-20260714134959</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-07-14T13:49:59</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Find the customer and order details for Rahul Mehta, then summarize what support should say.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Look up customer C-1002 and ORD-9002, then explain the delayed laptop stand order and next step.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>get_customer_profile,get_order_status</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>To look up Rahul Mehta’s customer and order details, I need a unique identifier.
-Please share:
-- Customer identifier: customer ID (e.g., C-1234) or email/phone on file
-- Order identifier(s): order ID(s) (e.g., ORD-1234). If you don’t have them, I can list recent orders once I have the customer ID
-- Optional: city/state on the account to avoid mixing up profiles if there are multiple Rahul Mehtas
-- Optional: the specific issue (late delivery, damage, return, refund) so I can tailor the support summary
-Next steps once I have this:
-- I’ll pull Rahul Mehta’s profile and recent orders, check each order’s latest status, and summarize exactly what support should say, including current status/ETA, any actions required, and refund/replacement eligibility if relevant.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I can’t look up a customer by name alone. Please share one of the following so I can retrieve Rahul Mehta’s details:
+- Customer ID (e.g., C-1234)
+- Any order ID (e.g., ORD-5678)
+- The email or phone number on the account
+Once I have that, I’ll pull his profile and order(s) and summarize exactly what support should say.
+In the meantime, here’s a concise support message template you can use once the details are known:
+- Greet Rahul and verify the account.
+- State the order number, items, and current status with tracking and ETA (or expected ship date if not shipped).
+- If delayed/backordered: apologize, explain cause, give a clear revised timeline, and offer options (keep order with expedited shipping when possible, switch to an alternative, or cancel).
+- If delivered: confirm delivery date and ask if any issues (missing/damaged items); offer replacement or refund as per policy.
+- If lost: apologize, initiate trace with the carrier, and offer replacement or refund immediately if eligible.
+- Close with next steps, a case/ticket number, and contact info for follow‑up.
+Share the ID(s) and I’ll fetch the exact details and tailor the message.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
@@ -1063,7 +1249,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CASE-001-20260714122913</t>
+          <t>CASE-001-20260714134756</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1128,6 +1314,19 @@
     ],
     isError=False
 )
+)
+MCPToolCall(
+    name='search_policy_docs',
+    args={'query': 'late delivery policy weather carrier delay compensation reship refund when to escalate'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"query": "late delivery policy weather carrier delay compensation reship refund when to escalate", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+        )
+    ],
+    isError=False
+)
 )</t>
         </is>
       </c>
@@ -1135,7 +1334,7 @@
         <is>
           <t>LLMTestCase(
     input='Customer C-1002 says their order is late. Check what happened and explain it.',
-    actual_output='Here’s what I found:\n- Order ORD-9002 for Rahul Mehta is currently marked delayed.\n- Delay reason: weather disruption at the regional sorting center.\n- The last estimated delivery date was 2026-07-13, so it’s now running late.\n\nWhat happens next:\n- Once the sorting center clears the weather backlog, the package should move and deliver, typically within 1–2 business days.\n- If it hasn’t arrived within 2 business days, we’ll escalate with the carrier and discuss alternatives (such as a replacement or refund).\n\nWould you like me to open a support ticket to monitor this and contact the carrier for an updated scan? I can also set up email updates to rahul@example.com.',
+    actual_output='Here’s what I found for Rahul Mehta (C-1002):\n\n- Order ORD-9002 (Laptop stand) is currently delayed.\n- Reason: Weather disruption at the regional sorting center.\n- Last carrier ETA was July 13, 2026, so it’s running late.\n\nWhat happens next:\n- These weather backlogs usually clear quickly, and carriers often deliver within the next 1–2 business days.\n- If it hasn’t arrived by July 16, I recommend we escalate a trace with the carrier. Per our policy, shipping fees may be refunded if the delay ends up exceeding 5 days.\n\nWould you like me to set up a proactive follow-up or open a ticket to monitor and escalate if it doesn’t move?',
     expected_output='Look up customer C-1002, inspect order ORD-9002, and explain the weather delay with the estimated delivery date.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
@@ -1160,6 +1359,19 @@
                 TextContent(
                     type="text",
                     text='{"order_id": "ORD-9002", "customer_id": "C-1002", "status": "delayed", "item": "Laptop stand", "amount": 45.0, "delay_reason": "Weather disruption at the regional sorting center.", "estimated_delivery": "2026-07-13"}'
+                )
+            ],
+            isError=False
+        )
+        ),
+        MCPToolCall(
+            name='search_policy_docs',
+            args={'query': 'late delivery policy weather carrier delay compensation reship refund when to escalate'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"query": "late delivery policy weather carrier delay compensation reship refund when to escalate", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
                 )
             ],
             isError=False
@@ -1203,12 +1415,29 @@
                         ],
                         isError=False
                     )
+                    ),
+                    MCPToolCall(
+                        name='search_policy_docs',
+                        args={'query': 'late delivery policy weather carrier delay compensation reship refund when to escalate'},
+                        result=CallToolResult(
+                        content=[
+                            TextContent(
+                                type="text",
+                                text='{"query": "late delivery policy weather carrier delay compensation reship refund when to escalate", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+                            )
+                        ],
+                        isError=False
+                    )
                     )
             ],
         ),
         Turn(
             role="assistant",
-            content='Here’s what I found:\n- Order ORD-9002 for Rahul Mehta is currently marked delayed.\n- Delay reason: weather disruption at the regional sorting center.\n- The last estimated delivery date was 2026-07-13, so it’s now running late.\n\nWhat happens next:\n- Once the sorting center clears the weather backlog, the package should move and deliver, typically within 1–2 business days.\n- If it hasn’t arrived within 2 business days, we’ll escalate with the carrier and discuss alternatives (such as a replacement or refund).\n\nWould you like me to open a support ticket to monitor this and contact the carrier for an updated scan? I can also set up email updates to rahul@example.com.',
+            content="The MCP tools returned the support data needed for the answer.",
+        ),
+        Turn(
+            role="assistant",
+            content='Here’s what I found for Rahul Mehta (C-1002):\n\n- Order ORD-9002 (Laptop stand) is currently delayed.\n- Reason: Weather disruption at the regional sorting center.\n- Last carrier ETA was July 13, 2026, so it’s running late.\n\nWhat happens next:\n- These weather backlogs usually clear quickly, and carriers often deliver within the next 1–2 business days.\n- If it hasn’t arrived by July 16, I recommend we escalate a trace with the carrier. Per our policy, shipping fees may be refunded if the delay ends up exceeding 5 days.\n\nWould you like me to set up a proactive follow-up or open a ticket to monitor and escalate if it doesn’t move?',
         ),
     ],
     mcp_servers=[dummy_support_server],
@@ -1219,7 +1448,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CASE-010-20260714123008</t>
+          <t>CASE-007-20260714134926</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1261,12 +1490,25 @@
         <is>
           <t>MCPToolCall(
     name='get_order_status',
-    args={'order_id': 'ORD-9010'},
+    args={'order_id': 'ORD-9008'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"order_id": "ORD-9010", "customer_id": "C-1004", "status": "shipped", "item": "Portable SSD", "amount": 119.0, "estimated_delivery": "2026-07-15", "issue": "Customer asks for current shipping status."}'
+            text='{"order_id": "ORD-9008", "customer_id": "C-1008", "status": "cancelled", "item": "USB-C hub", "amount": 39.0, "cancelled_reason": "Payment authorization failed.", "issue": "Customer asks why the order was not shipped."}'
+        )
+    ],
+    isError=False
+)
+)
+MCPToolCall(
+    name='get_customer_profile',
+    args={'customer_id': 'C-1008'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"customer_id": "C-1008", "name": "Omar Ali", "tier": "Standard", "primary_order_id": "ORD-9008", "email": "omar@example.com"}'
         )
     ],
     isError=False
@@ -1277,19 +1519,32 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>LLMTestCase(
-    input='Customer C-1004 asks for the current shipping status of order ORD-9010.',
-    actual_output='I checked order ORD-9010 for customer C-1004. It has shipped and is in transit. Estimated delivery is 2026-07-15.\n\nNext step: You can expect delivery tomorrow. If you’d like, I can send the tracking details or set up delivery notifications—just let me know your preference.',
-    expected_output='Look up C-1004, inspect ORD-9010, and provide shipped status plus estimated delivery.',
+    input="Why was Omar Ali's USB-C hub order ORD-9008 not shipped?",
+    actual_output='I checked order ORD-9008 for Omar Ali. The order was canceled and therefore not shipped because the payment authorization failed. \n\nNext steps:\n- If the payment method has been updated, you can place a new order for the USB‑C hub.\n- If you’d like, I can help verify the payment details on file or create a new order now.',
+    expected_output='Check customer/order details and explain that ORD-9008 was cancelled because payment authorization failed.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
         MCPToolCall(
             name='get_order_status',
-            args={'order_id': 'ORD-9010'},
+            args={'order_id': 'ORD-9008'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"order_id": "ORD-9010", "customer_id": "C-1004", "status": "shipped", "item": "Portable SSD", "amount": 119.0, "estimated_delivery": "2026-07-15", "issue": "Customer asks for current shipping status."}'
+                    text='{"order_id": "ORD-9008", "customer_id": "C-1008", "status": "cancelled", "item": "USB-C hub", "amount": 39.0, "cancelled_reason": "Payment authorization failed.", "issue": "Customer asks why the order was not shipped."}'
+                )
+            ],
+            isError=False
+        )
+        ),
+        MCPToolCall(
+            name='get_customer_profile',
+            args={'customer_id': 'C-1008'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"customer_id": "C-1008", "name": "Omar Ali", "tier": "Standard", "primary_order_id": "ORD-9008", "email": "omar@example.com"}'
                 )
             ],
             isError=False
@@ -1303,19 +1558,32 @@
         <is>
           <t>ConversationalTestCase(
     turns=[
-        Turn(role="user", content='Customer C-1004 asks for the current shipping status of order ORD-9010.'),
+        Turn(role="user", content="Why was Omar Ali's USB-C hub order ORD-9008 not shipped?"),
         Turn(
             role="assistant",
             content="I will use the available MCP tools to complete the request.",
             mcp_tools_called=[
                     MCPToolCall(
                         name='get_order_status',
-                        args={'order_id': 'ORD-9010'},
+                        args={'order_id': 'ORD-9008'},
                         result=CallToolResult(
                         content=[
                             TextContent(
                                 type="text",
-                                text='{"order_id": "ORD-9010", "customer_id": "C-1004", "status": "shipped", "item": "Portable SSD", "amount": 119.0, "estimated_delivery": "2026-07-15", "issue": "Customer asks for current shipping status."}'
+                                text='{"order_id": "ORD-9008", "customer_id": "C-1008", "status": "cancelled", "item": "USB-C hub", "amount": 39.0, "cancelled_reason": "Payment authorization failed.", "issue": "Customer asks why the order was not shipped."}'
+                            )
+                        ],
+                        isError=False
+                    )
+                    ),
+                    MCPToolCall(
+                        name='get_customer_profile',
+                        args={'customer_id': 'C-1008'},
+                        result=CallToolResult(
+                        content=[
+                            TextContent(
+                                type="text",
+                                text='{"customer_id": "C-1008", "name": "Omar Ali", "tier": "Standard", "primary_order_id": "ORD-9008", "email": "omar@example.com"}'
                             )
                         ],
                         isError=False
@@ -1325,7 +1593,11 @@
         ),
         Turn(
             role="assistant",
-            content='I checked order ORD-9010 for customer C-1004. It has shipped and is in transit. Estimated delivery is 2026-07-15.\n\nNext step: You can expect delivery tomorrow. If you’d like, I can send the tracking details or set up delivery notifications—just let me know your preference.',
+            content="The MCP tools returned the support data needed for the answer.",
+        ),
+        Turn(
+            role="assistant",
+            content='I checked order ORD-9008 for Omar Ali. The order was canceled and therefore not shipped because the payment authorization failed. \n\nNext steps:\n- If the payment method has been updated, you can place a new order for the USB‑C hub.\n- If you’d like, I can help verify the payment details on file or create a new order now.',
         ),
     ],
     mcp_servers=[dummy_support_server],
@@ -1336,7 +1608,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CASE-015-20260714123030</t>
+          <t>CASE-015-20260714134959</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1379,7 +1651,7 @@
         <is>
           <t>LLMTestCase(
     input='Find the customer and order details for Rahul Mehta, then summarize what support should say.',
-    actual_output='To look up Rahul Mehta’s customer and order details, I need a unique identifier.\n\nPlease share:\n- Customer identifier: customer ID (e.g., C-1234) or email/phone on file\n- Order identifier(s): order ID(s) (e.g., ORD-1234). If you don’t have them, I can list recent orders once I have the customer ID\n- Optional: city/state on the account to avoid mixing up profiles if there are multiple Rahul Mehtas\n- Optional: the specific issue (late delivery, damage, return, refund) so I can tailor the support summary\n\nNext steps once I have this:\n- I’ll pull Rahul Mehta’s profile and recent orders, check each order’s latest status, and summarize exactly what support should say, including current status/ETA, any actions required, and refund/replacement eligibility if relevant.',
+    actual_output='I can’t look up a customer by name alone. Please share one of the following so I can retrieve Rahul Mehta’s details:\n- Customer ID (e.g., C-1234)\n- Any order ID (e.g., ORD-5678)\n- The email or phone number on the account\n\nOnce I have that, I’ll pull his profile and order(s) and summarize exactly what support should say.\n\nIn the meantime, here’s a concise support message template you can use once the details are known:\n- Greet Rahul and verify the account.\n- State the order number, items, and current status with tracking and ETA (or expected ship date if not shipped).\n- If delayed/backordered: apologize, explain cause, give a clear revised timeline, and offer options (keep order with expedited shipping when possible, switch to an alternative, or cancel).\n- If delivered: confirm delivery date and ask if any issues (missing/damaged items); offer replacement or refund as per policy.\n- If lost: apologize, initiate trace with the carrier, and offer replacement or refund immediately if eligible.\n- Close with next steps, a case/ticket number, and contact info for follow‑up.\n\nShare the ID(s) and I’ll fetch the exact details and tailor the message.',
     expected_output='Look up customer C-1002 and ORD-9002, then explain the delayed laptop stand order and next step.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
@@ -1400,7 +1672,11 @@
         ),
         Turn(
             role="assistant",
-            content='To look up Rahul Mehta’s customer and order details, I need a unique identifier.\n\nPlease share:\n- Customer identifier: customer ID (e.g., C-1234) or email/phone on file\n- Order identifier(s): order ID(s) (e.g., ORD-1234). If you don’t have them, I can list recent orders once I have the customer ID\n- Optional: city/state on the account to avoid mixing up profiles if there are multiple Rahul Mehtas\n- Optional: the specific issue (late delivery, damage, return, refund) so I can tailor the support summary\n\nNext steps once I have this:\n- I’ll pull Rahul Mehta’s profile and recent orders, check each order’s latest status, and summarize exactly what support should say, including current status/ETA, any actions required, and refund/replacement eligibility if relevant.',
+            content="The MCP tools returned the support data needed for the answer.",
+        ),
+        Turn(
+            role="assistant",
+            content='I can’t look up a customer by name alone. Please share one of the following so I can retrieve Rahul Mehta’s details:\n- Customer ID (e.g., C-1234)\n- Any order ID (e.g., ORD-5678)\n- The email or phone number on the account\n\nOnce I have that, I’ll pull his profile and order(s) and summarize exactly what support should say.\n\nIn the meantime, here’s a concise support message template you can use once the details are known:\n- Greet Rahul and verify the account.\n- State the order number, items, and current status with tracking and ETA (or expected ship date if not shipped).\n- If delayed/backordered: apologize, explain cause, give a clear revised timeline, and offer options (keep order with expedited shipping when possible, switch to an alternative, or cancel).\n- If delivered: confirm delivery date and ask if any issues (missing/damaged items); offer replacement or refund as per policy.\n- If lost: apologize, initiate trace with the carrier, and offer replacement or refund immediately if eligible.\n- Close with next steps, a case/ticket number, and contact info for follow‑up.\n\nShare the ID(s) and I’ll fetch the exact details and tailor the message.',
         ),
     ],
     mcp_servers=[dummy_support_server],

--- a/Live_Dummy_MCP_Traces.xlsx
+++ b/Live_Dummy_MCP_Traces.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CASE-001-20260714134756</t>
+          <t>CASE-001-20260715163219</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-14T13:47:56</t>
+          <t>2026-07-15T16:32:19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -519,19 +519,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Here’s what I found for Rahul Mehta (C-1002):
-- Order ORD-9002 (Laptop stand) is currently delayed.
-- Reason: Weather disruption at the regional sorting center.
-- Last carrier ETA was July 13, 2026, so it’s running late.
+          <t>Here’s what I found for order ORD-9002 (Laptop stand) for Rahul Mehta:
+- Status: Delayed
+- Reason: Weather disruption at the regional sorting center
+- Last estimated delivery date: 2026-07-13 (now 2 days late)
 What happens next:
-- These weather backlogs usually clear quickly, and carriers often deliver within the next 1–2 business days.
-- If it hasn’t arrived by July 16, I recommend we escalate a trace with the carrier. Per our policy, shipping fees may be refunded if the delay ends up exceeding 5 days.
-Would you like me to set up a proactive follow-up or open a ticket to monitor and escalate if it doesn’t move?</t>
+- We’ll request an updated ETA from the carrier and keep you posted. Weather-related delays typically clear within 1–3 business days.
+- Per our delivery delay policy, shipping fees can be refunded if the delay exceeds 5 days. If it’s still not delivered by 2026-07-18, we can process a shipping-fee refund.
+- A full order refund isn’t eligible at this time because this order is outside the 30‑day refund window.
+If you’d like, I can open a support ticket to track updates and notify you as soon as the new ETA comes in.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status,search_policy_docs</t>
+          <t>get_customer_profile,get_order_status,search_policy_docs,calculate_refund</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -569,7 +570,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CASE-001-20260714134756</t>
+          <t>CASE-001-20260715163219</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -579,7 +580,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-14T13:47:56</t>
+          <t>2026-07-15T16:32:19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -599,19 +600,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Here’s what I found for Rahul Mehta (C-1002):
-- Order ORD-9002 (Laptop stand) is currently delayed.
-- Reason: Weather disruption at the regional sorting center.
-- Last carrier ETA was July 13, 2026, so it’s running late.
+          <t>Here’s what I found for order ORD-9002 (Laptop stand) for Rahul Mehta:
+- Status: Delayed
+- Reason: Weather disruption at the regional sorting center
+- Last estimated delivery date: 2026-07-13 (now 2 days late)
 What happens next:
-- These weather backlogs usually clear quickly, and carriers often deliver within the next 1–2 business days.
-- If it hasn’t arrived by July 16, I recommend we escalate a trace with the carrier. Per our policy, shipping fees may be refunded if the delay ends up exceeding 5 days.
-Would you like me to set up a proactive follow-up or open a ticket to monitor and escalate if it doesn’t move?</t>
+- We’ll request an updated ETA from the carrier and keep you posted. Weather-related delays typically clear within 1–3 business days.
+- Per our delivery delay policy, shipping fees can be refunded if the delay exceeds 5 days. If it’s still not delivered by 2026-07-18, we can process a shipping-fee refund.
+- A full order refund isn’t eligible at this time because this order is outside the 30‑day refund window.
+If you’d like, I can open a support ticket to track updates and notify you as soon as the new ETA comes in.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status,search_policy_docs</t>
+          <t>get_customer_profile,get_order_status,search_policy_docs,calculate_refund</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -651,7 +653,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CASE-001-20260714134756</t>
+          <t>CASE-001-20260715163219</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -661,7 +663,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-14T13:47:56</t>
+          <t>2026-07-15T16:32:19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -681,19 +683,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Here’s what I found for Rahul Mehta (C-1002):
-- Order ORD-9002 (Laptop stand) is currently delayed.
-- Reason: Weather disruption at the regional sorting center.
-- Last carrier ETA was July 13, 2026, so it’s running late.
+          <t>Here’s what I found for order ORD-9002 (Laptop stand) for Rahul Mehta:
+- Status: Delayed
+- Reason: Weather disruption at the regional sorting center
+- Last estimated delivery date: 2026-07-13 (now 2 days late)
 What happens next:
-- These weather backlogs usually clear quickly, and carriers often deliver within the next 1–2 business days.
-- If it hasn’t arrived by July 16, I recommend we escalate a trace with the carrier. Per our policy, shipping fees may be refunded if the delay ends up exceeding 5 days.
-Would you like me to set up a proactive follow-up or open a ticket to monitor and escalate if it doesn’t move?</t>
+- We’ll request an updated ETA from the carrier and keep you posted. Weather-related delays typically clear within 1–3 business days.
+- Per our delivery delay policy, shipping fees can be refunded if the delay exceeds 5 days. If it’s still not delivered by 2026-07-18, we can process a shipping-fee refund.
+- A full order refund isn’t eligible at this time because this order is outside the 30‑day refund window.
+If you’d like, I can open a support ticket to track updates and notify you as soon as the new ETA comes in.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status,search_policy_docs</t>
+          <t>get_customer_profile,get_order_status,search_policy_docs,calculate_refund</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -707,14 +710,14 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>{
-  "query": "late delivery policy weather carrier delay compensation reship refund when to escalate"
+  "query": "delivery delay due to weather disruption policy next steps escalation compensation refund eligibility"
 }</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>{
-  "query": "late delivery policy weather carrier delay compensation reship refund when to escalate",
+  "query": "delivery delay due to weather disruption policy next steps escalation compensation refund eligibility",
   "matches": [
     {
       "policy_id": "refund",
@@ -754,7 +757,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CASE-007-20260714134926</t>
+          <t>CASE-001-20260715163219</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -764,17 +767,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-14T13:49:26</t>
+          <t>2026-07-15T16:32:19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Why was Omar Ali's USB-C hub order ORD-9008 not shipped?</t>
+          <t>Customer C-1002 says their order is late. Check what happened and explain it.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Check customer/order details and explain that ORD-9008 was cancelled because payment authorization failed.</t>
+          <t>Look up customer C-1002, inspect order ORD-9002, and explain the weather delay with the estimated delivery date.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -784,42 +787,45 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I checked order ORD-9008 for Omar Ali. The order was canceled and therefore not shipped because the payment authorization failed. 
-Next steps:
-- If the payment method has been updated, you can place a new order for the USB‑C hub.
-- If you’d like, I can help verify the payment details on file or create a new order now.</t>
+          <t>Here’s what I found for order ORD-9002 (Laptop stand) for Rahul Mehta:
+- Status: Delayed
+- Reason: Weather disruption at the regional sorting center
+- Last estimated delivery date: 2026-07-13 (now 2 days late)
+What happens next:
+- We’ll request an updated ETA from the carrier and keep you posted. Weather-related delays typically clear within 1–3 business days.
+- Per our delivery delay policy, shipping fees can be refunded if the delay exceeds 5 days. If it’s still not delivered by 2026-07-18, we can process a shipping-fee refund.
+- A full order refund isn’t eligible at this time because this order is outside the 30‑day refund window.
+If you’d like, I can open a support ticket to track updates and notify you as soon as the new ETA comes in.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>get_order_status,get_customer_profile</t>
+          <t>get_customer_profile,get_order_status,search_policy_docs,calculate_refund</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>get_order_status</t>
+          <t>calculate_refund</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>{
-  "order_id": "ORD-9008"
+  "order_id": "ORD-9002",
+  "reason": "delivery delay due to weather disruption"
 }</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>{
-  "order_id": "ORD-9008",
-  "customer_id": "C-1008",
-  "status": "cancelled",
-  "item": "USB-C hub",
-  "amount": 39.0,
-  "cancelled_reason": "Payment authorization failed.",
-  "issue": "Customer asks why the order was not shipped."
+  "order_id": "ORD-9002",
+  "eligible": false,
+  "refund_amount": 0.0,
+  "reason": "Order is outside the 30 day refund window."
 }</t>
         </is>
       </c>
@@ -832,7 +838,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CASE-007-20260714134926</t>
+          <t>CASE-005-20260715163351</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -842,39 +848,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-14T13:49:26</t>
+          <t>2026-07-15T16:33:51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Why was Omar Ali's USB-C hub order ORD-9008 not shipped?</t>
+          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Check customer/order details and explain that ORD-9008 was cancelled because payment authorization failed.</t>
+          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status</t>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I checked order ORD-9008 for Omar Ali. The order was canceled and therefore not shipped because the payment authorization failed. 
+          <t>I checked Kabir Bose’s profile and order ORD-9006. The office chair is delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18. I’ve opened a high-priority support ticket (T-1001) to address and expedite the issue.
 Next steps:
-- If the payment method has been updated, you can place a new order for the USB‑C hub.
-- If you’d like, I can help verify the payment details on file or create a new order now.</t>
+- We’ll monitor the transfer and push for earlier dispatch if possible.
+- If the delivery slips further, we can discuss a partial refund or expedited shipping; let me know if you’d like me to initiate that now.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>get_order_status,get_customer_profile</t>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -884,18 +890,18 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>{
-  "customer_id": "C-1008"
+  "customer_id": "C-1006"
 }</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>{
-  "customer_id": "C-1008",
-  "name": "Omar Ali",
-  "tier": "Standard",
-  "primary_order_id": "ORD-9008",
-  "email": "omar@example.com"
+  "customer_id": "C-1006",
+  "name": "Kabir Bose",
+  "tier": "Silver",
+  "primary_order_id": "ORD-9006",
+  "email": "kabir@example.com"
 }</t>
         </is>
       </c>
@@ -908,7 +914,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CASE-015-20260714134959</t>
+          <t>CASE-005-20260715163351</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -918,47 +924,220 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-14T13:49:59</t>
+          <t>2026-07-15T16:33:51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Find the customer and order details for Rahul Mehta, then summarize what support should say.</t>
+          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Look up customer C-1002 and ORD-9002, then explain the delayed laptop stand order and next step.</t>
+          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I checked Kabir Bose’s profile and order ORD-9006. The office chair is delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18. I’ve opened a high-priority support ticket (T-1001) to address and expedite the issue.
+Next steps:
+- We’ll monitor the transfer and push for earlier dispatch if possible.
+- If the delivery slips further, we can discuss a partial refund or expedited shipping; let me know if you’d like me to initiate that now.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>get_order_status</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9006"
+}</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9006",
+  "customer_id": "C-1006",
+  "status": "delayed",
+  "item": "Office chair",
+  "amount": 249.0,
+  "delay_reason": "Inventory transfer from another warehouse.",
+  "estimated_delivery": "2026-07-18"
+}</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CASE-005-20260715163351</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-07-15T16:33:51</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I checked Kabir Bose’s profile and order ORD-9006. The office chair is delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18. I’ve opened a high-priority support ticket (T-1001) to address and expedite the issue.
+Next steps:
+- We’ll monitor the transfer and push for earlier dispatch if possible.
+- If the delivery slips further, we can discuss a partial refund or expedited shipping; let me know if you’d like me to initiate that now.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>create_support_ticket</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1006",
+  "issue_summary": "Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.",
+  "priority": "high"
+}</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>{
+  "ticket_id": "T-1001",
+  "customer_id": "C-1006",
+  "issue_summary": "Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.",
+  "priority": "high",
+  "status": "open",
+  "created_at": "2026-07-15T16:34:00"
+}</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CASE-010-20260715163647</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-15T16:36:47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Customer C-1004 asks for the current shipping status of order ORD-9010.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Look up C-1004, inspect ORD-9010, and provide shipped status plus estimated delivery.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>get_customer_profile,get_order_status</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>I can’t look up a customer by name alone. Please share one of the following so I can retrieve Rahul Mehta’s details:
-- Customer ID (e.g., C-1234)
-- Any order ID (e.g., ORD-5678)
-- The email or phone number on the account
-Once I have that, I’ll pull his profile and order(s) and summarize exactly what support should say.
-In the meantime, here’s a concise support message template you can use once the details are known:
-- Greet Rahul and verify the account.
-- State the order number, items, and current status with tracking and ETA (or expected ship date if not shipped).
-- If delayed/backordered: apologize, explain cause, give a clear revised timeline, and offer options (keep order with expedited shipping when possible, switch to an alternative, or cancel).
-- If delivered: confirm delivery date and ask if any issues (missing/damaged items); offer replacement or refund as per policy.
-- If lost: apologize, initiate trace with the carrier, and offer replacement or refund immediately if eligible.
-- Close with next steps, a case/ticket number, and contact info for follow‑up.
-Share the ID(s) and I’ll fetch the exact details and tailor the message.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I checked order ORD-9010 for customer C-1004. The status is shipped, with an estimated delivery of 2026-07-15 for the Portable SSD. No further action is needed unless the package doesn’t arrive by the estimate—if that happens, let me know and I can assist with tracking or starting an investigation.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>get_order_status</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>get_order_status</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9010"
+}</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9010",
+  "customer_id": "C-1004",
+  "status": "shipped",
+  "item": "Portable SSD",
+  "amount": 119.0,
+  "estimated_delivery": "2026-07-15",
+  "issue": "Customer asks for current shipping status."
+}</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
@@ -1249,7 +1428,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CASE-001-20260714134756</t>
+          <t>CASE-001-20260715163219</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1317,12 +1496,25 @@
 )
 MCPToolCall(
     name='search_policy_docs',
-    args={'query': 'late delivery policy weather carrier delay compensation reship refund when to escalate'},
+    args={'query': 'delivery delay due to weather disruption policy next steps escalation compensation refund eligibility'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"query": "late delivery policy weather carrier delay compensation reship refund when to escalate", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+            text='{"query": "delivery delay due to weather disruption policy next steps escalation compensation refund eligibility", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+        )
+    ],
+    isError=False
+)
+)
+MCPToolCall(
+    name='calculate_refund',
+    args={'order_id': 'ORD-9002', 'reason': 'delivery delay due to weather disruption'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"order_id": "ORD-9002", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
         )
     ],
     isError=False
@@ -1334,7 +1526,7 @@
         <is>
           <t>LLMTestCase(
     input='Customer C-1002 says their order is late. Check what happened and explain it.',
-    actual_output='Here’s what I found for Rahul Mehta (C-1002):\n\n- Order ORD-9002 (Laptop stand) is currently delayed.\n- Reason: Weather disruption at the regional sorting center.\n- Last carrier ETA was July 13, 2026, so it’s running late.\n\nWhat happens next:\n- These weather backlogs usually clear quickly, and carriers often deliver within the next 1–2 business days.\n- If it hasn’t arrived by July 16, I recommend we escalate a trace with the carrier. Per our policy, shipping fees may be refunded if the delay ends up exceeding 5 days.\n\nWould you like me to set up a proactive follow-up or open a ticket to monitor and escalate if it doesn’t move?',
+    actual_output='Here’s what I found for order ORD-9002 (Laptop stand) for Rahul Mehta:\n\n- Status: Delayed\n- Reason: Weather disruption at the regional sorting center\n- Last estimated delivery date: 2026-07-13 (now 2 days late)\n\nWhat happens next:\n- We’ll request an updated ETA from the carrier and keep you posted. Weather-related delays typically clear within 1–3 business days.\n- Per our delivery delay policy, shipping fees can be refunded if the delay exceeds 5 days. If it’s still not delivered by 2026-07-18, we can process a shipping-fee refund.\n- A full order refund isn’t eligible at this time because this order is outside the 30‑day refund window.\n\nIf you’d like, I can open a support ticket to track updates and notify you as soon as the new ETA comes in.',
     expected_output='Look up customer C-1002, inspect order ORD-9002, and explain the weather delay with the estimated delivery date.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
@@ -1366,12 +1558,25 @@
         ),
         MCPToolCall(
             name='search_policy_docs',
-            args={'query': 'late delivery policy weather carrier delay compensation reship refund when to escalate'},
+            args={'query': 'delivery delay due to weather disruption policy next steps escalation compensation refund eligibility'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"query": "late delivery policy weather carrier delay compensation reship refund when to escalate", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+                    text='{"query": "delivery delay due to weather disruption policy next steps escalation compensation refund eligibility", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+                )
+            ],
+            isError=False
+        )
+        ),
+        MCPToolCall(
+            name='calculate_refund',
+            args={'order_id': 'ORD-9002', 'reason': 'delivery delay due to weather disruption'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"order_id": "ORD-9002", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
                 )
             ],
             isError=False
@@ -1418,12 +1623,25 @@
                     ),
                     MCPToolCall(
                         name='search_policy_docs',
-                        args={'query': 'late delivery policy weather carrier delay compensation reship refund when to escalate'},
+                        args={'query': 'delivery delay due to weather disruption policy next steps escalation compensation refund eligibility'},
                         result=CallToolResult(
                         content=[
                             TextContent(
                                 type="text",
-                                text='{"query": "late delivery policy weather carrier delay compensation reship refund when to escalate", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+                                text='{"query": "delivery delay due to weather disruption policy next steps escalation compensation refund eligibility", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+                            )
+                        ],
+                        isError=False
+                    )
+                    ),
+                    MCPToolCall(
+                        name='calculate_refund',
+                        args={'order_id': 'ORD-9002', 'reason': 'delivery delay due to weather disruption'},
+                        result=CallToolResult(
+                        content=[
+                            TextContent(
+                                type="text",
+                                text='{"order_id": "ORD-9002", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
                             )
                         ],
                         isError=False
@@ -1437,7 +1655,7 @@
         ),
         Turn(
             role="assistant",
-            content='Here’s what I found for Rahul Mehta (C-1002):\n\n- Order ORD-9002 (Laptop stand) is currently delayed.\n- Reason: Weather disruption at the regional sorting center.\n- Last carrier ETA was July 13, 2026, so it’s running late.\n\nWhat happens next:\n- These weather backlogs usually clear quickly, and carriers often deliver within the next 1–2 business days.\n- If it hasn’t arrived by July 16, I recommend we escalate a trace with the carrier. Per our policy, shipping fees may be refunded if the delay ends up exceeding 5 days.\n\nWould you like me to set up a proactive follow-up or open a ticket to monitor and escalate if it doesn’t move?',
+            content='Here’s what I found for order ORD-9002 (Laptop stand) for Rahul Mehta:\n\n- Status: Delayed\n- Reason: Weather disruption at the regional sorting center\n- Last estimated delivery date: 2026-07-13 (now 2 days late)\n\nWhat happens next:\n- We’ll request an updated ETA from the carrier and keep you posted. Weather-related delays typically clear within 1–3 business days.\n- Per our delivery delay policy, shipping fees can be refunded if the delay exceeds 5 days. If it’s still not delivered by 2026-07-18, we can process a shipping-fee refund.\n- A full order refund isn’t eligible at this time because this order is outside the 30‑day refund window.\n\nIf you’d like, I can open a support ticket to track updates and notify you as soon as the new ETA comes in.',
         ),
     ],
     mcp_servers=[dummy_support_server],
@@ -1448,7 +1666,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CASE-007-20260714134926</t>
+          <t>CASE-005-20260715163351</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1489,26 +1707,39 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>MCPToolCall(
-    name='get_order_status',
-    args={'order_id': 'ORD-9008'},
+    name='get_customer_profile',
+    args={'customer_id': 'C-1006'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"order_id": "ORD-9008", "customer_id": "C-1008", "status": "cancelled", "item": "USB-C hub", "amount": 39.0, "cancelled_reason": "Payment authorization failed.", "issue": "Customer asks why the order was not shipped."}'
+            text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
         )
     ],
     isError=False
 )
 )
 MCPToolCall(
-    name='get_customer_profile',
-    args={'customer_id': 'C-1008'},
+    name='get_order_status',
+    args={'order_id': 'ORD-9006'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"customer_id": "C-1008", "name": "Omar Ali", "tier": "Standard", "primary_order_id": "ORD-9008", "email": "omar@example.com"}'
+            text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
+        )
+    ],
+    isError=False
+)
+)
+MCPToolCall(
+    name='create_support_ticket',
+    args={'customer_id': 'C-1006', 'issue_summary': 'Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.', 'priority': 'high'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.", "priority": "high", "status": "open", "created_at": "2026-07-15T16:34:00"}'
         )
     ],
     isError=False
@@ -1519,32 +1750,45 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>LLMTestCase(
-    input="Why was Omar Ali's USB-C hub order ORD-9008 not shipped?",
-    actual_output='I checked order ORD-9008 for Omar Ali. The order was canceled and therefore not shipped because the payment authorization failed. \n\nNext steps:\n- If the payment method has been updated, you can place a new order for the USB‑C hub.\n- If you’d like, I can help verify the payment details on file or create a new order now.',
-    expected_output='Check customer/order details and explain that ORD-9008 was cancelled because payment authorization failed.',
+    input='Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.',
+    actual_output='I checked Kabir Bose’s profile and order ORD-9006. The office chair is delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18. I’ve opened a high-priority support ticket (T-1001) to address and expedite the issue.\n\nNext steps:\n- We’ll monitor the transfer and push for earlier dispatch if possible.\n- If the delivery slips further, we can discuss a partial refund or expedited shipping; let me know if you’d like me to initiate that now.',
+    expected_output='Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
         MCPToolCall(
-            name='get_order_status',
-            args={'order_id': 'ORD-9008'},
+            name='get_customer_profile',
+            args={'customer_id': 'C-1006'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"order_id": "ORD-9008", "customer_id": "C-1008", "status": "cancelled", "item": "USB-C hub", "amount": 39.0, "cancelled_reason": "Payment authorization failed.", "issue": "Customer asks why the order was not shipped."}'
+                    text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
                 )
             ],
             isError=False
         )
         ),
         MCPToolCall(
-            name='get_customer_profile',
-            args={'customer_id': 'C-1008'},
+            name='get_order_status',
+            args={'order_id': 'ORD-9006'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"customer_id": "C-1008", "name": "Omar Ali", "tier": "Standard", "primary_order_id": "ORD-9008", "email": "omar@example.com"}'
+                    text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
+                )
+            ],
+            isError=False
+        )
+        ),
+        MCPToolCall(
+            name='create_support_ticket',
+            args={'customer_id': 'C-1006', 'issue_summary': 'Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.', 'priority': 'high'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.", "priority": "high", "status": "open", "created_at": "2026-07-15T16:34:00"}'
                 )
             ],
             isError=False
@@ -1558,32 +1802,45 @@
         <is>
           <t>ConversationalTestCase(
     turns=[
-        Turn(role="user", content="Why was Omar Ali's USB-C hub order ORD-9008 not shipped?"),
+        Turn(role="user", content='Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.'),
         Turn(
             role="assistant",
             content="I will use the available MCP tools to complete the request.",
             mcp_tools_called=[
                     MCPToolCall(
-                        name='get_order_status',
-                        args={'order_id': 'ORD-9008'},
+                        name='get_customer_profile',
+                        args={'customer_id': 'C-1006'},
                         result=CallToolResult(
                         content=[
                             TextContent(
                                 type="text",
-                                text='{"order_id": "ORD-9008", "customer_id": "C-1008", "status": "cancelled", "item": "USB-C hub", "amount": 39.0, "cancelled_reason": "Payment authorization failed.", "issue": "Customer asks why the order was not shipped."}'
+                                text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
                             )
                         ],
                         isError=False
                     )
                     ),
                     MCPToolCall(
-                        name='get_customer_profile',
-                        args={'customer_id': 'C-1008'},
+                        name='get_order_status',
+                        args={'order_id': 'ORD-9006'},
                         result=CallToolResult(
                         content=[
                             TextContent(
                                 type="text",
-                                text='{"customer_id": "C-1008", "name": "Omar Ali", "tier": "Standard", "primary_order_id": "ORD-9008", "email": "omar@example.com"}'
+                                text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
+                            )
+                        ],
+                        isError=False
+                    )
+                    ),
+                    MCPToolCall(
+                        name='create_support_ticket',
+                        args={'customer_id': 'C-1006', 'issue_summary': 'Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.', 'priority': 'high'},
+                        result=CallToolResult(
+                        content=[
+                            TextContent(
+                                type="text",
+                                text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.", "priority": "high", "status": "open", "created_at": "2026-07-15T16:34:00"}'
                             )
                         ],
                         isError=False
@@ -1597,7 +1854,7 @@
         ),
         Turn(
             role="assistant",
-            content='I checked order ORD-9008 for Omar Ali. The order was canceled and therefore not shipped because the payment authorization failed. \n\nNext steps:\n- If the payment method has been updated, you can place a new order for the USB‑C hub.\n- If you’d like, I can help verify the payment details on file or create a new order now.',
+            content='I checked Kabir Bose’s profile and order ORD-9006. The office chair is delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18. I’ve opened a high-priority support ticket (T-1001) to address and expedite the issue.\n\nNext steps:\n- We’ll monitor the transfer and push for earlier dispatch if possible.\n- If the delivery slips further, we can discuss a partial refund or expedited shipping; let me know if you’d like me to initiate that now.',
         ),
     ],
     mcp_servers=[dummy_support_server],
@@ -1608,7 +1865,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CASE-015-20260714134959</t>
+          <t>CASE-010-20260715163647</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1646,15 +1903,44 @@
 )</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MCPToolCall(
+    name='get_order_status',
+    args={'order_id': 'ORD-9010'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"order_id": "ORD-9010", "customer_id": "C-1004", "status": "shipped", "item": "Portable SSD", "amount": 119.0, "estimated_delivery": "2026-07-15", "issue": "Customer asks for current shipping status."}'
+        )
+    ],
+    isError=False
+)
+)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>LLMTestCase(
-    input='Find the customer and order details for Rahul Mehta, then summarize what support should say.',
-    actual_output='I can’t look up a customer by name alone. Please share one of the following so I can retrieve Rahul Mehta’s details:\n- Customer ID (e.g., C-1234)\n- Any order ID (e.g., ORD-5678)\n- The email or phone number on the account\n\nOnce I have that, I’ll pull his profile and order(s) and summarize exactly what support should say.\n\nIn the meantime, here’s a concise support message template you can use once the details are known:\n- Greet Rahul and verify the account.\n- State the order number, items, and current status with tracking and ETA (or expected ship date if not shipped).\n- If delayed/backordered: apologize, explain cause, give a clear revised timeline, and offer options (keep order with expedited shipping when possible, switch to an alternative, or cancel).\n- If delivered: confirm delivery date and ask if any issues (missing/damaged items); offer replacement or refund as per policy.\n- If lost: apologize, initiate trace with the carrier, and offer replacement or refund immediately if eligible.\n- Close with next steps, a case/ticket number, and contact info for follow‑up.\n\nShare the ID(s) and I’ll fetch the exact details and tailor the message.',
-    expected_output='Look up customer C-1002 and ORD-9002, then explain the delayed laptop stand order and next step.',
+    input='Customer C-1004 asks for the current shipping status of order ORD-9010.',
+    actual_output='I checked order ORD-9010 for customer C-1004. The status is shipped, with an estimated delivery of 2026-07-15 for the Portable SSD. No further action is needed unless the package doesn’t arrive by the estimate—if that happens, let me know and I can assist with tracking or starting an investigation.',
+    expected_output='Look up C-1004, inspect ORD-9010, and provide shipped status plus estimated delivery.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
+        MCPToolCall(
+            name='get_order_status',
+            args={'order_id': 'ORD-9010'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"order_id": "ORD-9010", "customer_id": "C-1004", "status": "shipped", "item": "Portable SSD", "amount": 119.0, "estimated_delivery": "2026-07-15", "issue": "Customer asks for current shipping status."}'
+                )
+            ],
+            isError=False
+        )
+        )
     ],
 )</t>
         </is>
@@ -1663,11 +1949,24 @@
         <is>
           <t>ConversationalTestCase(
     turns=[
-        Turn(role="user", content='Find the customer and order details for Rahul Mehta, then summarize what support should say.'),
+        Turn(role="user", content='Customer C-1004 asks for the current shipping status of order ORD-9010.'),
         Turn(
             role="assistant",
             content="I will use the available MCP tools to complete the request.",
             mcp_tools_called=[
+                    MCPToolCall(
+                        name='get_order_status',
+                        args={'order_id': 'ORD-9010'},
+                        result=CallToolResult(
+                        content=[
+                            TextContent(
+                                type="text",
+                                text='{"order_id": "ORD-9010", "customer_id": "C-1004", "status": "shipped", "item": "Portable SSD", "amount": 119.0, "estimated_delivery": "2026-07-15", "issue": "Customer asks for current shipping status."}'
+                            )
+                        ],
+                        isError=False
+                    )
+                    )
             ],
         ),
         Turn(
@@ -1676,7 +1975,7 @@
         ),
         Turn(
             role="assistant",
-            content='I can’t look up a customer by name alone. Please share one of the following so I can retrieve Rahul Mehta’s details:\n- Customer ID (e.g., C-1234)\n- Any order ID (e.g., ORD-5678)\n- The email or phone number on the account\n\nOnce I have that, I’ll pull his profile and order(s) and summarize exactly what support should say.\n\nIn the meantime, here’s a concise support message template you can use once the details are known:\n- Greet Rahul and verify the account.\n- State the order number, items, and current status with tracking and ETA (or expected ship date if not shipped).\n- If delayed/backordered: apologize, explain cause, give a clear revised timeline, and offer options (keep order with expedited shipping when possible, switch to an alternative, or cancel).\n- If delivered: confirm delivery date and ask if any issues (missing/damaged items); offer replacement or refund as per policy.\n- If lost: apologize, initiate trace with the carrier, and offer replacement or refund immediately if eligible.\n- Close with next steps, a case/ticket number, and contact info for follow‑up.\n\nShare the ID(s) and I’ll fetch the exact details and tailor the message.',
+            content='I checked order ORD-9010 for customer C-1004. The status is shipped, with an estimated delivery of 2026-07-15 for the Portable SSD. No further action is needed unless the package doesn’t arrive by the estimate—if that happens, let me know and I can assist with tracking or starting an investigation.',
         ),
     ],
     mcp_servers=[dummy_support_server],

--- a/Live_Dummy_MCP_Traces.xlsx
+++ b/Live_Dummy_MCP_Traces.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,15 +472,25 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>mcp_jsonrpc_request_json</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>mcp_jsonrpc_response_json</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>tool_arguments_json</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tool_result_json</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>run_status</t>
         </is>
@@ -489,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CASE-001-20260715163219</t>
+          <t>CASE-005-20260715190257</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,40 +509,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-15T16:32:19</t>
+          <t>2026-07-15T19:02:57</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Customer C-1002 says their order is late. Check what happened and explain it.</t>
+          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Look up customer C-1002, inspect order ORD-9002, and explain the weather delay with the estimated delivery date.</t>
+          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status</t>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Here’s what I found for order ORD-9002 (Laptop stand) for Rahul Mehta:
-- Status: Delayed
-- Reason: Weather disruption at the regional sorting center
-- Last estimated delivery date: 2026-07-13 (now 2 days late)
-What happens next:
-- We’ll request an updated ETA from the carrier and keep you posted. Weather-related delays typically clear within 1–3 business days.
-- Per our delivery delay policy, shipping fees can be refunded if the delay exceeds 5 days. If it’s still not delivered by 2026-07-18, we can process a shipping-fee refund.
-- A full order refund isn’t eligible at this time because this order is outside the 30‑day refund window.
-If you’d like, I can open a support ticket to track updates and notify you as soon as the new ETA comes in.</t>
+          <t>I checked Kabir Bose’s order ORD-9006. It’s delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18.
+I’ve opened a high-priority support ticket (T-1001) to expedite the shipment and ensure updates are sent to the customer. Next steps: we’ll push the warehouse team for faster transfer and send Kabir status updates until delivery.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status,search_policy_docs,calculate_refund</t>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -546,22 +549,61 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>{
-  "customer_id": "C-1002"
+  "jsonrpc": "2.0",
+  "id": 1,
+  "method": "tools/call",
+  "params": {
+    "name": "get_customer_profile",
+    "arguments": {
+      "customer_id": "C-1006"
+    }
+  }
 }</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>{
-  "customer_id": "C-1002",
-  "name": "Rahul Mehta",
+  "jsonrpc": "2.0",
+  "id": 1,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"customer_id\": \"C-1006\", \"name\": \"Kabir Bose\", \"tier\": \"Silver\", \"primary_order_id\": \"ORD-9006\", \"email\": \"kabir@example.com\"}"
+      }
+    ],
+    "structuredContent": {
+      "customer_id": "C-1006",
+      "name": "Kabir Bose",
+      "tier": "Silver",
+      "primary_order_id": "ORD-9006",
+      "email": "kabir@example.com"
+    },
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1006"
+}</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1006",
+  "name": "Kabir Bose",
   "tier": "Silver",
-  "primary_order_id": "ORD-9002",
-  "email": "rahul@example.com"
-}</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+  "primary_order_id": "ORD-9006",
+  "email": "kabir@example.com"
+}</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
@@ -570,7 +612,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CASE-001-20260715163219</t>
+          <t>CASE-005-20260715190257</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -580,40 +622,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-15T16:32:19</t>
+          <t>2026-07-15T19:02:57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Customer C-1002 says their order is late. Check what happened and explain it.</t>
+          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Look up customer C-1002, inspect order ORD-9002, and explain the weather delay with the estimated delivery date.</t>
+          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status</t>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Here’s what I found for order ORD-9002 (Laptop stand) for Rahul Mehta:
-- Status: Delayed
-- Reason: Weather disruption at the regional sorting center
-- Last estimated delivery date: 2026-07-13 (now 2 days late)
-What happens next:
-- We’ll request an updated ETA from the carrier and keep you posted. Weather-related delays typically clear within 1–3 business days.
-- Per our delivery delay policy, shipping fees can be refunded if the delay exceeds 5 days. If it’s still not delivered by 2026-07-18, we can process a shipping-fee refund.
-- A full order refund isn’t eligible at this time because this order is outside the 30‑day refund window.
-If you’d like, I can open a support ticket to track updates and notify you as soon as the new ETA comes in.</t>
+          <t>I checked Kabir Bose’s order ORD-9006. It’s delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18.
+I’ve opened a high-priority support ticket (T-1001) to expedite the shipment and ensure updates are sent to the customer. Next steps: we’ll push the warehouse team for faster transfer and send Kabir status updates until delivery.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status,search_policy_docs,calculate_refund</t>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -627,24 +662,65 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>{
-  "order_id": "ORD-9002"
+  "jsonrpc": "2.0",
+  "id": 2,
+  "method": "tools/call",
+  "params": {
+    "name": "get_order_status",
+    "arguments": {
+      "order_id": "ORD-9006"
+    }
+  }
 }</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>{
-  "order_id": "ORD-9002",
-  "customer_id": "C-1002",
+  "jsonrpc": "2.0",
+  "id": 2,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"order_id\": \"ORD-9006\", \"customer_id\": \"C-1006\", \"status\": \"delayed\", \"item\": \"Office chair\", \"amount\": 249.0, \"delay_reason\": \"Inventory transfer from another warehouse.\", \"estimated_delivery\": \"2026-07-18\"}"
+      }
+    ],
+    "structuredContent": {
+      "order_id": "ORD-9006",
+      "customer_id": "C-1006",
+      "status": "delayed",
+      "item": "Office chair",
+      "amount": 249.0,
+      "delay_reason": "Inventory transfer from another warehouse.",
+      "estimated_delivery": "2026-07-18"
+    },
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9006"
+}</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9006",
+  "customer_id": "C-1006",
   "status": "delayed",
-  "item": "Laptop stand",
-  "amount": 45.0,
-  "delay_reason": "Weather disruption at the regional sorting center.",
-  "estimated_delivery": "2026-07-13"
-}</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+  "item": "Office chair",
+  "amount": 249.0,
+  "delay_reason": "Inventory transfer from another warehouse.",
+  "estimated_delivery": "2026-07-18"
+}</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
@@ -653,7 +729,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CASE-001-20260715163219</t>
+          <t>CASE-005-20260715190257</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -663,40 +739,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-15T16:32:19</t>
+          <t>2026-07-15T19:02:57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Customer C-1002 says their order is late. Check what happened and explain it.</t>
+          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Look up customer C-1002, inspect order ORD-9002, and explain the weather delay with the estimated delivery date.</t>
+          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status</t>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Here’s what I found for order ORD-9002 (Laptop stand) for Rahul Mehta:
-- Status: Delayed
-- Reason: Weather disruption at the regional sorting center
-- Last estimated delivery date: 2026-07-13 (now 2 days late)
-What happens next:
-- We’ll request an updated ETA from the carrier and keep you posted. Weather-related delays typically clear within 1–3 business days.
-- Per our delivery delay policy, shipping fees can be refunded if the delay exceeds 5 days. If it’s still not delivered by 2026-07-18, we can process a shipping-fee refund.
-- A full order refund isn’t eligible at this time because this order is outside the 30‑day refund window.
-If you’d like, I can open a support ticket to track updates and notify you as soon as the new ETA comes in.</t>
+          <t>I checked Kabir Bose’s order ORD-9006. It’s delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18.
+I’ve opened a high-priority support ticket (T-1001) to expedite the shipment and ensure updates are sent to the customer. Next steps: we’ll push the warehouse team for faster transfer and send Kabir status updates until delivery.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status,search_policy_docs,calculate_refund</t>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -704,20 +773,1204 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>create_support_ticket</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 3,
+  "method": "tools/call",
+  "params": {
+    "name": "create_support_ticket",
+    "arguments": {
+      "customer_id": "C-1006",
+      "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.",
+      "priority": "high"
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 3,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"ticket_id\": \"T-1001\", \"customer_id\": \"C-1006\", \"issue_summary\": \"Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.\", \"priority\": \"high\", \"status\": \"open\", \"created_at\": \"2026-07-15T19:03:09\"}"
+      }
+    ],
+    "structuredContent": {
+      "ticket_id": "T-1001",
+      "customer_id": "C-1006",
+      "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.",
+      "priority": "high",
+      "status": "open",
+      "created_at": "2026-07-15T19:03:09"
+    },
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1006",
+  "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.",
+  "priority": "high"
+}</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>{
+  "ticket_id": "T-1001",
+  "customer_id": "C-1006",
+  "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.",
+  "priority": "high",
+  "status": "open",
+  "created_at": "2026-07-15T19:03:09"
+}</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CUSTOM-20260715191112</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-15T19:11:12</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Customer C-1006 is asking about his deliveries</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>User-created chatbot case. Review actual output and tool calls against the requested support task.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Here’s what I found for Kabir Bose (C-1006): his current order ORD-9006 (office chair) is delayed due to an inventory transfer from another warehouse. The updated estimated delivery date is 2026-07-18.
+Next steps: I’ll keep an eye on this and can send him an update to kabir@example.com. If it doesn’t ship or arrive by the 18th, we can escalate or discuss options (wait, cancel, or refund). Would you like me to set up notifications or check if he has any other active orders?</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>get_customer_profile</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 1,
+  "method": "tools/call",
+  "params": {
+    "name": "get_customer_profile",
+    "arguments": {
+      "customer_id": "C-1006"
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 1,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"customer_id\": \"C-1006\", \"name\": \"Kabir Bose\", \"tier\": \"Silver\", \"primary_order_id\": \"ORD-9006\", \"email\": \"kabir@example.com\"}"
+      }
+    ],
+    "structuredContent": {
+      "customer_id": "C-1006",
+      "name": "Kabir Bose",
+      "tier": "Silver",
+      "primary_order_id": "ORD-9006",
+      "email": "kabir@example.com"
+    },
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1006"
+}</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1006",
+  "name": "Kabir Bose",
+  "tier": "Silver",
+  "primary_order_id": "ORD-9006",
+  "email": "kabir@example.com"
+}</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CUSTOM-20260715191112</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-07-15T19:11:12</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Customer C-1006 is asking about his deliveries</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>User-created chatbot case. Review actual output and tool calls against the requested support task.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Here’s what I found for Kabir Bose (C-1006): his current order ORD-9006 (office chair) is delayed due to an inventory transfer from another warehouse. The updated estimated delivery date is 2026-07-18.
+Next steps: I’ll keep an eye on this and can send him an update to kabir@example.com. If it doesn’t ship or arrive by the 18th, we can escalate or discuss options (wait, cancel, or refund). Would you like me to set up notifications or check if he has any other active orders?</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>get_order_status</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 2,
+  "method": "tools/call",
+  "params": {
+    "name": "get_order_status",
+    "arguments": {
+      "order_id": "ORD-9006"
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 2,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"order_id\": \"ORD-9006\", \"customer_id\": \"C-1006\", \"status\": \"delayed\", \"item\": \"Office chair\", \"amount\": 249.0, \"delay_reason\": \"Inventory transfer from another warehouse.\", \"estimated_delivery\": \"2026-07-18\"}"
+      }
+    ],
+    "structuredContent": {
+      "order_id": "ORD-9006",
+      "customer_id": "C-1006",
+      "status": "delayed",
+      "item": "Office chair",
+      "amount": 249.0,
+      "delay_reason": "Inventory transfer from another warehouse.",
+      "estimated_delivery": "2026-07-18"
+    },
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9006"
+}</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9006",
+  "customer_id": "C-1006",
+  "status": "delayed",
+  "item": "Office chair",
+  "amount": 249.0,
+  "delay_reason": "Inventory transfer from another warehouse.",
+  "estimated_delivery": "2026-07-18"
+}</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CASE-005-20260715192952</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-07-15T19:29:52</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Here’s what I found and what I’ve done:
+- Order and status: ORD-9006 for an office chair is currently delayed.
+- Reason for delay: Inventory transfer from another warehouse.
+- Current estimated delivery: 2026-07-18.
+- Customer profile: Kabir Bose (Silver), email kabir@example.com.
+Ticket opened:
+- Ticket ID: T-1001
+- Priority: High
+- Status: Open
+- Summary: Escalated the delay for ORD-9006; requested checks on expediting or alternative fulfillment and set up proactive updates to kabir@example.com.
+Next steps:
+- We’ll monitor the shipment and send updates if anything changes.
+- If you prefer a different contact method or want us to explore switching to an in-stock alternative, expediting options, or other arrangements, let me know your preference.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>get_customer_profile</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 1,
+  "method": "tools/call",
+  "params": {
+    "name": "get_customer_profile",
+    "arguments": {
+      "customer_id": "C-1006"
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 1,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"customer_id\": \"C-1006\", \"name\": \"Kabir Bose\", \"tier\": \"Silver\", \"primary_order_id\": \"ORD-9006\", \"email\": \"kabir@example.com\"}"
+      }
+    ],
+    "structuredContent": {
+      "customer_id": "C-1006",
+      "name": "Kabir Bose",
+      "tier": "Silver",
+      "primary_order_id": "ORD-9006",
+      "email": "kabir@example.com"
+    },
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1006"
+}</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1006",
+  "name": "Kabir Bose",
+  "tier": "Silver",
+  "primary_order_id": "ORD-9006",
+  "email": "kabir@example.com"
+}</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CASE-005-20260715192952</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-07-15T19:29:52</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Here’s what I found and what I’ve done:
+- Order and status: ORD-9006 for an office chair is currently delayed.
+- Reason for delay: Inventory transfer from another warehouse.
+- Current estimated delivery: 2026-07-18.
+- Customer profile: Kabir Bose (Silver), email kabir@example.com.
+Ticket opened:
+- Ticket ID: T-1001
+- Priority: High
+- Status: Open
+- Summary: Escalated the delay for ORD-9006; requested checks on expediting or alternative fulfillment and set up proactive updates to kabir@example.com.
+Next steps:
+- We’ll monitor the shipment and send updates if anything changes.
+- If you prefer a different contact method or want us to explore switching to an in-stock alternative, expediting options, or other arrangements, let me know your preference.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>get_order_status</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 2,
+  "method": "tools/call",
+  "params": {
+    "name": "get_order_status",
+    "arguments": {
+      "order_id": "ORD-9006"
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 2,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"order_id\": \"ORD-9006\", \"customer_id\": \"C-1006\", \"status\": \"delayed\", \"item\": \"Office chair\", \"amount\": 249.0, \"delay_reason\": \"Inventory transfer from another warehouse.\", \"estimated_delivery\": \"2026-07-18\"}"
+      }
+    ],
+    "structuredContent": {
+      "order_id": "ORD-9006",
+      "customer_id": "C-1006",
+      "status": "delayed",
+      "item": "Office chair",
+      "amount": 249.0,
+      "delay_reason": "Inventory transfer from another warehouse.",
+      "estimated_delivery": "2026-07-18"
+    },
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9006"
+}</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9006",
+  "customer_id": "C-1006",
+  "status": "delayed",
+  "item": "Office chair",
+  "amount": 249.0,
+  "delay_reason": "Inventory transfer from another warehouse.",
+  "estimated_delivery": "2026-07-18"
+}</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CASE-005-20260715192952</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-15T19:29:52</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Here’s what I found and what I’ve done:
+- Order and status: ORD-9006 for an office chair is currently delayed.
+- Reason for delay: Inventory transfer from another warehouse.
+- Current estimated delivery: 2026-07-18.
+- Customer profile: Kabir Bose (Silver), email kabir@example.com.
+Ticket opened:
+- Ticket ID: T-1001
+- Priority: High
+- Status: Open
+- Summary: Escalated the delay for ORD-9006; requested checks on expediting or alternative fulfillment and set up proactive updates to kabir@example.com.
+Next steps:
+- We’ll monitor the shipment and send updates if anything changes.
+- If you prefer a different contact method or want us to explore switching to an in-stock alternative, expediting options, or other arrangements, let me know your preference.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>create_support_ticket</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 3,
+  "method": "tools/call",
+  "params": {
+    "name": "create_support_ticket",
+    "arguments": {
+      "customer_id": "C-1006",
+      "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.",
+      "priority": "high"
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 3,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"ticket_id\": \"T-1001\", \"customer_id\": \"C-1006\", \"issue_summary\": \"Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.\", \"priority\": \"high\", \"status\": \"open\", \"created_at\": \"2026-07-15T19:30:16\"}"
+      }
+    ],
+    "structuredContent": {
+      "ticket_id": "T-1001",
+      "customer_id": "C-1006",
+      "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.",
+      "priority": "high",
+      "status": "open",
+      "created_at": "2026-07-15T19:30:16"
+    },
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1006",
+  "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.",
+  "priority": "high"
+}</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>{
+  "ticket_id": "T-1001",
+  "customer_id": "C-1006",
+  "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.",
+  "priority": "high",
+  "status": "open",
+  "created_at": "2026-07-15T19:30:16"
+}</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CASE-008-20260715193141</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-15T19:31:41</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Look up C-1004, inspect ORD-9004, and share the processing status with estimated delivery.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Here’s what I see for your order:
+- Customer: Dev Kapoor (C-1004)
+- Order: ORD-9004 — Ergonomic keyboard
+- Status: Processing
+- Estimated delivery date: 2026-07-16
+Policy reference: For processing orders, we share the current status and the estimated delivery date when available.
+Recommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,search_policy_docs,search_policy_docs,search_policy_docs</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>get_customer_profile</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 1,
+  "method": "tools/call",
+  "params": {
+    "name": "get_customer_profile",
+    "arguments": {
+      "customer_id": "C-1004"
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 1,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"customer_id\": \"C-1004\", \"name\": \"Dev Kapoor\", \"tier\": \"Gold\", \"primary_order_id\": \"ORD-9004\", \"email\": \"dev@example.com\"}"
+      }
+    ],
+    "structuredContent": {
+      "customer_id": "C-1004",
+      "name": "Dev Kapoor",
+      "tier": "Gold",
+      "primary_order_id": "ORD-9004",
+      "email": "dev@example.com"
+    },
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1004"
+}</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1004",
+  "name": "Dev Kapoor",
+  "tier": "Gold",
+  "primary_order_id": "ORD-9004",
+  "email": "dev@example.com"
+}</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CASE-008-20260715193141</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-15T19:31:41</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Look up C-1004, inspect ORD-9004, and share the processing status with estimated delivery.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Here’s what I see for your order:
+- Customer: Dev Kapoor (C-1004)
+- Order: ORD-9004 — Ergonomic keyboard
+- Status: Processing
+- Estimated delivery date: 2026-07-16
+Policy reference: For processing orders, we share the current status and the estimated delivery date when available.
+Recommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,search_policy_docs,search_policy_docs,search_policy_docs</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>get_order_status</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 2,
+  "method": "tools/call",
+  "params": {
+    "name": "get_order_status",
+    "arguments": {
+      "order_id": "ORD-9004"
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 2,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"order_id\": \"ORD-9004\", \"customer_id\": \"C-1004\", \"status\": \"processing\", \"item\": \"Ergonomic keyboard\", \"amount\": 89.0, \"estimated_delivery\": \"2026-07-16\", \"issue\": \"Customer wants delivery expectations before travel.\"}"
+      }
+    ],
+    "structuredContent": {
+      "order_id": "ORD-9004",
+      "customer_id": "C-1004",
+      "status": "processing",
+      "item": "Ergonomic keyboard",
+      "amount": 89.0,
+      "estimated_delivery": "2026-07-16",
+      "issue": "Customer wants delivery expectations before travel."
+    },
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9004"
+}</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9004",
+  "customer_id": "C-1004",
+  "status": "processing",
+  "item": "Ergonomic keyboard",
+  "amount": 89.0,
+  "estimated_delivery": "2026-07-16",
+  "issue": "Customer wants delivery expectations before travel."
+}</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CASE-008-20260715193141</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-07-15T19:31:41</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Look up C-1004, inspect ORD-9004, and share the processing status with estimated delivery.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Here’s what I see for your order:
+- Customer: Dev Kapoor (C-1004)
+- Order: ORD-9004 — Ergonomic keyboard
+- Status: Processing
+- Estimated delivery date: 2026-07-16
+Policy reference: For processing orders, we share the current status and the estimated delivery date when available.
+Recommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,search_policy_docs,search_policy_docs,search_policy_docs</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>search_policy_docs</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>{
-  "query": "delivery delay due to weather disruption policy next steps escalation compensation refund eligibility"
-}</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>{
-  "query": "delivery delay due to weather disruption policy next steps escalation compensation refund eligibility",
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 3,
+  "method": "tools/call",
+  "params": {
+    "name": "search_policy_docs",
+    "arguments": {
+      "query": "shipping-status updates notification email tracking when order is processing"
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 3,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"query\": \"shipping-status updates notification email tracking when order is processing\", \"matches\": [{\"policy_id\": \"delivery\", \"title\": \"Delivery delay policy\", \"summary\": \"If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days.\"}, {\"policy_id\": \"damaged_item\", \"title\": \"Damaged item policy\", \"summary\": \"Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases.\"}, {\"policy_id\": \"cancellation\", \"title\": \"Cancellation policy\", \"summary\": \"Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails.\"}, {\"policy_id\": \"shipping_status\", \"title\": \"Shipping status policy\", \"summary\": \"For shipped or processing orders, share the current status and estimated delivery date when available.\"}]}"
+      }
+    ],
+    "structuredContent": {
+      "query": "shipping-status updates notification email tracking when order is processing",
+      "matches": [
+        {
+          "policy_id": "delivery",
+          "title": "Delivery delay policy",
+          "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."
+        },
+        {
+          "policy_id": "damaged_item",
+          "title": "Damaged item policy",
+          "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."
+        },
+        {
+          "policy_id": "cancellation",
+          "title": "Cancellation policy",
+          "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."
+        },
+        {
+          "policy_id": "shipping_status",
+          "title": "Shipping status policy",
+          "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."
+        }
+      ]
+    },
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>{
+  "query": "shipping-status updates notification email tracking when order is processing"
+}</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>{
+  "query": "shipping-status updates notification email tracking when order is processing",
+  "matches": [
+    {
+      "policy_id": "delivery",
+      "title": "Delivery delay policy",
+      "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."
+    },
+    {
+      "policy_id": "damaged_item",
+      "title": "Damaged item policy",
+      "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."
+    },
+    {
+      "policy_id": "cancellation",
+      "title": "Cancellation policy",
+      "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."
+    },
+    {
+      "policy_id": "shipping_status",
+      "title": "Shipping status policy",
+      "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CASE-008-20260715193141</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-07-15T19:31:41</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Look up C-1004, inspect ORD-9004, and share the processing status with estimated delivery.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Here’s what I see for your order:
+- Customer: Dev Kapoor (C-1004)
+- Order: ORD-9004 — Ergonomic keyboard
+- Status: Processing
+- Estimated delivery date: 2026-07-16
+Policy reference: For processing orders, we share the current status and the estimated delivery date when available.
+Recommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,search_policy_docs,search_policy_docs,search_policy_docs</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>search_policy_docs</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 4,
+  "method": "tools/call",
+  "params": {
+    "name": "search_policy_docs",
+    "arguments": {
+      "query": "address change after order placed processing policy hold at carrier pickup reroute"
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 4,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"query\": \"address change after order placed processing policy hold at carrier pickup reroute\", \"matches\": [{\"policy_id\": \"refund\", \"title\": \"Refund policy\", \"summary\": \"Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review.\"}, {\"policy_id\": \"delivery\", \"title\": \"Delivery delay policy\", \"summary\": \"If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days.\"}, {\"policy_id\": \"damaged_item\", \"title\": \"Damaged item policy\", \"summary\": \"Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases.\"}, {\"policy_id\": \"cancellation\", \"title\": \"Cancellation policy\", \"summary\": \"Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails.\"}, {\"policy_id\": \"shipping_status\", \"title\": \"Shipping status policy\", \"summary\": \"For shipped or processing orders, share the current status and estimated delivery date when available.\"}]}"
+      }
+    ],
+    "structuredContent": {
+      "query": "address change after order placed processing policy hold at carrier pickup reroute",
+      "matches": [
+        {
+          "policy_id": "refund",
+          "title": "Refund policy",
+          "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."
+        },
+        {
+          "policy_id": "delivery",
+          "title": "Delivery delay policy",
+          "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."
+        },
+        {
+          "policy_id": "damaged_item",
+          "title": "Damaged item policy",
+          "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."
+        },
+        {
+          "policy_id": "cancellation",
+          "title": "Cancellation policy",
+          "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."
+        },
+        {
+          "policy_id": "shipping_status",
+          "title": "Shipping status policy",
+          "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."
+        }
+      ]
+    },
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>{
+  "query": "address change after order placed processing policy hold at carrier pickup reroute"
+}</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>{
+  "query": "address change after order placed processing policy hold at carrier pickup reroute",
   "matches": [
     {
       "policy_id": "refund",
@@ -748,396 +2001,171 @@
 }</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CASE-001-20260715163219</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CASE-008-20260715193141</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>single_turn</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-07-15T16:32:19</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Customer C-1002 says their order is late. Check what happened and explain it.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Look up customer C-1002, inspect order ORD-9002, and explain the weather delay with the estimated delivery date.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-07-15T19:31:41</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Look up C-1004, inspect ORD-9004, and share the processing status with estimated delivery.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>get_customer_profile,get_order_status</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Here’s what I found for order ORD-9002 (Laptop stand) for Rahul Mehta:
-- Status: Delayed
-- Reason: Weather disruption at the regional sorting center
-- Last estimated delivery date: 2026-07-13 (now 2 days late)
-What happens next:
-- We’ll request an updated ETA from the carrier and keep you posted. Weather-related delays typically clear within 1–3 business days.
-- Per our delivery delay policy, shipping fees can be refunded if the delay exceeds 5 days. If it’s still not delivered by 2026-07-18, we can process a shipping-fee refund.
-- A full order refund isn’t eligible at this time because this order is outside the 30‑day refund window.
-If you’d like, I can open a support ticket to track updates and notify you as soon as the new ETA comes in.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,search_policy_docs,calculate_refund</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>calculate_refund</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9002",
-  "reason": "delivery delay due to weather disruption"
-}</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9002",
-  "eligible": false,
-  "refund_amount": 0.0,
-  "reason": "Order is outside the 30 day refund window."
-}</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CASE-005-20260715163351</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-07-15T16:33:51</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>I checked Kabir Bose’s profile and order ORD-9006. The office chair is delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18. I’ve opened a high-priority support ticket (T-1001) to address and expedite the issue.
-Next steps:
-- We’ll monitor the transfer and push for earlier dispatch if possible.
-- If the delivery slips further, we can discuss a partial refund or expedited shipping; let me know if you’d like me to initiate that now.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>get_customer_profile</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1006"
-}</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1006",
-  "name": "Kabir Bose",
-  "tier": "Silver",
-  "primary_order_id": "ORD-9006",
-  "email": "kabir@example.com"
-}</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CASE-005-20260715163351</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-07-15T16:33:51</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>I checked Kabir Bose’s profile and order ORD-9006. The office chair is delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18. I’ve opened a high-priority support ticket (T-1001) to address and expedite the issue.
-Next steps:
-- We’ll monitor the transfer and push for earlier dispatch if possible.
-- If the delivery slips further, we can discuss a partial refund or expedited shipping; let me know if you’d like me to initiate that now.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>get_order_status</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9006"
-}</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9006",
-  "customer_id": "C-1006",
-  "status": "delayed",
-  "item": "Office chair",
-  "amount": 249.0,
-  "delay_reason": "Inventory transfer from another warehouse.",
-  "estimated_delivery": "2026-07-18"
-}</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CASE-005-20260715163351</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-07-15T16:33:51</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>I checked Kabir Bose’s profile and order ORD-9006. The office chair is delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18. I’ve opened a high-priority support ticket (T-1001) to address and expedite the issue.
-Next steps:
-- We’ll monitor the transfer and push for earlier dispatch if possible.
-- If the delivery slips further, we can discuss a partial refund or expedited shipping; let me know if you’d like me to initiate that now.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>create_support_ticket</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1006",
-  "issue_summary": "Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.",
-  "priority": "high"
-}</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>{
-  "ticket_id": "T-1001",
-  "customer_id": "C-1006",
-  "issue_summary": "Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.",
-  "priority": "high",
-  "status": "open",
-  "created_at": "2026-07-15T16:34:00"
-}</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CASE-010-20260715163647</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-07-15T16:36:47</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Customer C-1004 asks for the current shipping status of order ORD-9010.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Look up C-1004, inspect ORD-9010, and provide shipped status plus estimated delivery.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>I checked order ORD-9010 for customer C-1004. The status is shipped, with an estimated delivery of 2026-07-15 for the Portable SSD. No further action is needed unless the package doesn’t arrive by the estimate—if that happens, let me know and I can assist with tracking or starting an investigation.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>get_order_status</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>get_order_status</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9010"
-}</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9010",
-  "customer_id": "C-1004",
-  "status": "shipped",
-  "item": "Portable SSD",
-  "amount": 119.0,
-  "estimated_delivery": "2026-07-15",
-  "issue": "Customer asks for current shipping status."
-}</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Here’s what I see for your order:
+- Customer: Dev Kapoor (C-1004)
+- Order: ORD-9004 — Ergonomic keyboard
+- Status: Processing
+- Estimated delivery date: 2026-07-16
+Policy reference: For processing orders, we share the current status and the estimated delivery date when available.
+Recommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status,search_policy_docs,search_policy_docs,search_policy_docs</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>search_policy_docs</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 5,
+  "method": "tools/call",
+  "params": {
+    "name": "search_policy_docs",
+    "arguments": {
+      "query": "expedited shipping request after order placed policy"
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 5,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"query\": \"expedited shipping request after order placed policy\", \"matches\": [{\"policy_id\": \"refund\", \"title\": \"Refund policy\", \"summary\": \"Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review.\"}, {\"policy_id\": \"delivery\", \"title\": \"Delivery delay policy\", \"summary\": \"If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days.\"}, {\"policy_id\": \"damaged_item\", \"title\": \"Damaged item policy\", \"summary\": \"Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases.\"}, {\"policy_id\": \"cancellation\", \"title\": \"Cancellation policy\", \"summary\": \"Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails.\"}, {\"policy_id\": \"shipping_status\", \"title\": \"Shipping status policy\", \"summary\": \"For shipped or processing orders, share the current status and estimated delivery date when available.\"}]}"
+      }
+    ],
+    "structuredContent": {
+      "query": "expedited shipping request after order placed policy",
+      "matches": [
+        {
+          "policy_id": "refund",
+          "title": "Refund policy",
+          "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."
+        },
+        {
+          "policy_id": "delivery",
+          "title": "Delivery delay policy",
+          "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."
+        },
+        {
+          "policy_id": "damaged_item",
+          "title": "Damaged item policy",
+          "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."
+        },
+        {
+          "policy_id": "cancellation",
+          "title": "Cancellation policy",
+          "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."
+        },
+        {
+          "policy_id": "shipping_status",
+          "title": "Shipping status policy",
+          "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."
+        }
+      ]
+    },
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>{
+  "query": "expedited shipping request after order placed policy"
+}</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>{
+  "query": "expedited shipping request after order placed policy",
+  "matches": [
+    {
+      "policy_id": "refund",
+      "title": "Refund policy",
+      "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."
+    },
+    {
+      "policy_id": "delivery",
+      "title": "Delivery delay policy",
+      "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."
+    },
+    {
+      "policy_id": "damaged_item",
+      "title": "Damaged item policy",
+      "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."
+    },
+    {
+      "policy_id": "cancellation",
+      "title": "Cancellation policy",
+      "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."
+    },
+    {
+      "policy_id": "shipping_status",
+      "title": "Shipping status policy",
+      "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
@@ -1395,7 +2423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1428,7 +2456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CASE-001-20260715163219</t>
+          <t>CASE-005-20260715190257</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1470,12 +2498,12 @@
         <is>
           <t>MCPToolCall(
     name='get_customer_profile',
-    args={'customer_id': 'C-1002'},
+    args={'customer_id': 'C-1006'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"customer_id": "C-1002", "name": "Rahul Mehta", "tier": "Silver", "primary_order_id": "ORD-9002", "email": "rahul@example.com"}'
+            text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
         )
     ],
     isError=False
@@ -1483,38 +2511,25 @@
 )
 MCPToolCall(
     name='get_order_status',
-    args={'order_id': 'ORD-9002'},
+    args={'order_id': 'ORD-9006'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"order_id": "ORD-9002", "customer_id": "C-1002", "status": "delayed", "item": "Laptop stand", "amount": 45.0, "delay_reason": "Weather disruption at the regional sorting center.", "estimated_delivery": "2026-07-13"}'
+            text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
         )
     ],
     isError=False
 )
 )
 MCPToolCall(
-    name='search_policy_docs',
-    args={'query': 'delivery delay due to weather disruption policy next steps escalation compensation refund eligibility'},
+    name='create_support_ticket',
+    args={'customer_id': 'C-1006', 'issue_summary': 'Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.', 'priority': 'high'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"query": "delivery delay due to weather disruption policy next steps escalation compensation refund eligibility", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
-        )
-    ],
-    isError=False
-)
-)
-MCPToolCall(
-    name='calculate_refund',
-    args={'order_id': 'ORD-9002', 'reason': 'delivery delay due to weather disruption'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"order_id": "ORD-9002", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
+            text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.", "priority": "high", "status": "open", "created_at": "2026-07-15T19:03:09"}'
         )
     ],
     isError=False
@@ -1525,19 +2540,19 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>LLMTestCase(
-    input='Customer C-1002 says their order is late. Check what happened and explain it.',
-    actual_output='Here’s what I found for order ORD-9002 (Laptop stand) for Rahul Mehta:\n\n- Status: Delayed\n- Reason: Weather disruption at the regional sorting center\n- Last estimated delivery date: 2026-07-13 (now 2 days late)\n\nWhat happens next:\n- We’ll request an updated ETA from the carrier and keep you posted. Weather-related delays typically clear within 1–3 business days.\n- Per our delivery delay policy, shipping fees can be refunded if the delay exceeds 5 days. If it’s still not delivered by 2026-07-18, we can process a shipping-fee refund.\n- A full order refund isn’t eligible at this time because this order is outside the 30‑day refund window.\n\nIf you’d like, I can open a support ticket to track updates and notify you as soon as the new ETA comes in.',
-    expected_output='Look up customer C-1002, inspect order ORD-9002, and explain the weather delay with the estimated delivery date.',
+    input='Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.',
+    actual_output='I checked Kabir Bose’s order ORD-9006. It’s delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18.\n\nI’ve opened a high-priority support ticket (T-1001) to expedite the shipment and ensure updates are sent to the customer. Next steps: we’ll push the warehouse team for faster transfer and send Kabir status updates until delivery.',
+    expected_output='Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
         MCPToolCall(
             name='get_customer_profile',
-            args={'customer_id': 'C-1002'},
+            args={'customer_id': 'C-1006'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"customer_id": "C-1002", "name": "Rahul Mehta", "tier": "Silver", "primary_order_id": "ORD-9002", "email": "rahul@example.com"}'
+                    text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
                 )
             ],
             isError=False
@@ -1545,38 +2560,25 @@
         ),
         MCPToolCall(
             name='get_order_status',
-            args={'order_id': 'ORD-9002'},
+            args={'order_id': 'ORD-9006'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"order_id": "ORD-9002", "customer_id": "C-1002", "status": "delayed", "item": "Laptop stand", "amount": 45.0, "delay_reason": "Weather disruption at the regional sorting center.", "estimated_delivery": "2026-07-13"}'
+                    text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
                 )
             ],
             isError=False
         )
         ),
         MCPToolCall(
-            name='search_policy_docs',
-            args={'query': 'delivery delay due to weather disruption policy next steps escalation compensation refund eligibility'},
+            name='create_support_ticket',
+            args={'customer_id': 'C-1006', 'issue_summary': 'Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.', 'priority': 'high'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"query": "delivery delay due to weather disruption policy next steps escalation compensation refund eligibility", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
-                )
-            ],
-            isError=False
-        )
-        ),
-        MCPToolCall(
-            name='calculate_refund',
-            args={'order_id': 'ORD-9002', 'reason': 'delivery delay due to weather disruption'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"order_id": "ORD-9002", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
+                    text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.", "priority": "high", "status": "open", "created_at": "2026-07-15T19:03:09"}'
                 )
             ],
             isError=False
@@ -1590,19 +2592,19 @@
         <is>
           <t>ConversationalTestCase(
     turns=[
-        Turn(role="user", content='Customer C-1002 says their order is late. Check what happened and explain it.'),
+        Turn(role="user", content='Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.'),
         Turn(
             role="assistant",
-            content="I will use the available MCP tools to complete the request.",
+            content='I checked Kabir Bose’s order ORD-9006. It’s delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18.\n\nI’ve opened a high-priority support ticket (T-1001) to expedite the shipment and ensure updates are sent to the customer. Next steps: we’ll push the warehouse team for faster transfer and send Kabir status updates until delivery.',
             mcp_tools_called=[
                     MCPToolCall(
                         name='get_customer_profile',
-                        args={'customer_id': 'C-1002'},
+                        args={'customer_id': 'C-1006'},
                         result=CallToolResult(
                         content=[
                             TextContent(
                                 type="text",
-                                text='{"customer_id": "C-1002", "name": "Rahul Mehta", "tier": "Silver", "primary_order_id": "ORD-9002", "email": "rahul@example.com"}'
+                                text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
                             )
                         ],
                         isError=False
@@ -1610,38 +2612,25 @@
                     ),
                     MCPToolCall(
                         name='get_order_status',
-                        args={'order_id': 'ORD-9002'},
+                        args={'order_id': 'ORD-9006'},
                         result=CallToolResult(
                         content=[
                             TextContent(
                                 type="text",
-                                text='{"order_id": "ORD-9002", "customer_id": "C-1002", "status": "delayed", "item": "Laptop stand", "amount": 45.0, "delay_reason": "Weather disruption at the regional sorting center.", "estimated_delivery": "2026-07-13"}'
+                                text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
                             )
                         ],
                         isError=False
                     )
                     ),
                     MCPToolCall(
-                        name='search_policy_docs',
-                        args={'query': 'delivery delay due to weather disruption policy next steps escalation compensation refund eligibility'},
+                        name='create_support_ticket',
+                        args={'customer_id': 'C-1006', 'issue_summary': 'Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.', 'priority': 'high'},
                         result=CallToolResult(
                         content=[
                             TextContent(
                                 type="text",
-                                text='{"query": "delivery delay due to weather disruption policy next steps escalation compensation refund eligibility", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
-                            )
-                        ],
-                        isError=False
-                    )
-                    ),
-                    MCPToolCall(
-                        name='calculate_refund',
-                        args={'order_id': 'ORD-9002', 'reason': 'delivery delay due to weather disruption'},
-                        result=CallToolResult(
-                        content=[
-                            TextContent(
-                                type="text",
-                                text='{"order_id": "ORD-9002", "eligible": false, "refund_amount": 0.0, "reason": "Order is outside the 30 day refund window."}'
+                                text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.", "priority": "high", "status": "open", "created_at": "2026-07-15T19:03:09"}'
                             )
                         ],
                         isError=False
@@ -1649,14 +2638,6 @@
                     )
             ],
         ),
-        Turn(
-            role="assistant",
-            content="The MCP tools returned the support data needed for the answer.",
-        ),
-        Turn(
-            role="assistant",
-            content='Here’s what I found for order ORD-9002 (Laptop stand) for Rahul Mehta:\n\n- Status: Delayed\n- Reason: Weather disruption at the regional sorting center\n- Last estimated delivery date: 2026-07-13 (now 2 days late)\n\nWhat happens next:\n- We’ll request an updated ETA from the carrier and keep you posted. Weather-related delays typically clear within 1–3 business days.\n- Per our delivery delay policy, shipping fees can be refunded if the delay exceeds 5 days. If it’s still not delivered by 2026-07-18, we can process a shipping-fee refund.\n- A full order refund isn’t eligible at this time because this order is outside the 30‑day refund window.\n\nIf you’d like, I can open a support ticket to track updates and notify you as soon as the new ETA comes in.',
-        ),
     ],
     mcp_servers=[dummy_support_server],
 )</t>
@@ -1666,7 +2647,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CASE-005-20260715163351</t>
+          <t>CUSTOM-20260715191112</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1731,15 +2712,167 @@
     ],
     isError=False
 )
-)
-MCPToolCall(
-    name='create_support_ticket',
-    args={'customer_id': 'C-1006', 'issue_summary': 'Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.', 'priority': 'high'},
+)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LLMTestCase(
+    input='Customer C-1006 is asking about his deliveries',
+    actual_output='Here’s what I found for Kabir Bose (C-1006): his current order ORD-9006 (office chair) is delayed due to an inventory transfer from another warehouse. The updated estimated delivery date is 2026-07-18.\n\nNext steps: I’ll keep an eye on this and can send him an update to kabir@example.com. If it doesn’t ship or arrive by the 18th, we can escalate or discuss options (wait, cancel, or refund). Would you like me to set up notifications or check if he has any other active orders?',
+    expected_output='User-created chatbot case. Review actual output and tool calls against the requested support task.',
+    mcp_servers=[dummy_support_server],
+    mcp_tools_called=[
+        MCPToolCall(
+            name='get_customer_profile',
+            args={'customer_id': 'C-1006'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
+                )
+            ],
+            isError=False
+        )
+        ),
+        MCPToolCall(
+            name='get_order_status',
+            args={'order_id': 'ORD-9006'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
+                )
+            ],
+            isError=False
+        )
+        )
+    ],
+)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ConversationalTestCase(
+    turns=[
+        Turn(role="user", content='Customer C-1006 is asking about his deliveries'),
+        Turn(
+            role="assistant",
+            content='Here’s what I found for Kabir Bose (C-1006): his current order ORD-9006 (office chair) is delayed due to an inventory transfer from another warehouse. The updated estimated delivery date is 2026-07-18.\n\nNext steps: I’ll keep an eye on this and can send him an update to kabir@example.com. If it doesn’t ship or arrive by the 18th, we can escalate or discuss options (wait, cancel, or refund). Would you like me to set up notifications or check if he has any other active orders?',
+            mcp_tools_called=[
+                    MCPToolCall(
+                        name='get_customer_profile',
+                        args={'customer_id': 'C-1006'},
+                        result=CallToolResult(
+                        content=[
+                            TextContent(
+                                type="text",
+                                text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
+                            )
+                        ],
+                        isError=False
+                    )
+                    ),
+                    MCPToolCall(
+                        name='get_order_status',
+                        args={'order_id': 'ORD-9006'},
+                        result=CallToolResult(
+                        content=[
+                            TextContent(
+                                type="text",
+                                text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
+                            )
+                        ],
+                        isError=False
+                    )
+                    )
+            ],
+        ),
+    ],
+    mcp_servers=[dummy_support_server],
+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CASE-005-20260715192952</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dummy_support_server = MCPServer(
+    server_name="dummy_support",
+    transport="streamable-http",
+    available_tools=[
+        Tool(
+            name='get_customer_profile',
+            description='Get a customer profile by customer ID.',
+            inputSchema={'type': 'object', 'properties': {'customer_id': {'type': 'string', 'description': 'Customer ID such as C-1002.'}}, 'required': ['customer_id'], 'additionalProperties': False},
+        ),
+        Tool(
+            name='get_order_status',
+            description='Get order status and order details by order ID.',
+            inputSchema={'type': 'object', 'properties': {'order_id': {'type': 'string', 'description': 'Order ID such as ORD-9002.'}}, 'required': ['order_id'], 'additionalProperties': False},
+        ),
+        Tool(
+            name='search_policy_docs',
+            description='Search support policy documents.',
+            inputSchema={'type': 'object', 'properties': {'query': {'type': 'string', 'description': 'Policy search query.'}}, 'required': ['query'], 'additionalProperties': False},
+        ),
+        Tool(
+            name='calculate_refund',
+            description='Calculate refund eligibility for an order.',
+            inputSchema={'type': 'object', 'properties': {'order_id': {'type': 'string'}, 'reason': {'type': 'string'}}, 'required': ['order_id', 'reason'], 'additionalProperties': False},
+        ),
+        Tool(
+            name='create_support_ticket',
+            description='Create a support ticket for a customer issue.',
+            inputSchema={'type': 'object', 'properties': {'customer_id': {'type': 'string'}, 'issue_summary': {'type': 'string'}, 'priority': {'type': 'string', 'enum': ['low', 'normal', 'high']}}, 'required': ['customer_id', 'issue_summary', 'priority'], 'additionalProperties': False},
+        )
+    ],
+)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MCPToolCall(
+    name='get_customer_profile',
+    args={'customer_id': 'C-1006'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.", "priority": "high", "status": "open", "created_at": "2026-07-15T16:34:00"}'
+            text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
+        )
+    ],
+    isError=False
+)
+)
+MCPToolCall(
+    name='get_order_status',
+    args={'order_id': 'ORD-9006'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
+        )
+    ],
+    isError=False
+)
+)
+MCPToolCall(
+    name='create_support_ticket',
+    args={'customer_id': 'C-1006', 'issue_summary': 'Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.', 'priority': 'high'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.", "priority": "high", "status": "open", "created_at": "2026-07-15T19:30:16"}'
         )
     ],
     isError=False
@@ -1747,11 +2880,11 @@
 )</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>LLMTestCase(
     input='Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.',
-    actual_output='I checked Kabir Bose’s profile and order ORD-9006. The office chair is delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18. I’ve opened a high-priority support ticket (T-1001) to address and expedite the issue.\n\nNext steps:\n- We’ll monitor the transfer and push for earlier dispatch if possible.\n- If the delivery slips further, we can discuss a partial refund or expedited shipping; let me know if you’d like me to initiate that now.',
+    actual_output='Here’s what I found and what I’ve done:\n\n- Order and status: ORD-9006 for an office chair is currently delayed.\n- Reason for delay: Inventory transfer from another warehouse.\n- Current estimated delivery: 2026-07-18.\n- Customer profile: Kabir Bose (Silver), email kabir@example.com.\n\nTicket opened:\n- Ticket ID: T-1001\n- Priority: High\n- Status: Open\n- Summary: Escalated the delay for ORD-9006; requested checks on expediting or alternative fulfillment and set up proactive updates to kabir@example.com.\n\nNext steps:\n- We’ll monitor the shipment and send updates if anything changes.\n- If you prefer a different contact method or want us to explore switching to an in-stock alternative, expediting options, or other arrangements, let me know your preference.',
     expected_output='Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
@@ -1783,12 +2916,12 @@
         ),
         MCPToolCall(
             name='create_support_ticket',
-            args={'customer_id': 'C-1006', 'issue_summary': 'Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.', 'priority': 'high'},
+            args={'customer_id': 'C-1006', 'issue_summary': 'Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.', 'priority': 'high'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.", "priority": "high", "status": "open", "created_at": "2026-07-15T16:34:00"}'
+                    text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.", "priority": "high", "status": "open", "created_at": "2026-07-15T19:30:16"}'
                 )
             ],
             isError=False
@@ -1798,14 +2931,14 @@
 )</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>ConversationalTestCase(
     turns=[
         Turn(role="user", content='Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.'),
         Turn(
             role="assistant",
-            content="I will use the available MCP tools to complete the request.",
+            content='Here’s what I found and what I’ve done:\n\n- Order and status: ORD-9006 for an office chair is currently delayed.\n- Reason for delay: Inventory transfer from another warehouse.\n- Current estimated delivery: 2026-07-18.\n- Customer profile: Kabir Bose (Silver), email kabir@example.com.\n\nTicket opened:\n- Ticket ID: T-1001\n- Priority: High\n- Status: Open\n- Summary: Escalated the delay for ORD-9006; requested checks on expediting or alternative fulfillment and set up proactive updates to kabir@example.com.\n\nNext steps:\n- We’ll monitor the shipment and send updates if anything changes.\n- If you prefer a different contact method or want us to explore switching to an in-stock alternative, expediting options, or other arrangements, let me know your preference.',
             mcp_tools_called=[
                     MCPToolCall(
                         name='get_customer_profile',
@@ -1835,12 +2968,12 @@
                     ),
                     MCPToolCall(
                         name='create_support_ticket',
-                        args={'customer_id': 'C-1006', 'issue_summary': 'Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.', 'priority': 'high'},
+                        args={'customer_id': 'C-1006', 'issue_summary': 'Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.', 'priority': 'high'},
                         result=CallToolResult(
                         content=[
                             TextContent(
                                 type="text",
-                                text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Order ORD-9006 (office chair) delayed due to inventory transfer; customer upset and requests resolution/expedite.", "priority": "high", "status": "open", "created_at": "2026-07-15T16:34:00"}'
+                                text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.", "priority": "high", "status": "open", "created_at": "2026-07-15T19:30:16"}'
                             )
                         ],
                         isError=False
@@ -1848,27 +2981,19 @@
                     )
             ],
         ),
-        Turn(
-            role="assistant",
-            content="The MCP tools returned the support data needed for the answer.",
-        ),
-        Turn(
-            role="assistant",
-            content='I checked Kabir Bose’s profile and order ORD-9006. The office chair is delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18. I’ve opened a high-priority support ticket (T-1001) to address and expedite the issue.\n\nNext steps:\n- We’ll monitor the transfer and push for earlier dispatch if possible.\n- If the delivery slips further, we can discuss a partial refund or expedited shipping; let me know if you’d like me to initiate that now.',
-        ),
     ],
     mcp_servers=[dummy_support_server],
 )</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CASE-010-20260715163647</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CASE-008-20260715193141</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>dummy_support_server = MCPServer(
     server_name="dummy_support",
@@ -1903,16 +3028,68 @@
 )</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>MCPToolCall(
-    name='get_order_status',
-    args={'order_id': 'ORD-9010'},
+    name='get_customer_profile',
+    args={'customer_id': 'C-1004'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"order_id": "ORD-9010", "customer_id": "C-1004", "status": "shipped", "item": "Portable SSD", "amount": 119.0, "estimated_delivery": "2026-07-15", "issue": "Customer asks for current shipping status."}'
+            text='{"customer_id": "C-1004", "name": "Dev Kapoor", "tier": "Gold", "primary_order_id": "ORD-9004", "email": "dev@example.com"}'
+        )
+    ],
+    isError=False
+)
+)
+MCPToolCall(
+    name='get_order_status',
+    args={'order_id': 'ORD-9004'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"order_id": "ORD-9004", "customer_id": "C-1004", "status": "processing", "item": "Ergonomic keyboard", "amount": 89.0, "estimated_delivery": "2026-07-16", "issue": "Customer wants delivery expectations before travel."}'
+        )
+    ],
+    isError=False
+)
+)
+MCPToolCall(
+    name='search_policy_docs',
+    args={'query': 'shipping-status updates notification email tracking when order is processing'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"query": "shipping-status updates notification email tracking when order is processing", "matches": [{"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+        )
+    ],
+    isError=False
+)
+)
+MCPToolCall(
+    name='search_policy_docs',
+    args={'query': 'address change after order placed processing policy hold at carrier pickup reroute'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"query": "address change after order placed processing policy hold at carrier pickup reroute", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+        )
+    ],
+    isError=False
+)
+)
+MCPToolCall(
+    name='search_policy_docs',
+    args={'query': 'expedited shipping request after order placed policy'},
+    result=CallToolResult(
+    content=[
+        TextContent(
+            type="text",
+            text='{"query": "expedited shipping request after order placed policy", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
         )
     ],
     isError=False
@@ -1920,22 +3097,74 @@
 )</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>LLMTestCase(
-    input='Customer C-1004 asks for the current shipping status of order ORD-9010.',
-    actual_output='I checked order ORD-9010 for customer C-1004. The status is shipped, with an estimated delivery of 2026-07-15 for the Portable SSD. No further action is needed unless the package doesn’t arrive by the estimate—if that happens, let me know and I can assist with tracking or starting an investigation.',
-    expected_output='Look up C-1004, inspect ORD-9010, and provide shipped status plus estimated delivery.',
+    input='Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.',
+    actual_output='Here’s what I see for your order:\n\n- Customer: Dev Kapoor (C-1004)\n- Order: ORD-9004 — Ergonomic keyboard\n- Status: Processing\n- Estimated delivery date: 2026-07-16\n\nPolicy reference: For processing orders, we share the current status and the estimated delivery date when available.\n\nRecommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.',
+    expected_output='Look up C-1004, inspect ORD-9004, and share the processing status with estimated delivery.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
         MCPToolCall(
-            name='get_order_status',
-            args={'order_id': 'ORD-9010'},
+            name='get_customer_profile',
+            args={'customer_id': 'C-1004'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"order_id": "ORD-9010", "customer_id": "C-1004", "status": "shipped", "item": "Portable SSD", "amount": 119.0, "estimated_delivery": "2026-07-15", "issue": "Customer asks for current shipping status."}'
+                    text='{"customer_id": "C-1004", "name": "Dev Kapoor", "tier": "Gold", "primary_order_id": "ORD-9004", "email": "dev@example.com"}'
+                )
+            ],
+            isError=False
+        )
+        ),
+        MCPToolCall(
+            name='get_order_status',
+            args={'order_id': 'ORD-9004'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"order_id": "ORD-9004", "customer_id": "C-1004", "status": "processing", "item": "Ergonomic keyboard", "amount": 89.0, "estimated_delivery": "2026-07-16", "issue": "Customer wants delivery expectations before travel."}'
+                )
+            ],
+            isError=False
+        )
+        ),
+        MCPToolCall(
+            name='search_policy_docs',
+            args={'query': 'shipping-status updates notification email tracking when order is processing'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"query": "shipping-status updates notification email tracking when order is processing", "matches": [{"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+                )
+            ],
+            isError=False
+        )
+        ),
+        MCPToolCall(
+            name='search_policy_docs',
+            args={'query': 'address change after order placed processing policy hold at carrier pickup reroute'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"query": "address change after order placed processing policy hold at carrier pickup reroute", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+                )
+            ],
+            isError=False
+        )
+        ),
+        MCPToolCall(
+            name='search_policy_docs',
+            args={'query': 'expedited shipping request after order placed policy'},
+            result=CallToolResult(
+            content=[
+                TextContent(
+                    type="text",
+                    text='{"query": "expedited shipping request after order placed policy", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
                 )
             ],
             isError=False
@@ -1945,37 +3174,81 @@
 )</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>ConversationalTestCase(
     turns=[
-        Turn(role="user", content='Customer C-1004 asks for the current shipping status of order ORD-9010.'),
+        Turn(role="user", content='Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.'),
         Turn(
             role="assistant",
-            content="I will use the available MCP tools to complete the request.",
+            content='Here’s what I see for your order:\n\n- Customer: Dev Kapoor (C-1004)\n- Order: ORD-9004 — Ergonomic keyboard\n- Status: Processing\n- Estimated delivery date: 2026-07-16\n\nPolicy reference: For processing orders, we share the current status and the estimated delivery date when available.\n\nRecommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.',
             mcp_tools_called=[
                     MCPToolCall(
-                        name='get_order_status',
-                        args={'order_id': 'ORD-9010'},
+                        name='get_customer_profile',
+                        args={'customer_id': 'C-1004'},
                         result=CallToolResult(
                         content=[
                             TextContent(
                                 type="text",
-                                text='{"order_id": "ORD-9010", "customer_id": "C-1004", "status": "shipped", "item": "Portable SSD", "amount": 119.0, "estimated_delivery": "2026-07-15", "issue": "Customer asks for current shipping status."}'
+                                text='{"customer_id": "C-1004", "name": "Dev Kapoor", "tier": "Gold", "primary_order_id": "ORD-9004", "email": "dev@example.com"}'
+                            )
+                        ],
+                        isError=False
+                    )
+                    ),
+                    MCPToolCall(
+                        name='get_order_status',
+                        args={'order_id': 'ORD-9004'},
+                        result=CallToolResult(
+                        content=[
+                            TextContent(
+                                type="text",
+                                text='{"order_id": "ORD-9004", "customer_id": "C-1004", "status": "processing", "item": "Ergonomic keyboard", "amount": 89.0, "estimated_delivery": "2026-07-16", "issue": "Customer wants delivery expectations before travel."}'
+                            )
+                        ],
+                        isError=False
+                    )
+                    ),
+                    MCPToolCall(
+                        name='search_policy_docs',
+                        args={'query': 'shipping-status updates notification email tracking when order is processing'},
+                        result=CallToolResult(
+                        content=[
+                            TextContent(
+                                type="text",
+                                text='{"query": "shipping-status updates notification email tracking when order is processing", "matches": [{"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+                            )
+                        ],
+                        isError=False
+                    )
+                    ),
+                    MCPToolCall(
+                        name='search_policy_docs',
+                        args={'query': 'address change after order placed processing policy hold at carrier pickup reroute'},
+                        result=CallToolResult(
+                        content=[
+                            TextContent(
+                                type="text",
+                                text='{"query": "address change after order placed processing policy hold at carrier pickup reroute", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
+                            )
+                        ],
+                        isError=False
+                    )
+                    ),
+                    MCPToolCall(
+                        name='search_policy_docs',
+                        args={'query': 'expedited shipping request after order placed policy'},
+                        result=CallToolResult(
+                        content=[
+                            TextContent(
+                                type="text",
+                                text='{"query": "expedited shipping request after order placed policy", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
                             )
                         ],
                         isError=False
                     )
                     )
             ],
-        ),
-        Turn(
-            role="assistant",
-            content="The MCP tools returned the support data needed for the answer.",
-        ),
-        Turn(
-            role="assistant",
-            content='I checked order ORD-9010 for customer C-1004. The status is shipped, with an estimated delivery of 2026-07-15 for the Portable SSD. No further action is needed unless the package doesn’t arrive by the estimate—if that happens, let me know and I can assist with tracking or starting an investigation.',
         ),
     ],
     mcp_servers=[dummy_support_server],

--- a/Live_Dummy_MCP_Traces.xlsx
+++ b/Live_Dummy_MCP_Traces.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CASE-005-20260715190257</t>
+          <t>CASE-002-20260715201406</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -509,33 +509,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-15T19:02:57</t>
+          <t>2026-07-15T20:14:06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
+          <t>Customer C-1003 wants to know whether order ORD-9003 can be refunded.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
+          <t>Inspect ORD-9003, review refund policy, calculate eligibility, and explain that the order is outside the standard 30-day window.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+          <t>get_order_status,search_policy_docs,calculate_refund</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I checked Kabir Bose’s order ORD-9006. It’s delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18.
-I’ve opened a high-priority support ticket (T-1001) to expedite the shipment and ensure updates are sent to the customer. Next steps: we’ll push the warehouse team for faster transfer and send Kabir status updates until delivery.</t>
+          <t>Here’s what I found for order ORD-9003 (Smartwatch) for customer C-1003: it was delivered 42 days ago. Our refund policy allows most delivered items to be refunded within 30 days. Since this is beyond 30 days, it isn’t eligible for a standard refund.
+If the smartwatch arrived damaged or defective, we can submit it for a manual review even after 30 days. If that’s the case, please share a brief description of the issue and a few photos showing the problem, and I can open a high-priority ticket for you.
+Next best step: let me know if the item is damaged/defective and if you’d like me to create a review ticket. If not, I’m afraid we won’t be able to process a refund for this order.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+          <t>get_order_status,search_policy_docs</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -543,7 +544,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>get_customer_profile</t>
+          <t>get_order_status</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -553,9 +554,9 @@
   "id": 1,
   "method": "tools/call",
   "params": {
-    "name": "get_customer_profile",
+    "name": "get_order_status",
     "arguments": {
-      "customer_id": "C-1006"
+      "order_id": "ORD-9003"
     }
   }
 }</t>
@@ -570,15 +571,17 @@
     "content": [
       {
         "type": "text",
-        "text": "{\"customer_id\": \"C-1006\", \"name\": \"Kabir Bose\", \"tier\": \"Silver\", \"primary_order_id\": \"ORD-9006\", \"email\": \"kabir@example.com\"}"
+        "text": "{\"order_id\": \"ORD-9003\", \"customer_id\": \"C-1003\", \"status\": \"delivered\", \"item\": \"Smartwatch\", \"amount\": 149.0, \"delivered_days_ago\": 42, \"issue\": \"Customer asked about refund eligibility.\"}"
       }
     ],
     "structuredContent": {
-      "customer_id": "C-1006",
-      "name": "Kabir Bose",
-      "tier": "Silver",
-      "primary_order_id": "ORD-9006",
-      "email": "kabir@example.com"
+      "order_id": "ORD-9003",
+      "customer_id": "C-1003",
+      "status": "delivered",
+      "item": "Smartwatch",
+      "amount": 149.0,
+      "delivered_days_ago": 42,
+      "issue": "Customer asked about refund eligibility."
     },
     "isError": false
   }
@@ -588,18 +591,20 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>{
-  "customer_id": "C-1006"
+  "order_id": "ORD-9003"
 }</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>{
-  "customer_id": "C-1006",
-  "name": "Kabir Bose",
-  "tier": "Silver",
-  "primary_order_id": "ORD-9006",
-  "email": "kabir@example.com"
+  "order_id": "ORD-9003",
+  "customer_id": "C-1003",
+  "status": "delivered",
+  "item": "Smartwatch",
+  "amount": 149.0,
+  "delivered_days_ago": 42,
+  "issue": "Customer asked about refund eligibility."
 }</t>
         </is>
       </c>
@@ -612,7 +617,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CASE-005-20260715190257</t>
+          <t>CASE-002-20260715201406</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -622,33 +627,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-15T19:02:57</t>
+          <t>2026-07-15T20:14:06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
+          <t>Customer C-1003 wants to know whether order ORD-9003 can be refunded.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
+          <t>Inspect ORD-9003, review refund policy, calculate eligibility, and explain that the order is outside the standard 30-day window.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+          <t>get_order_status,search_policy_docs,calculate_refund</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I checked Kabir Bose’s order ORD-9006. It’s delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18.
-I’ve opened a high-priority support ticket (T-1001) to expedite the shipment and ensure updates are sent to the customer. Next steps: we’ll push the warehouse team for faster transfer and send Kabir status updates until delivery.</t>
+          <t>Here’s what I found for order ORD-9003 (Smartwatch) for customer C-1003: it was delivered 42 days ago. Our refund policy allows most delivered items to be refunded within 30 days. Since this is beyond 30 days, it isn’t eligible for a standard refund.
+If the smartwatch arrived damaged or defective, we can submit it for a manual review even after 30 days. If that’s the case, please share a brief description of the issue and a few photos showing the problem, and I can open a high-priority ticket for you.
+Next best step: let me know if the item is damaged/defective and if you’d like me to create a review ticket. If not, I’m afraid we won’t be able to process a refund for this order.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
+          <t>get_order_status,search_policy_docs</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -656,7 +662,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>get_order_status</t>
+          <t>search_policy_docs</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -666,9 +672,9 @@
   "id": 2,
   "method": "tools/call",
   "params": {
-    "name": "get_order_status",
+    "name": "search_policy_docs",
     "arguments": {
-      "order_id": "ORD-9006"
+      "query": "refund policy return window delivered days eligibility delivered_days_ago 42 smartwatch"
     }
   }
 }</t>
@@ -683,1250 +689,11 @@
     "content": [
       {
         "type": "text",
-        "text": "{\"order_id\": \"ORD-9006\", \"customer_id\": \"C-1006\", \"status\": \"delayed\", \"item\": \"Office chair\", \"amount\": 249.0, \"delay_reason\": \"Inventory transfer from another warehouse.\", \"estimated_delivery\": \"2026-07-18\"}"
+        "text": "{\"query\": \"refund policy return window delivered days eligibility delivered_days_ago 42 smartwatch\", \"matches\": [{\"policy_id\": \"refund\", \"title\": \"Refund policy\", \"summary\": \"Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review.\"}, {\"policy_id\": \"delivery\", \"title\": \"Delivery delay policy\", \"summary\": \"If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days.\"}, {\"policy_id\": \"damaged_item\", \"title\": \"Damaged item policy\", \"summary\": \"Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases.\"}, {\"policy_id\": \"cancellation\", \"title\": \"Cancellation policy\", \"summary\": \"Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails.\"}, {\"policy_id\": \"shipping_status\", \"title\": \"Shipping status policy\", \"summary\": \"For shipped or processing orders, share the current status and estimated delivery date when available.\"}]}"
       }
     ],
     "structuredContent": {
-      "order_id": "ORD-9006",
-      "customer_id": "C-1006",
-      "status": "delayed",
-      "item": "Office chair",
-      "amount": 249.0,
-      "delay_reason": "Inventory transfer from another warehouse.",
-      "estimated_delivery": "2026-07-18"
-    },
-    "isError": false
-  }
-}</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9006"
-}</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9006",
-  "customer_id": "C-1006",
-  "status": "delayed",
-  "item": "Office chair",
-  "amount": 249.0,
-  "delay_reason": "Inventory transfer from another warehouse.",
-  "estimated_delivery": "2026-07-18"
-}</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CASE-005-20260715190257</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-07-15T19:02:57</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>I checked Kabir Bose’s order ORD-9006. It’s delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18.
-I’ve opened a high-priority support ticket (T-1001) to expedite the shipment and ensure updates are sent to the customer. Next steps: we’ll push the warehouse team for faster transfer and send Kabir status updates until delivery.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>create_support_ticket</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 3,
-  "method": "tools/call",
-  "params": {
-    "name": "create_support_ticket",
-    "arguments": {
-      "customer_id": "C-1006",
-      "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.",
-      "priority": "high"
-    }
-  }
-}</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 3,
-  "result": {
-    "content": [
-      {
-        "type": "text",
-        "text": "{\"ticket_id\": \"T-1001\", \"customer_id\": \"C-1006\", \"issue_summary\": \"Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.\", \"priority\": \"high\", \"status\": \"open\", \"created_at\": \"2026-07-15T19:03:09\"}"
-      }
-    ],
-    "structuredContent": {
-      "ticket_id": "T-1001",
-      "customer_id": "C-1006",
-      "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.",
-      "priority": "high",
-      "status": "open",
-      "created_at": "2026-07-15T19:03:09"
-    },
-    "isError": false
-  }
-}</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1006",
-  "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.",
-  "priority": "high"
-}</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>{
-  "ticket_id": "T-1001",
-  "customer_id": "C-1006",
-  "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.",
-  "priority": "high",
-  "status": "open",
-  "created_at": "2026-07-15T19:03:09"
-}</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CUSTOM-20260715191112</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-07-15T19:11:12</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Customer C-1006 is asking about his deliveries</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>User-created chatbot case. Review actual output and tool calls against the requested support task.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Here’s what I found for Kabir Bose (C-1006): his current order ORD-9006 (office chair) is delayed due to an inventory transfer from another warehouse. The updated estimated delivery date is 2026-07-18.
-Next steps: I’ll keep an eye on this and can send him an update to kabir@example.com. If it doesn’t ship or arrive by the 18th, we can escalate or discuss options (wait, cancel, or refund). Would you like me to set up notifications or check if he has any other active orders?</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>get_customer_profile</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 1,
-  "method": "tools/call",
-  "params": {
-    "name": "get_customer_profile",
-    "arguments": {
-      "customer_id": "C-1006"
-    }
-  }
-}</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 1,
-  "result": {
-    "content": [
-      {
-        "type": "text",
-        "text": "{\"customer_id\": \"C-1006\", \"name\": \"Kabir Bose\", \"tier\": \"Silver\", \"primary_order_id\": \"ORD-9006\", \"email\": \"kabir@example.com\"}"
-      }
-    ],
-    "structuredContent": {
-      "customer_id": "C-1006",
-      "name": "Kabir Bose",
-      "tier": "Silver",
-      "primary_order_id": "ORD-9006",
-      "email": "kabir@example.com"
-    },
-    "isError": false
-  }
-}</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1006"
-}</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1006",
-  "name": "Kabir Bose",
-  "tier": "Silver",
-  "primary_order_id": "ORD-9006",
-  "email": "kabir@example.com"
-}</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CUSTOM-20260715191112</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-07-15T19:11:12</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Customer C-1006 is asking about his deliveries</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>User-created chatbot case. Review actual output and tool calls against the requested support task.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Here’s what I found for Kabir Bose (C-1006): his current order ORD-9006 (office chair) is delayed due to an inventory transfer from another warehouse. The updated estimated delivery date is 2026-07-18.
-Next steps: I’ll keep an eye on this and can send him an update to kabir@example.com. If it doesn’t ship or arrive by the 18th, we can escalate or discuss options (wait, cancel, or refund). Would you like me to set up notifications or check if he has any other active orders?</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>get_order_status</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 2,
-  "method": "tools/call",
-  "params": {
-    "name": "get_order_status",
-    "arguments": {
-      "order_id": "ORD-9006"
-    }
-  }
-}</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 2,
-  "result": {
-    "content": [
-      {
-        "type": "text",
-        "text": "{\"order_id\": \"ORD-9006\", \"customer_id\": \"C-1006\", \"status\": \"delayed\", \"item\": \"Office chair\", \"amount\": 249.0, \"delay_reason\": \"Inventory transfer from another warehouse.\", \"estimated_delivery\": \"2026-07-18\"}"
-      }
-    ],
-    "structuredContent": {
-      "order_id": "ORD-9006",
-      "customer_id": "C-1006",
-      "status": "delayed",
-      "item": "Office chair",
-      "amount": 249.0,
-      "delay_reason": "Inventory transfer from another warehouse.",
-      "estimated_delivery": "2026-07-18"
-    },
-    "isError": false
-  }
-}</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9006"
-}</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9006",
-  "customer_id": "C-1006",
-  "status": "delayed",
-  "item": "Office chair",
-  "amount": 249.0,
-  "delay_reason": "Inventory transfer from another warehouse.",
-  "estimated_delivery": "2026-07-18"
-}</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CASE-005-20260715192952</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-07-15T19:29:52</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Here’s what I found and what I’ve done:
-- Order and status: ORD-9006 for an office chair is currently delayed.
-- Reason for delay: Inventory transfer from another warehouse.
-- Current estimated delivery: 2026-07-18.
-- Customer profile: Kabir Bose (Silver), email kabir@example.com.
-Ticket opened:
-- Ticket ID: T-1001
-- Priority: High
-- Status: Open
-- Summary: Escalated the delay for ORD-9006; requested checks on expediting or alternative fulfillment and set up proactive updates to kabir@example.com.
-Next steps:
-- We’ll monitor the shipment and send updates if anything changes.
-- If you prefer a different contact method or want us to explore switching to an in-stock alternative, expediting options, or other arrangements, let me know your preference.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>get_customer_profile</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 1,
-  "method": "tools/call",
-  "params": {
-    "name": "get_customer_profile",
-    "arguments": {
-      "customer_id": "C-1006"
-    }
-  }
-}</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 1,
-  "result": {
-    "content": [
-      {
-        "type": "text",
-        "text": "{\"customer_id\": \"C-1006\", \"name\": \"Kabir Bose\", \"tier\": \"Silver\", \"primary_order_id\": \"ORD-9006\", \"email\": \"kabir@example.com\"}"
-      }
-    ],
-    "structuredContent": {
-      "customer_id": "C-1006",
-      "name": "Kabir Bose",
-      "tier": "Silver",
-      "primary_order_id": "ORD-9006",
-      "email": "kabir@example.com"
-    },
-    "isError": false
-  }
-}</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1006"
-}</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1006",
-  "name": "Kabir Bose",
-  "tier": "Silver",
-  "primary_order_id": "ORD-9006",
-  "email": "kabir@example.com"
-}</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CASE-005-20260715192952</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-07-15T19:29:52</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Here’s what I found and what I’ve done:
-- Order and status: ORD-9006 for an office chair is currently delayed.
-- Reason for delay: Inventory transfer from another warehouse.
-- Current estimated delivery: 2026-07-18.
-- Customer profile: Kabir Bose (Silver), email kabir@example.com.
-Ticket opened:
-- Ticket ID: T-1001
-- Priority: High
-- Status: Open
-- Summary: Escalated the delay for ORD-9006; requested checks on expediting or alternative fulfillment and set up proactive updates to kabir@example.com.
-Next steps:
-- We’ll monitor the shipment and send updates if anything changes.
-- If you prefer a different contact method or want us to explore switching to an in-stock alternative, expediting options, or other arrangements, let me know your preference.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>get_order_status</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 2,
-  "method": "tools/call",
-  "params": {
-    "name": "get_order_status",
-    "arguments": {
-      "order_id": "ORD-9006"
-    }
-  }
-}</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 2,
-  "result": {
-    "content": [
-      {
-        "type": "text",
-        "text": "{\"order_id\": \"ORD-9006\", \"customer_id\": \"C-1006\", \"status\": \"delayed\", \"item\": \"Office chair\", \"amount\": 249.0, \"delay_reason\": \"Inventory transfer from another warehouse.\", \"estimated_delivery\": \"2026-07-18\"}"
-      }
-    ],
-    "structuredContent": {
-      "order_id": "ORD-9006",
-      "customer_id": "C-1006",
-      "status": "delayed",
-      "item": "Office chair",
-      "amount": 249.0,
-      "delay_reason": "Inventory transfer from another warehouse.",
-      "estimated_delivery": "2026-07-18"
-    },
-    "isError": false
-  }
-}</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9006"
-}</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9006",
-  "customer_id": "C-1006",
-  "status": "delayed",
-  "item": "Office chair",
-  "amount": 249.0,
-  "delay_reason": "Inventory transfer from another warehouse.",
-  "estimated_delivery": "2026-07-18"
-}</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CASE-005-20260715192952</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-07-15T19:29:52</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Here’s what I found and what I’ve done:
-- Order and status: ORD-9006 for an office chair is currently delayed.
-- Reason for delay: Inventory transfer from another warehouse.
-- Current estimated delivery: 2026-07-18.
-- Customer profile: Kabir Bose (Silver), email kabir@example.com.
-Ticket opened:
-- Ticket ID: T-1001
-- Priority: High
-- Status: Open
-- Summary: Escalated the delay for ORD-9006; requested checks on expediting or alternative fulfillment and set up proactive updates to kabir@example.com.
-Next steps:
-- We’ll monitor the shipment and send updates if anything changes.
-- If you prefer a different contact method or want us to explore switching to an in-stock alternative, expediting options, or other arrangements, let me know your preference.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,create_support_ticket</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>create_support_ticket</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 3,
-  "method": "tools/call",
-  "params": {
-    "name": "create_support_ticket",
-    "arguments": {
-      "customer_id": "C-1006",
-      "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.",
-      "priority": "high"
-    }
-  }
-}</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 3,
-  "result": {
-    "content": [
-      {
-        "type": "text",
-        "text": "{\"ticket_id\": \"T-1001\", \"customer_id\": \"C-1006\", \"issue_summary\": \"Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.\", \"priority\": \"high\", \"status\": \"open\", \"created_at\": \"2026-07-15T19:30:16\"}"
-      }
-    ],
-    "structuredContent": {
-      "ticket_id": "T-1001",
-      "customer_id": "C-1006",
-      "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.",
-      "priority": "high",
-      "status": "open",
-      "created_at": "2026-07-15T19:30:16"
-    },
-    "isError": false
-  }
-}</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1006",
-  "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.",
-  "priority": "high"
-}</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>{
-  "ticket_id": "T-1001",
-  "customer_id": "C-1006",
-  "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.",
-  "priority": "high",
-  "status": "open",
-  "created_at": "2026-07-15T19:30:16"
-}</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CASE-008-20260715193141</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-07-15T19:31:41</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Look up C-1004, inspect ORD-9004, and share the processing status with estimated delivery.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Here’s what I see for your order:
-- Customer: Dev Kapoor (C-1004)
-- Order: ORD-9004 — Ergonomic keyboard
-- Status: Processing
-- Estimated delivery date: 2026-07-16
-Policy reference: For processing orders, we share the current status and the estimated delivery date when available.
-Recommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,search_policy_docs,search_policy_docs,search_policy_docs</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>get_customer_profile</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 1,
-  "method": "tools/call",
-  "params": {
-    "name": "get_customer_profile",
-    "arguments": {
-      "customer_id": "C-1004"
-    }
-  }
-}</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 1,
-  "result": {
-    "content": [
-      {
-        "type": "text",
-        "text": "{\"customer_id\": \"C-1004\", \"name\": \"Dev Kapoor\", \"tier\": \"Gold\", \"primary_order_id\": \"ORD-9004\", \"email\": \"dev@example.com\"}"
-      }
-    ],
-    "structuredContent": {
-      "customer_id": "C-1004",
-      "name": "Dev Kapoor",
-      "tier": "Gold",
-      "primary_order_id": "ORD-9004",
-      "email": "dev@example.com"
-    },
-    "isError": false
-  }
-}</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1004"
-}</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>{
-  "customer_id": "C-1004",
-  "name": "Dev Kapoor",
-  "tier": "Gold",
-  "primary_order_id": "ORD-9004",
-  "email": "dev@example.com"
-}</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CASE-008-20260715193141</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-07-15T19:31:41</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Look up C-1004, inspect ORD-9004, and share the processing status with estimated delivery.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Here’s what I see for your order:
-- Customer: Dev Kapoor (C-1004)
-- Order: ORD-9004 — Ergonomic keyboard
-- Status: Processing
-- Estimated delivery date: 2026-07-16
-Policy reference: For processing orders, we share the current status and the estimated delivery date when available.
-Recommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,search_policy_docs,search_policy_docs,search_policy_docs</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>get_order_status</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 2,
-  "method": "tools/call",
-  "params": {
-    "name": "get_order_status",
-    "arguments": {
-      "order_id": "ORD-9004"
-    }
-  }
-}</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 2,
-  "result": {
-    "content": [
-      {
-        "type": "text",
-        "text": "{\"order_id\": \"ORD-9004\", \"customer_id\": \"C-1004\", \"status\": \"processing\", \"item\": \"Ergonomic keyboard\", \"amount\": 89.0, \"estimated_delivery\": \"2026-07-16\", \"issue\": \"Customer wants delivery expectations before travel.\"}"
-      }
-    ],
-    "structuredContent": {
-      "order_id": "ORD-9004",
-      "customer_id": "C-1004",
-      "status": "processing",
-      "item": "Ergonomic keyboard",
-      "amount": 89.0,
-      "estimated_delivery": "2026-07-16",
-      "issue": "Customer wants delivery expectations before travel."
-    },
-    "isError": false
-  }
-}</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9004"
-}</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>{
-  "order_id": "ORD-9004",
-  "customer_id": "C-1004",
-  "status": "processing",
-  "item": "Ergonomic keyboard",
-  "amount": 89.0,
-  "estimated_delivery": "2026-07-16",
-  "issue": "Customer wants delivery expectations before travel."
-}</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CASE-008-20260715193141</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-07-15T19:31:41</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Look up C-1004, inspect ORD-9004, and share the processing status with estimated delivery.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Here’s what I see for your order:
-- Customer: Dev Kapoor (C-1004)
-- Order: ORD-9004 — Ergonomic keyboard
-- Status: Processing
-- Estimated delivery date: 2026-07-16
-Policy reference: For processing orders, we share the current status and the estimated delivery date when available.
-Recommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,search_policy_docs,search_policy_docs,search_policy_docs</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>search_policy_docs</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 3,
-  "method": "tools/call",
-  "params": {
-    "name": "search_policy_docs",
-    "arguments": {
-      "query": "shipping-status updates notification email tracking when order is processing"
-    }
-  }
-}</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 3,
-  "result": {
-    "content": [
-      {
-        "type": "text",
-        "text": "{\"query\": \"shipping-status updates notification email tracking when order is processing\", \"matches\": [{\"policy_id\": \"delivery\", \"title\": \"Delivery delay policy\", \"summary\": \"If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days.\"}, {\"policy_id\": \"damaged_item\", \"title\": \"Damaged item policy\", \"summary\": \"Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases.\"}, {\"policy_id\": \"cancellation\", \"title\": \"Cancellation policy\", \"summary\": \"Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails.\"}, {\"policy_id\": \"shipping_status\", \"title\": \"Shipping status policy\", \"summary\": \"For shipped or processing orders, share the current status and estimated delivery date when available.\"}]}"
-      }
-    ],
-    "structuredContent": {
-      "query": "shipping-status updates notification email tracking when order is processing",
-      "matches": [
-        {
-          "policy_id": "delivery",
-          "title": "Delivery delay policy",
-          "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."
-        },
-        {
-          "policy_id": "damaged_item",
-          "title": "Damaged item policy",
-          "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."
-        },
-        {
-          "policy_id": "cancellation",
-          "title": "Cancellation policy",
-          "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."
-        },
-        {
-          "policy_id": "shipping_status",
-          "title": "Shipping status policy",
-          "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."
-        }
-      ]
-    },
-    "isError": false
-  }
-}</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>{
-  "query": "shipping-status updates notification email tracking when order is processing"
-}</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>{
-  "query": "shipping-status updates notification email tracking when order is processing",
-  "matches": [
-    {
-      "policy_id": "delivery",
-      "title": "Delivery delay policy",
-      "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."
-    },
-    {
-      "policy_id": "damaged_item",
-      "title": "Damaged item policy",
-      "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."
-    },
-    {
-      "policy_id": "cancellation",
-      "title": "Cancellation policy",
-      "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."
-    },
-    {
-      "policy_id": "shipping_status",
-      "title": "Shipping status policy",
-      "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CASE-008-20260715193141</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>single_turn</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-07-15T19:31:41</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Look up C-1004, inspect ORD-9004, and share the processing status with estimated delivery.</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Here’s what I see for your order:
-- Customer: Dev Kapoor (C-1004)
-- Order: ORD-9004 — Ergonomic keyboard
-- Status: Processing
-- Estimated delivery date: 2026-07-16
-Policy reference: For processing orders, we share the current status and the estimated delivery date when available.
-Recommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,search_policy_docs,search_policy_docs,search_policy_docs</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>search_policy_docs</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 4,
-  "method": "tools/call",
-  "params": {
-    "name": "search_policy_docs",
-    "arguments": {
-      "query": "address change after order placed processing policy hold at carrier pickup reroute"
-    }
-  }
-}</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>{
-  "jsonrpc": "2.0",
-  "id": 4,
-  "result": {
-    "content": [
-      {
-        "type": "text",
-        "text": "{\"query\": \"address change after order placed processing policy hold at carrier pickup reroute\", \"matches\": [{\"policy_id\": \"refund\", \"title\": \"Refund policy\", \"summary\": \"Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review.\"}, {\"policy_id\": \"delivery\", \"title\": \"Delivery delay policy\", \"summary\": \"If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days.\"}, {\"policy_id\": \"damaged_item\", \"title\": \"Damaged item policy\", \"summary\": \"Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases.\"}, {\"policy_id\": \"cancellation\", \"title\": \"Cancellation policy\", \"summary\": \"Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails.\"}, {\"policy_id\": \"shipping_status\", \"title\": \"Shipping status policy\", \"summary\": \"For shipped or processing orders, share the current status and estimated delivery date when available.\"}]}"
-      }
-    ],
-    "structuredContent": {
-      "query": "address change after order placed processing policy hold at carrier pickup reroute",
+      "query": "refund policy return window delivered days eligibility delivered_days_ago 42 smartwatch",
       "matches": [
         {
           "policy_id": "refund",
@@ -1960,17 +727,17 @@
 }</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>{
-  "query": "address change after order placed processing policy hold at carrier pickup reroute"
-}</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>{
-  "query": "address change after order placed processing policy hold at carrier pickup reroute",
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>{
+  "query": "refund policy return window delivered days eligibility delivered_days_ago 42 smartwatch"
+}</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>{
+  "query": "refund policy return window delivered days eligibility delivered_days_ago 42 smartwatch",
   "matches": [
     {
       "policy_id": "refund",
@@ -2001,171 +768,237 @@
 }</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CASE-008-20260715193141</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CASE-008-20260715201443</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>single_turn</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-07-15T19:31:41</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-15T20:14:43</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Look up C-1004, inspect ORD-9004, and share the processing status with estimated delivery.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>get_customer_profile,get_order_status</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Here’s what I see for your order:
-- Customer: Dev Kapoor (C-1004)
-- Order: ORD-9004 — Ergonomic keyboard
-- Status: Processing
-- Estimated delivery date: 2026-07-16
-Policy reference: For processing orders, we share the current status and the estimated delivery date when available.
-Recommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>get_customer_profile,get_order_status,search_policy_docs,search_policy_docs,search_policy_docs</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>search_policy_docs</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I checked your order. The ergonomic keyboard (order ORD-9004) is currently processing and is estimated to be delivered on 2026-07-16.
+If that timing conflicts with your travel, I can look into available options (such as updating the delivery address or arranging a carrier hold, if eligible). Next best step: let me know your departure date and whether you want me to check delivery-change options or create a support ticket on your behalf.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>get_customer_profile</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>{
   "jsonrpc": "2.0",
-  "id": 5,
+  "id": 1,
   "method": "tools/call",
   "params": {
-    "name": "search_policy_docs",
+    "name": "get_customer_profile",
     "arguments": {
-      "query": "expedited shipping request after order placed policy"
+      "customer_id": "C-1004"
     }
   }
 }</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>{
   "jsonrpc": "2.0",
-  "id": 5,
+  "id": 1,
   "result": {
     "content": [
       {
         "type": "text",
-        "text": "{\"query\": \"expedited shipping request after order placed policy\", \"matches\": [{\"policy_id\": \"refund\", \"title\": \"Refund policy\", \"summary\": \"Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review.\"}, {\"policy_id\": \"delivery\", \"title\": \"Delivery delay policy\", \"summary\": \"If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days.\"}, {\"policy_id\": \"damaged_item\", \"title\": \"Damaged item policy\", \"summary\": \"Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases.\"}, {\"policy_id\": \"cancellation\", \"title\": \"Cancellation policy\", \"summary\": \"Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails.\"}, {\"policy_id\": \"shipping_status\", \"title\": \"Shipping status policy\", \"summary\": \"For shipped or processing orders, share the current status and estimated delivery date when available.\"}]}"
+        "text": "{\"customer_id\": \"C-1004\", \"name\": \"Dev Kapoor\", \"tier\": \"Gold\", \"primary_order_id\": \"ORD-9004\", \"email\": \"dev@example.com\"}"
       }
     ],
     "structuredContent": {
-      "query": "expedited shipping request after order placed policy",
-      "matches": [
-        {
-          "policy_id": "refund",
-          "title": "Refund policy",
-          "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."
-        },
-        {
-          "policy_id": "delivery",
-          "title": "Delivery delay policy",
-          "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."
-        },
-        {
-          "policy_id": "damaged_item",
-          "title": "Damaged item policy",
-          "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."
-        },
-        {
-          "policy_id": "cancellation",
-          "title": "Cancellation policy",
-          "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."
-        },
-        {
-          "policy_id": "shipping_status",
-          "title": "Shipping status policy",
-          "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."
-        }
-      ]
+      "customer_id": "C-1004",
+      "name": "Dev Kapoor",
+      "tier": "Gold",
+      "primary_order_id": "ORD-9004",
+      "email": "dev@example.com"
     },
     "isError": false
   }
 }</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>{
-  "query": "expedited shipping request after order placed policy"
-}</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>{
-  "query": "expedited shipping request after order placed policy",
-  "matches": [
-    {
-      "policy_id": "refund",
-      "title": "Refund policy",
-      "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1004"
+}</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>{
+  "customer_id": "C-1004",
+  "name": "Dev Kapoor",
+  "tier": "Gold",
+  "primary_order_id": "ORD-9004",
+  "email": "dev@example.com"
+}</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CASE-008-20260715201443</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>single_turn</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-15T20:14:43</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Look up C-1004, inspect ORD-9004, and share the processing status with estimated delivery.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I checked your order. The ergonomic keyboard (order ORD-9004) is currently processing and is estimated to be delivered on 2026-07-16.
+If that timing conflicts with your travel, I can look into available options (such as updating the delivery address or arranging a carrier hold, if eligible). Next best step: let me know your departure date and whether you want me to check delivery-change options or create a support ticket on your behalf.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>get_customer_profile,get_order_status</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>get_order_status</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 2,
+  "method": "tools/call",
+  "params": {
+    "name": "get_order_status",
+    "arguments": {
+      "order_id": "ORD-9004"
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>{
+  "jsonrpc": "2.0",
+  "id": 2,
+  "result": {
+    "content": [
+      {
+        "type": "text",
+        "text": "{\"order_id\": \"ORD-9004\", \"customer_id\": \"C-1004\", \"status\": \"processing\", \"item\": \"Ergonomic keyboard\", \"amount\": 89.0, \"estimated_delivery\": \"2026-07-16\", \"issue\": \"Customer wants delivery expectations before travel.\"}"
+      }
+    ],
+    "structuredContent": {
+      "order_id": "ORD-9004",
+      "customer_id": "C-1004",
+      "status": "processing",
+      "item": "Ergonomic keyboard",
+      "amount": 89.0,
+      "estimated_delivery": "2026-07-16",
+      "issue": "Customer wants delivery expectations before travel."
     },
-    {
-      "policy_id": "delivery",
-      "title": "Delivery delay policy",
-      "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."
-    },
-    {
-      "policy_id": "damaged_item",
-      "title": "Damaged item policy",
-      "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."
-    },
-    {
-      "policy_id": "cancellation",
-      "title": "Cancellation policy",
-      "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."
-    },
-    {
-      "policy_id": "shipping_status",
-      "title": "Shipping status policy",
-      "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+    "isError": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9004"
+}</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>{
+  "order_id": "ORD-9004",
+  "customer_id": "C-1004",
+  "status": "processing",
+  "item": "Ergonomic keyboard",
+  "amount": 89.0,
+  "estimated_delivery": "2026-07-16",
+  "issue": "Customer wants delivery expectations before travel."
+}</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
@@ -2423,7 +1256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,7 +1289,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CASE-005-20260715190257</t>
+          <t>CASE-002-20260715201406</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2497,39 +1330,26 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>MCPToolCall(
-    name='get_customer_profile',
-    args={'customer_id': 'C-1006'},
+    name='get_order_status',
+    args={'order_id': 'ORD-9003'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
+            text='{"order_id": "ORD-9003", "customer_id": "C-1003", "status": "delivered", "item": "Smartwatch", "amount": 149.0, "delivered_days_ago": 42, "issue": "Customer asked about refund eligibility."}'
         )
     ],
     isError=False
 )
 )
 MCPToolCall(
-    name='get_order_status',
-    args={'order_id': 'ORD-9006'},
+    name='search_policy_docs',
+    args={'query': 'refund policy return window delivered days eligibility delivered_days_ago 42 smartwatch'},
     result=CallToolResult(
     content=[
         TextContent(
             type="text",
-            text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
-        )
-    ],
-    isError=False
-)
-)
-MCPToolCall(
-    name='create_support_ticket',
-    args={'customer_id': 'C-1006', 'issue_summary': 'Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.', 'priority': 'high'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.", "priority": "high", "status": "open", "created_at": "2026-07-15T19:03:09"}'
+            text='{"query": "refund policy return window delivered days eligibility delivered_days_ago 42 smartwatch", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
         )
     ],
     isError=False
@@ -2540,45 +1360,32 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>LLMTestCase(
-    input='Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.',
-    actual_output='I checked Kabir Bose’s order ORD-9006. It’s delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18.\n\nI’ve opened a high-priority support ticket (T-1001) to expedite the shipment and ensure updates are sent to the customer. Next steps: we’ll push the warehouse team for faster transfer and send Kabir status updates until delivery.',
-    expected_output='Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.',
+    input='Customer C-1003 wants to know whether order ORD-9003 can be refunded.',
+    actual_output='Here’s what I found for order ORD-9003 (Smartwatch) for customer C-1003: it was delivered 42 days ago. Our refund policy allows most delivered items to be refunded within 30 days. Since this is beyond 30 days, it isn’t eligible for a standard refund.\n\nIf the smartwatch arrived damaged or defective, we can submit it for a manual review even after 30 days. If that’s the case, please share a brief description of the issue and a few photos showing the problem, and I can open a high-priority ticket for you.\n\nNext best step: let me know if the item is damaged/defective and if you’d like me to create a review ticket. If not, I’m afraid we won’t be able to process a refund for this order.',
+    expected_output='Inspect ORD-9003, review refund policy, calculate eligibility, and explain that the order is outside the standard 30-day window.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
         MCPToolCall(
-            name='get_customer_profile',
-            args={'customer_id': 'C-1006'},
+            name='get_order_status',
+            args={'order_id': 'ORD-9003'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
+                    text='{"order_id": "ORD-9003", "customer_id": "C-1003", "status": "delivered", "item": "Smartwatch", "amount": 149.0, "delivered_days_ago": 42, "issue": "Customer asked about refund eligibility."}'
                 )
             ],
             isError=False
         )
         ),
         MCPToolCall(
-            name='get_order_status',
-            args={'order_id': 'ORD-9006'},
+            name='search_policy_docs',
+            args={'query': 'refund policy return window delivered days eligibility delivered_days_ago 42 smartwatch'},
             result=CallToolResult(
             content=[
                 TextContent(
                     type="text",
-                    text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
-                )
-            ],
-            isError=False
-        )
-        ),
-        MCPToolCall(
-            name='create_support_ticket',
-            args={'customer_id': 'C-1006', 'issue_summary': 'Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.', 'priority': 'high'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.", "priority": "high", "status": "open", "created_at": "2026-07-15T19:03:09"}'
+                    text='{"query": "refund policy return window delivered days eligibility delivered_days_ago 42 smartwatch", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
                 )
             ],
             isError=False
@@ -2592,45 +1399,32 @@
         <is>
           <t>ConversationalTestCase(
     turns=[
-        Turn(role="user", content='Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.'),
+        Turn(role="user", content='Customer C-1003 wants to know whether order ORD-9003 can be refunded.'),
         Turn(
             role="assistant",
-            content='I checked Kabir Bose’s order ORD-9006. It’s delayed due to an inventory transfer from another warehouse, with an estimated delivery of 2026-07-18.\n\nI’ve opened a high-priority support ticket (T-1001) to expedite the shipment and ensure updates are sent to the customer. Next steps: we’ll push the warehouse team for faster transfer and send Kabir status updates until delivery.',
+            content='Here’s what I found for order ORD-9003 (Smartwatch) for customer C-1003: it was delivered 42 days ago. Our refund policy allows most delivered items to be refunded within 30 days. Since this is beyond 30 days, it isn’t eligible for a standard refund.\n\nIf the smartwatch arrived damaged or defective, we can submit it for a manual review even after 30 days. If that’s the case, please share a brief description of the issue and a few photos showing the problem, and I can open a high-priority ticket for you.\n\nNext best step: let me know if the item is damaged/defective and if you’d like me to create a review ticket. If not, I’m afraid we won’t be able to process a refund for this order.',
             mcp_tools_called=[
                     MCPToolCall(
-                        name='get_customer_profile',
-                        args={'customer_id': 'C-1006'},
+                        name='get_order_status',
+                        args={'order_id': 'ORD-9003'},
                         result=CallToolResult(
                         content=[
                             TextContent(
                                 type="text",
-                                text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
+                                text='{"order_id": "ORD-9003", "customer_id": "C-1003", "status": "delivered", "item": "Smartwatch", "amount": 149.0, "delivered_days_ago": 42, "issue": "Customer asked about refund eligibility."}'
                             )
                         ],
                         isError=False
                     )
                     ),
                     MCPToolCall(
-                        name='get_order_status',
-                        args={'order_id': 'ORD-9006'},
+                        name='search_policy_docs',
+                        args={'query': 'refund policy return window delivered days eligibility delivered_days_ago 42 smartwatch'},
                         result=CallToolResult(
                         content=[
                             TextContent(
                                 type="text",
-                                text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
-                            )
-                        ],
-                        isError=False
-                    )
-                    ),
-                    MCPToolCall(
-                        name='create_support_ticket',
-                        args={'customer_id': 'C-1006', 'issue_summary': 'Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.', 'priority': 'high'},
-                        result=CallToolResult(
-                        content=[
-                            TextContent(
-                                type="text",
-                                text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Order ORD-9006 delayed (office chair). Delay due to inventory transfer from another warehouse. Customer upset; expedite and keep customer updated.", "priority": "high", "status": "open", "created_at": "2026-07-15T19:03:09"}'
+                                text='{"query": "refund policy return window delivered days eligibility delivered_days_ago 42 smartwatch", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
                             )
                         ],
                         isError=False
@@ -2638,6 +1432,8 @@
                     )
             ],
         ),
+        Turn(role="user", content='Thank you.'),
+        Turn(role="assistant", content='You are welcome. I hope the information provided was helpful.'),
     ],
     mcp_servers=[dummy_support_server],
 )</t>
@@ -2647,7 +1443,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CUSTOM-20260715191112</t>
+          <t>CASE-008-20260715201443</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2689,349 +1485,6 @@
         <is>
           <t>MCPToolCall(
     name='get_customer_profile',
-    args={'customer_id': 'C-1006'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
-        )
-    ],
-    isError=False
-)
-)
-MCPToolCall(
-    name='get_order_status',
-    args={'order_id': 'ORD-9006'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
-        )
-    ],
-    isError=False
-)
-)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LLMTestCase(
-    input='Customer C-1006 is asking about his deliveries',
-    actual_output='Here’s what I found for Kabir Bose (C-1006): his current order ORD-9006 (office chair) is delayed due to an inventory transfer from another warehouse. The updated estimated delivery date is 2026-07-18.\n\nNext steps: I’ll keep an eye on this and can send him an update to kabir@example.com. If it doesn’t ship or arrive by the 18th, we can escalate or discuss options (wait, cancel, or refund). Would you like me to set up notifications or check if he has any other active orders?',
-    expected_output='User-created chatbot case. Review actual output and tool calls against the requested support task.',
-    mcp_servers=[dummy_support_server],
-    mcp_tools_called=[
-        MCPToolCall(
-            name='get_customer_profile',
-            args={'customer_id': 'C-1006'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
-                )
-            ],
-            isError=False
-        )
-        ),
-        MCPToolCall(
-            name='get_order_status',
-            args={'order_id': 'ORD-9006'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
-                )
-            ],
-            isError=False
-        )
-        )
-    ],
-)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ConversationalTestCase(
-    turns=[
-        Turn(role="user", content='Customer C-1006 is asking about his deliveries'),
-        Turn(
-            role="assistant",
-            content='Here’s what I found for Kabir Bose (C-1006): his current order ORD-9006 (office chair) is delayed due to an inventory transfer from another warehouse. The updated estimated delivery date is 2026-07-18.\n\nNext steps: I’ll keep an eye on this and can send him an update to kabir@example.com. If it doesn’t ship or arrive by the 18th, we can escalate or discuss options (wait, cancel, or refund). Would you like me to set up notifications or check if he has any other active orders?',
-            mcp_tools_called=[
-                    MCPToolCall(
-                        name='get_customer_profile',
-                        args={'customer_id': 'C-1006'},
-                        result=CallToolResult(
-                        content=[
-                            TextContent(
-                                type="text",
-                                text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
-                            )
-                        ],
-                        isError=False
-                    )
-                    ),
-                    MCPToolCall(
-                        name='get_order_status',
-                        args={'order_id': 'ORD-9006'},
-                        result=CallToolResult(
-                        content=[
-                            TextContent(
-                                type="text",
-                                text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
-                            )
-                        ],
-                        isError=False
-                    )
-                    )
-            ],
-        ),
-    ],
-    mcp_servers=[dummy_support_server],
-)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CASE-005-20260715192952</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>dummy_support_server = MCPServer(
-    server_name="dummy_support",
-    transport="streamable-http",
-    available_tools=[
-        Tool(
-            name='get_customer_profile',
-            description='Get a customer profile by customer ID.',
-            inputSchema={'type': 'object', 'properties': {'customer_id': {'type': 'string', 'description': 'Customer ID such as C-1002.'}}, 'required': ['customer_id'], 'additionalProperties': False},
-        ),
-        Tool(
-            name='get_order_status',
-            description='Get order status and order details by order ID.',
-            inputSchema={'type': 'object', 'properties': {'order_id': {'type': 'string', 'description': 'Order ID such as ORD-9002.'}}, 'required': ['order_id'], 'additionalProperties': False},
-        ),
-        Tool(
-            name='search_policy_docs',
-            description='Search support policy documents.',
-            inputSchema={'type': 'object', 'properties': {'query': {'type': 'string', 'description': 'Policy search query.'}}, 'required': ['query'], 'additionalProperties': False},
-        ),
-        Tool(
-            name='calculate_refund',
-            description='Calculate refund eligibility for an order.',
-            inputSchema={'type': 'object', 'properties': {'order_id': {'type': 'string'}, 'reason': {'type': 'string'}}, 'required': ['order_id', 'reason'], 'additionalProperties': False},
-        ),
-        Tool(
-            name='create_support_ticket',
-            description='Create a support ticket for a customer issue.',
-            inputSchema={'type': 'object', 'properties': {'customer_id': {'type': 'string'}, 'issue_summary': {'type': 'string'}, 'priority': {'type': 'string', 'enum': ['low', 'normal', 'high']}}, 'required': ['customer_id', 'issue_summary', 'priority'], 'additionalProperties': False},
-        )
-    ],
-)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>MCPToolCall(
-    name='get_customer_profile',
-    args={'customer_id': 'C-1006'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
-        )
-    ],
-    isError=False
-)
-)
-MCPToolCall(
-    name='get_order_status',
-    args={'order_id': 'ORD-9006'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
-        )
-    ],
-    isError=False
-)
-)
-MCPToolCall(
-    name='create_support_ticket',
-    args={'customer_id': 'C-1006', 'issue_summary': 'Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.', 'priority': 'high'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.", "priority": "high", "status": "open", "created_at": "2026-07-15T19:30:16"}'
-        )
-    ],
-    isError=False
-)
-)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LLMTestCase(
-    input='Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.',
-    actual_output='Here’s what I found and what I’ve done:\n\n- Order and status: ORD-9006 for an office chair is currently delayed.\n- Reason for delay: Inventory transfer from another warehouse.\n- Current estimated delivery: 2026-07-18.\n- Customer profile: Kabir Bose (Silver), email kabir@example.com.\n\nTicket opened:\n- Ticket ID: T-1001\n- Priority: High\n- Status: Open\n- Summary: Escalated the delay for ORD-9006; requested checks on expediting or alternative fulfillment and set up proactive updates to kabir@example.com.\n\nNext steps:\n- We’ll monitor the shipment and send updates if anything changes.\n- If you prefer a different contact method or want us to explore switching to an in-stock alternative, expediting options, or other arrangements, let me know your preference.',
-    expected_output='Look up C-1006, inspect ORD-9006, explain the inventory-transfer delay, and create a high-priority ticket.',
-    mcp_servers=[dummy_support_server],
-    mcp_tools_called=[
-        MCPToolCall(
-            name='get_customer_profile',
-            args={'customer_id': 'C-1006'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
-                )
-            ],
-            isError=False
-        )
-        ),
-        MCPToolCall(
-            name='get_order_status',
-            args={'order_id': 'ORD-9006'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
-                )
-            ],
-            isError=False
-        )
-        ),
-        MCPToolCall(
-            name='create_support_ticket',
-            args={'customer_id': 'C-1006', 'issue_summary': 'Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.', 'priority': 'high'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.", "priority": "high", "status": "open", "created_at": "2026-07-15T19:30:16"}'
-                )
-            ],
-            isError=False
-        )
-        )
-    ],
-)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ConversationalTestCase(
-    turns=[
-        Turn(role="user", content='Customer C-1006 is upset about a delayed office chair. Find the reason and open a high priority ticket.'),
-        Turn(
-            role="assistant",
-            content='Here’s what I found and what I’ve done:\n\n- Order and status: ORD-9006 for an office chair is currently delayed.\n- Reason for delay: Inventory transfer from another warehouse.\n- Current estimated delivery: 2026-07-18.\n- Customer profile: Kabir Bose (Silver), email kabir@example.com.\n\nTicket opened:\n- Ticket ID: T-1001\n- Priority: High\n- Status: Open\n- Summary: Escalated the delay for ORD-9006; requested checks on expediting or alternative fulfillment and set up proactive updates to kabir@example.com.\n\nNext steps:\n- We’ll monitor the shipment and send updates if anything changes.\n- If you prefer a different contact method or want us to explore switching to an in-stock alternative, expediting options, or other arrangements, let me know your preference.',
-            mcp_tools_called=[
-                    MCPToolCall(
-                        name='get_customer_profile',
-                        args={'customer_id': 'C-1006'},
-                        result=CallToolResult(
-                        content=[
-                            TextContent(
-                                type="text",
-                                text='{"customer_id": "C-1006", "name": "Kabir Bose", "tier": "Silver", "primary_order_id": "ORD-9006", "email": "kabir@example.com"}'
-                            )
-                        ],
-                        isError=False
-                    )
-                    ),
-                    MCPToolCall(
-                        name='get_order_status',
-                        args={'order_id': 'ORD-9006'},
-                        result=CallToolResult(
-                        content=[
-                            TextContent(
-                                type="text",
-                                text='{"order_id": "ORD-9006", "customer_id": "C-1006", "status": "delayed", "item": "Office chair", "amount": 249.0, "delay_reason": "Inventory transfer from another warehouse.", "estimated_delivery": "2026-07-18"}'
-                            )
-                        ],
-                        isError=False
-                    )
-                    ),
-                    MCPToolCall(
-                        name='create_support_ticket',
-                        args={'customer_id': 'C-1006', 'issue_summary': 'Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.', 'priority': 'high'},
-                        result=CallToolResult(
-                        content=[
-                            TextContent(
-                                type="text",
-                                text='{"ticket_id": "T-1001", "customer_id": "C-1006", "issue_summary": "Customer is upset about delayed order ORD-9006 (Office chair). Order status: delayed due to inventory transfer from another warehouse. Current ETA: 2026-07-18. Request high-priority escalation, check if expediting or alternative fulfillment is possible, and set up proactive updates to the customer at kabir@example.com.", "priority": "high", "status": "open", "created_at": "2026-07-15T19:30:16"}'
-                            )
-                        ],
-                        isError=False
-                    )
-                    )
-            ],
-        ),
-    ],
-    mcp_servers=[dummy_support_server],
-)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CASE-008-20260715193141</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>dummy_support_server = MCPServer(
-    server_name="dummy_support",
-    transport="streamable-http",
-    available_tools=[
-        Tool(
-            name='get_customer_profile',
-            description='Get a customer profile by customer ID.',
-            inputSchema={'type': 'object', 'properties': {'customer_id': {'type': 'string', 'description': 'Customer ID such as C-1002.'}}, 'required': ['customer_id'], 'additionalProperties': False},
-        ),
-        Tool(
-            name='get_order_status',
-            description='Get order status and order details by order ID.',
-            inputSchema={'type': 'object', 'properties': {'order_id': {'type': 'string', 'description': 'Order ID such as ORD-9002.'}}, 'required': ['order_id'], 'additionalProperties': False},
-        ),
-        Tool(
-            name='search_policy_docs',
-            description='Search support policy documents.',
-            inputSchema={'type': 'object', 'properties': {'query': {'type': 'string', 'description': 'Policy search query.'}}, 'required': ['query'], 'additionalProperties': False},
-        ),
-        Tool(
-            name='calculate_refund',
-            description='Calculate refund eligibility for an order.',
-            inputSchema={'type': 'object', 'properties': {'order_id': {'type': 'string'}, 'reason': {'type': 'string'}}, 'required': ['order_id', 'reason'], 'additionalProperties': False},
-        ),
-        Tool(
-            name='create_support_ticket',
-            description='Create a support ticket for a customer issue.',
-            inputSchema={'type': 'object', 'properties': {'customer_id': {'type': 'string'}, 'issue_summary': {'type': 'string'}, 'priority': {'type': 'string', 'enum': ['low', 'normal', 'high']}}, 'required': ['customer_id', 'issue_summary', 'priority'], 'additionalProperties': False},
-        )
-    ],
-)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MCPToolCall(
-    name='get_customer_profile',
     args={'customer_id': 'C-1004'},
     result=CallToolResult(
     content=[
@@ -3055,53 +1508,14 @@
     ],
     isError=False
 )
-)
-MCPToolCall(
-    name='search_policy_docs',
-    args={'query': 'shipping-status updates notification email tracking when order is processing'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"query": "shipping-status updates notification email tracking when order is processing", "matches": [{"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
-        )
-    ],
-    isError=False
-)
-)
-MCPToolCall(
-    name='search_policy_docs',
-    args={'query': 'address change after order placed processing policy hold at carrier pickup reroute'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"query": "address change after order placed processing policy hold at carrier pickup reroute", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
-        )
-    ],
-    isError=False
-)
-)
-MCPToolCall(
-    name='search_policy_docs',
-    args={'query': 'expedited shipping request after order placed policy'},
-    result=CallToolResult(
-    content=[
-        TextContent(
-            type="text",
-            text='{"query": "expedited shipping request after order placed policy", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
-        )
-    ],
-    isError=False
-)
 )</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>LLMTestCase(
     input='Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.',
-    actual_output='Here’s what I see for your order:\n\n- Customer: Dev Kapoor (C-1004)\n- Order: ORD-9004 — Ergonomic keyboard\n- Status: Processing\n- Estimated delivery date: 2026-07-16\n\nPolicy reference: For processing orders, we share the current status and the estimated delivery date when available.\n\nRecommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.',
+    actual_output='I checked your order. The ergonomic keyboard (order ORD-9004) is currently processing and is estimated to be delivered on 2026-07-16.\n\nIf that timing conflicts with your travel, I can look into available options (such as updating the delivery address or arranging a carrier hold, if eligible). Next best step: let me know your departure date and whether you want me to check delivery-change options or create a support ticket on your behalf.',
     expected_output='Look up C-1004, inspect ORD-9004, and share the processing status with estimated delivery.',
     mcp_servers=[dummy_support_server],
     mcp_tools_called=[
@@ -3130,58 +1544,19 @@
             ],
             isError=False
         )
-        ),
-        MCPToolCall(
-            name='search_policy_docs',
-            args={'query': 'shipping-status updates notification email tracking when order is processing'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"query": "shipping-status updates notification email tracking when order is processing", "matches": [{"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
-                )
-            ],
-            isError=False
-        )
-        ),
-        MCPToolCall(
-            name='search_policy_docs',
-            args={'query': 'address change after order placed processing policy hold at carrier pickup reroute'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"query": "address change after order placed processing policy hold at carrier pickup reroute", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
-                )
-            ],
-            isError=False
-        )
-        ),
-        MCPToolCall(
-            name='search_policy_docs',
-            args={'query': 'expedited shipping request after order placed policy'},
-            result=CallToolResult(
-            content=[
-                TextContent(
-                    type="text",
-                    text='{"query": "expedited shipping request after order placed policy", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
-                )
-            ],
-            isError=False
-        )
         )
     ],
 )</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>ConversationalTestCase(
     turns=[
         Turn(role="user", content='Customer C-1004 is travelling soon and asks when the ergonomic keyboard will arrive.'),
         Turn(
             role="assistant",
-            content='Here’s what I see for your order:\n\n- Customer: Dev Kapoor (C-1004)\n- Order: ORD-9004 — Ergonomic keyboard\n- Status: Processing\n- Estimated delivery date: 2026-07-16\n\nPolicy reference: For processing orders, we share the current status and the estimated delivery date when available.\n\nRecommended next step: Please let me know if 2026-07-16 works with your travel schedule. If you’ll be away before then, tell me your travel dates and I can advise the best next step.',
+            content='I checked your order. The ergonomic keyboard (order ORD-9004) is currently processing and is estimated to be delivered on 2026-07-16.\n\nIf that timing conflicts with your travel, I can look into available options (such as updating the delivery address or arranging a carrier hold, if eligible). Next best step: let me know your departure date and whether you want me to check delivery-change options or create a support ticket on your behalf.',
             mcp_tools_called=[
                     MCPToolCall(
                         name='get_customer_profile',
@@ -3208,48 +1583,11 @@
                         ],
                         isError=False
                     )
-                    ),
-                    MCPToolCall(
-                        name='search_policy_docs',
-                        args={'query': 'shipping-status updates notification email tracking when order is processing'},
-                        result=CallToolResult(
-                        content=[
-                            TextContent(
-                                type="text",
-                                text='{"query": "shipping-status updates notification email tracking when order is processing", "matches": [{"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
-                            )
-                        ],
-                        isError=False
-                    )
-                    ),
-                    MCPToolCall(
-                        name='search_policy_docs',
-                        args={'query': 'address change after order placed processing policy hold at carrier pickup reroute'},
-                        result=CallToolResult(
-                        content=[
-                            TextContent(
-                                type="text",
-                                text='{"query": "address change after order placed processing policy hold at carrier pickup reroute", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
-                            )
-                        ],
-                        isError=False
-                    )
-                    ),
-                    MCPToolCall(
-                        name='search_policy_docs',
-                        args={'query': 'expedited shipping request after order placed policy'},
-                        result=CallToolResult(
-                        content=[
-                            TextContent(
-                                type="text",
-                                text='{"query": "expedited shipping request after order placed policy", "matches": [{"policy_id": "refund", "title": "Refund policy", "summary": "Most delivered items are refundable within 30 days. Damaged items can be escalated after 30 days for manual review."}, {"policy_id": "delivery", "title": "Delivery delay policy", "summary": "If an order is delayed, share the reason and estimated delivery date. Shipping fees may be refunded for delays over 5 days."}, {"policy_id": "damaged_item", "title": "Damaged item policy", "summary": "Damaged delivered items should be reviewed with order details. Create a high-priority ticket for expensive or urgent damaged-item cases."}, {"policy_id": "cancellation", "title": "Cancellation policy", "summary": "Cancelled orders should be explained using the cancellation reason. Ask the customer to retry payment or contact billing when payment authorization fails."}, {"policy_id": "shipping_status", "title": "Shipping status policy", "summary": "For shipped or processing orders, share the current status and estimated delivery date when available."}]}'
-                            )
-                        ],
-                        isError=False
-                    )
                     )
             ],
         ),
+        Turn(role="user", content='Thank you.'),
+        Turn(role="assistant", content='You are welcome. I hope the information provided was helpful.'),
     ],
     mcp_servers=[dummy_support_server],
 )</t>
